--- a/email/data/Chair-Cochair.xlsx
+++ b/email/data/Chair-Cochair.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\admin\Coding\panchi\iumrs_icm\email\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E89B78C-94BA-4E5E-BD1B-DC2696A1607D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1353C1AE-5BC2-418B-A224-93E082B4EB71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Chair-cochairs" sheetId="9" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="678" uniqueCount="255">
   <si>
     <t>Total KN</t>
   </si>
@@ -842,6 +842,9 @@
   </si>
   <si>
     <t>Dr. Wiwat Nuansing</t>
+  </si>
+  <si>
+    <t>Dr. Phatthamon Kongkhambut</t>
   </si>
 </sst>
 </file>
@@ -1427,16 +1430,16 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A3:H58"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="13.2"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="12.75"/>
   <cols>
-    <col min="1" max="1" width="4.6640625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="69.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.6640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="42.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="67.21875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="26.5546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.7109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="69.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.7109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="42.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="67.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="26.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="3" spans="1:8">
@@ -2066,7 +2069,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="18">
+    <row r="30" spans="1:7" ht="18.75">
       <c r="A30">
         <v>6</v>
       </c>
@@ -2089,7 +2092,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="18">
+    <row r="31" spans="1:7" ht="18.75">
       <c r="A31">
         <v>7</v>
       </c>
@@ -2158,7 +2161,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="18">
+    <row r="34" spans="1:7" ht="18.75">
       <c r="A34">
         <v>8</v>
       </c>
@@ -2273,7 +2276,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="39" spans="1:7" ht="18">
+    <row r="39" spans="1:7" ht="18.75">
       <c r="A39">
         <v>10</v>
       </c>
@@ -2471,7 +2474,7 @@
         <v>187</v>
       </c>
       <c r="E47" t="s">
-        <v>188</v>
+        <v>254</v>
       </c>
       <c r="F47" t="s">
         <v>21</v>
@@ -2747,20 +2750,20 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:S1036"/>
-  <sheetFormatPr defaultColWidth="12.5546875" defaultRowHeight="15.75" customHeight="1"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="40" customWidth="1"/>
-    <col min="2" max="2" width="13.44140625" customWidth="1"/>
-    <col min="3" max="3" width="32.109375" customWidth="1"/>
-    <col min="4" max="4" width="41.21875" customWidth="1"/>
-    <col min="5" max="5" width="23.44140625" customWidth="1"/>
+    <col min="2" max="2" width="13.42578125" customWidth="1"/>
+    <col min="3" max="3" width="32.140625" customWidth="1"/>
+    <col min="4" max="4" width="41.28515625" customWidth="1"/>
+    <col min="5" max="5" width="23.42578125" customWidth="1"/>
     <col min="6" max="6" width="32" customWidth="1"/>
-    <col min="10" max="10" width="15.44140625" customWidth="1"/>
-    <col min="11" max="11" width="17.88671875" customWidth="1"/>
-    <col min="12" max="12" width="16.77734375" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
+    <col min="11" max="11" width="17.85546875" customWidth="1"/>
+    <col min="12" max="12" width="16.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="13.2">
+    <row r="1" spans="1:19" ht="12.75">
       <c r="A1" s="1"/>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -2785,7 +2788,7 @@
       <c r="R1" s="2"/>
       <c r="S1" s="2"/>
     </row>
-    <row r="2" spans="1:19" ht="13.2">
+    <row r="2" spans="1:19" ht="12.75">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2812,7 +2815,7 @@
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
     </row>
-    <row r="3" spans="1:19" ht="17.399999999999999">
+    <row r="3" spans="1:19" ht="18.75">
       <c r="A3" s="4" t="s">
         <v>2</v>
       </c>
@@ -2855,7 +2858,7 @@
       <c r="R3" s="2"/>
       <c r="S3" s="2"/>
     </row>
-    <row r="4" spans="1:19" ht="18">
+    <row r="4" spans="1:19" ht="18.75">
       <c r="A4" s="8"/>
       <c r="B4" s="9" t="s">
         <v>13</v>
@@ -2898,7 +2901,7 @@
       <c r="R4" s="2"/>
       <c r="S4" s="2"/>
     </row>
-    <row r="5" spans="1:19" ht="18">
+    <row r="5" spans="1:19" ht="18.75">
       <c r="A5" s="8" t="s">
         <v>17</v>
       </c>
@@ -2931,7 +2934,7 @@
       <c r="R5" s="2"/>
       <c r="S5" s="2"/>
     </row>
-    <row r="6" spans="1:19" ht="18">
+    <row r="6" spans="1:19" ht="18.75">
       <c r="A6" s="13"/>
       <c r="B6" s="18" t="s">
         <v>23</v>
@@ -2962,7 +2965,7 @@
       <c r="R6" s="2"/>
       <c r="S6" s="2"/>
     </row>
-    <row r="7" spans="1:19" ht="18">
+    <row r="7" spans="1:19" ht="18.75">
       <c r="A7" s="13"/>
       <c r="B7" s="20" t="s">
         <v>23</v>
@@ -3024,7 +3027,7 @@
       <c r="R8" s="2"/>
       <c r="S8" s="2"/>
     </row>
-    <row r="9" spans="1:19" ht="18">
+    <row r="9" spans="1:19" ht="18.75">
       <c r="A9" s="13"/>
       <c r="B9" s="20" t="s">
         <v>23</v>
@@ -3055,7 +3058,7 @@
       <c r="R9" s="2"/>
       <c r="S9" s="2"/>
     </row>
-    <row r="10" spans="1:19" ht="17.399999999999999">
+    <row r="10" spans="1:19" ht="18.75">
       <c r="A10" s="13"/>
       <c r="B10" s="9" t="s">
         <v>13</v>
@@ -3098,7 +3101,7 @@
       <c r="R10" s="2"/>
       <c r="S10" s="2"/>
     </row>
-    <row r="11" spans="1:19" ht="18">
+    <row r="11" spans="1:19" ht="18.75">
       <c r="A11" s="16" t="s">
         <v>40</v>
       </c>
@@ -3131,7 +3134,7 @@
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
     </row>
-    <row r="12" spans="1:19" ht="18">
+    <row r="12" spans="1:19" ht="18.75">
       <c r="A12" s="13"/>
       <c r="B12" s="18" t="s">
         <v>23</v>
@@ -3162,7 +3165,7 @@
       <c r="R12" s="2"/>
       <c r="S12" s="2"/>
     </row>
-    <row r="13" spans="1:19" ht="18">
+    <row r="13" spans="1:19" ht="18.75">
       <c r="A13" s="13"/>
       <c r="B13" s="18" t="s">
         <v>23</v>
@@ -3193,7 +3196,7 @@
       <c r="R13" s="2"/>
       <c r="S13" s="2"/>
     </row>
-    <row r="14" spans="1:19" ht="18">
+    <row r="14" spans="1:19" ht="18.75">
       <c r="A14" s="13"/>
       <c r="B14" s="18" t="s">
         <v>23</v>
@@ -3224,7 +3227,7 @@
       <c r="R14" s="2"/>
       <c r="S14" s="2"/>
     </row>
-    <row r="15" spans="1:19" ht="21">
+    <row r="15" spans="1:19" ht="21.75">
       <c r="A15" s="13"/>
       <c r="B15" s="18" t="s">
         <v>23</v>
@@ -3255,7 +3258,7 @@
       <c r="R15" s="2"/>
       <c r="S15" s="2"/>
     </row>
-    <row r="16" spans="1:19" ht="25.8">
+    <row r="16" spans="1:19" ht="18.75">
       <c r="A16" s="13"/>
       <c r="B16" s="38" t="s">
         <v>23</v>
@@ -3286,7 +3289,7 @@
       <c r="R16" s="2"/>
       <c r="S16" s="2"/>
     </row>
-    <row r="17" spans="1:19" ht="18">
+    <row r="17" spans="1:19" ht="18.75">
       <c r="A17" s="8" t="s">
         <v>64</v>
       </c>
@@ -3329,7 +3332,7 @@
       <c r="R17" s="2"/>
       <c r="S17" s="2"/>
     </row>
-    <row r="18" spans="1:19" ht="18">
+    <row r="18" spans="1:19" ht="18.75">
       <c r="B18" s="14" t="s">
         <v>18</v>
       </c>
@@ -3359,7 +3362,7 @@
       <c r="R18" s="2"/>
       <c r="S18" s="2"/>
     </row>
-    <row r="19" spans="1:19" ht="18">
+    <row r="19" spans="1:19" ht="18.75">
       <c r="A19" s="13"/>
       <c r="B19" s="18" t="s">
         <v>23</v>
@@ -3390,7 +3393,7 @@
       <c r="R19" s="2"/>
       <c r="S19" s="2"/>
     </row>
-    <row r="20" spans="1:19" ht="18">
+    <row r="20" spans="1:19" ht="18.75">
       <c r="A20" s="13"/>
       <c r="B20" s="18" t="s">
         <v>23</v>
@@ -3421,7 +3424,7 @@
       <c r="R20" s="2"/>
       <c r="S20" s="2"/>
     </row>
-    <row r="21" spans="1:19" ht="18">
+    <row r="21" spans="1:19" ht="18.75">
       <c r="A21" s="8" t="s">
         <v>80</v>
       </c>
@@ -3452,7 +3455,7 @@
       <c r="R21" s="2"/>
       <c r="S21" s="2"/>
     </row>
-    <row r="22" spans="1:19" ht="18">
+    <row r="22" spans="1:19" ht="18.75">
       <c r="A22" s="8"/>
       <c r="B22" s="14" t="s">
         <v>18</v>
@@ -3495,7 +3498,7 @@
       <c r="R22" s="2"/>
       <c r="S22" s="2"/>
     </row>
-    <row r="23" spans="1:19" ht="18">
+    <row r="23" spans="1:19" ht="18.75">
       <c r="A23" s="40"/>
       <c r="B23" s="18" t="s">
         <v>23</v>
@@ -3526,7 +3529,7 @@
       <c r="R23" s="2"/>
       <c r="S23" s="2"/>
     </row>
-    <row r="24" spans="1:19" ht="18">
+    <row r="24" spans="1:19" ht="18.75">
       <c r="A24" s="13"/>
       <c r="B24" s="18" t="s">
         <v>23</v>
@@ -3557,7 +3560,7 @@
       <c r="R24" s="2"/>
       <c r="S24" s="2"/>
     </row>
-    <row r="25" spans="1:19" ht="18">
+    <row r="25" spans="1:19" ht="18.75">
       <c r="A25" s="13"/>
       <c r="B25" s="18" t="s">
         <v>23</v>
@@ -3588,7 +3591,7 @@
       <c r="R25" s="2"/>
       <c r="S25" s="2"/>
     </row>
-    <row r="26" spans="1:19" ht="18">
+    <row r="26" spans="1:19" ht="18.75">
       <c r="A26" s="13"/>
       <c r="B26" s="18" t="s">
         <v>23</v>
@@ -3619,7 +3622,7 @@
       <c r="R26" s="2"/>
       <c r="S26" s="2"/>
     </row>
-    <row r="27" spans="1:19" ht="54">
+    <row r="27" spans="1:19" ht="56.25">
       <c r="A27" s="44" t="s">
         <v>98</v>
       </c>
@@ -3654,7 +3657,7 @@
       <c r="R27" s="2"/>
       <c r="S27" s="2"/>
     </row>
-    <row r="28" spans="1:19" ht="18">
+    <row r="28" spans="1:19" ht="18.75">
       <c r="B28" s="14" t="s">
         <v>18</v>
       </c>
@@ -3686,7 +3689,7 @@
       <c r="R28" s="2"/>
       <c r="S28" s="2"/>
     </row>
-    <row r="29" spans="1:19" ht="18">
+    <row r="29" spans="1:19" ht="18.75">
       <c r="A29" s="13"/>
       <c r="B29" s="18" t="s">
         <v>23</v>
@@ -3720,7 +3723,7 @@
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
     </row>
-    <row r="30" spans="1:19" ht="18">
+    <row r="30" spans="1:19" ht="18.75">
       <c r="A30" s="8" t="s">
         <v>107</v>
       </c>
@@ -3753,7 +3756,7 @@
       <c r="R30" s="2"/>
       <c r="S30" s="2"/>
     </row>
-    <row r="31" spans="1:19" ht="18">
+    <row r="31" spans="1:19" ht="18.75">
       <c r="A31" s="13"/>
       <c r="B31" s="18" t="s">
         <v>23</v>
@@ -3784,7 +3787,7 @@
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
     </row>
-    <row r="32" spans="1:19" ht="16.8">
+    <row r="32" spans="1:19" ht="16.5">
       <c r="A32" s="13"/>
       <c r="B32" s="20"/>
       <c r="C32" s="13"/>
@@ -3805,7 +3808,7 @@
       <c r="R32" s="2"/>
       <c r="S32" s="2"/>
     </row>
-    <row r="33" spans="1:19" ht="18">
+    <row r="33" spans="1:19" ht="18.75">
       <c r="A33" s="8" t="s">
         <v>115</v>
       </c>
@@ -3842,7 +3845,7 @@
       <c r="R33" s="2"/>
       <c r="S33" s="2"/>
     </row>
-    <row r="34" spans="1:19" ht="18">
+    <row r="34" spans="1:19" ht="18.75">
       <c r="B34" s="14" t="s">
         <v>18</v>
       </c>
@@ -3872,7 +3875,7 @@
       <c r="R34" s="2"/>
       <c r="S34" s="2"/>
     </row>
-    <row r="35" spans="1:19" ht="18">
+    <row r="35" spans="1:19" ht="18.75">
       <c r="A35" s="13"/>
       <c r="B35" s="18" t="s">
         <v>23</v>
@@ -3903,7 +3906,7 @@
       <c r="R35" s="2"/>
       <c r="S35" s="2"/>
     </row>
-    <row r="36" spans="1:19" ht="18">
+    <row r="36" spans="1:19" ht="18.75">
       <c r="A36" s="13"/>
       <c r="B36" s="18" t="s">
         <v>23</v>
@@ -3934,7 +3937,7 @@
       <c r="R36" s="2"/>
       <c r="S36" s="2"/>
     </row>
-    <row r="37" spans="1:19" ht="18">
+    <row r="37" spans="1:19" ht="18.75">
       <c r="A37" s="13"/>
       <c r="B37" s="18" t="s">
         <v>23</v>
@@ -3965,7 +3968,7 @@
       <c r="R37" s="2"/>
       <c r="S37" s="2"/>
     </row>
-    <row r="38" spans="1:19" ht="18">
+    <row r="38" spans="1:19" ht="18.75">
       <c r="A38" s="8" t="s">
         <v>130</v>
       </c>
@@ -4000,7 +4003,7 @@
       <c r="R38" s="2"/>
       <c r="S38" s="2"/>
     </row>
-    <row r="39" spans="1:19" ht="18">
+    <row r="39" spans="1:19" ht="18.75">
       <c r="B39" s="14" t="s">
         <v>18</v>
       </c>
@@ -4030,7 +4033,7 @@
       <c r="R39" s="2"/>
       <c r="S39" s="2"/>
     </row>
-    <row r="40" spans="1:19" ht="18">
+    <row r="40" spans="1:19" ht="18.75">
       <c r="A40" s="40"/>
       <c r="B40" s="18" t="s">
         <v>23</v>
@@ -4061,7 +4064,7 @@
       <c r="R40" s="2"/>
       <c r="S40" s="2"/>
     </row>
-    <row r="41" spans="1:19" ht="18">
+    <row r="41" spans="1:19" ht="18.75">
       <c r="A41" s="13"/>
       <c r="B41" s="18" t="s">
         <v>23</v>
@@ -4092,7 +4095,7 @@
       <c r="R41" s="2"/>
       <c r="S41" s="2"/>
     </row>
-    <row r="42" spans="1:19" ht="18">
+    <row r="42" spans="1:19" ht="18.75">
       <c r="A42" s="8" t="s">
         <v>143</v>
       </c>
@@ -4127,7 +4130,7 @@
       <c r="R42" s="2"/>
       <c r="S42" s="2"/>
     </row>
-    <row r="43" spans="1:19" ht="18">
+    <row r="43" spans="1:19" ht="18.75">
       <c r="B43" s="14" t="s">
         <v>18</v>
       </c>
@@ -4157,7 +4160,7 @@
       <c r="R43" s="2"/>
       <c r="S43" s="2"/>
     </row>
-    <row r="44" spans="1:19" ht="18">
+    <row r="44" spans="1:19" ht="18.75">
       <c r="A44" s="13"/>
       <c r="B44" s="18" t="s">
         <v>23</v>
@@ -4188,7 +4191,7 @@
       <c r="R44" s="2"/>
       <c r="S44" s="2"/>
     </row>
-    <row r="45" spans="1:19" ht="18">
+    <row r="45" spans="1:19" ht="18.75">
       <c r="A45" s="13"/>
       <c r="B45" s="18" t="s">
         <v>23</v>
@@ -4219,7 +4222,7 @@
       <c r="R45" s="2"/>
       <c r="S45" s="2"/>
     </row>
-    <row r="46" spans="1:19" ht="54">
+    <row r="46" spans="1:19" ht="56.25">
       <c r="A46" s="44" t="s">
         <v>154</v>
       </c>
@@ -4260,7 +4263,7 @@
       <c r="R46" s="2"/>
       <c r="S46" s="2"/>
     </row>
-    <row r="47" spans="1:19" ht="18">
+    <row r="47" spans="1:19" ht="18.75">
       <c r="B47" s="14" t="s">
         <v>18</v>
       </c>
@@ -4290,7 +4293,7 @@
       <c r="R47" s="2"/>
       <c r="S47" s="2"/>
     </row>
-    <row r="48" spans="1:19" ht="18">
+    <row r="48" spans="1:19" ht="18.75">
       <c r="A48" s="13"/>
       <c r="B48" s="18" t="s">
         <v>23</v>
@@ -4321,7 +4324,7 @@
       <c r="R48" s="2"/>
       <c r="S48" s="2"/>
     </row>
-    <row r="49" spans="1:19" ht="18">
+    <row r="49" spans="1:19" ht="18.75">
       <c r="A49" s="13"/>
       <c r="B49" s="18" t="s">
         <v>23</v>
@@ -4344,7 +4347,7 @@
       <c r="R49" s="2"/>
       <c r="S49" s="2"/>
     </row>
-    <row r="50" spans="1:19" ht="28.8">
+    <row r="50" spans="1:19" ht="30">
       <c r="A50" s="8" t="s">
         <v>164</v>
       </c>
@@ -4387,7 +4390,7 @@
       <c r="R50" s="2"/>
       <c r="S50" s="2"/>
     </row>
-    <row r="51" spans="1:19" ht="18">
+    <row r="51" spans="1:19" ht="18.75">
       <c r="B51" s="14" t="s">
         <v>18</v>
       </c>
@@ -4417,7 +4420,7 @@
       <c r="R51" s="2"/>
       <c r="S51" s="2"/>
     </row>
-    <row r="52" spans="1:19" ht="18">
+    <row r="52" spans="1:19" ht="18.75">
       <c r="A52" s="13"/>
       <c r="B52" s="18" t="s">
         <v>23</v>
@@ -4448,7 +4451,7 @@
       <c r="R52" s="2"/>
       <c r="S52" s="2"/>
     </row>
-    <row r="53" spans="1:19" ht="18">
+    <row r="53" spans="1:19" ht="18.75">
       <c r="A53" s="13"/>
       <c r="B53" s="18" t="s">
         <v>23</v>
@@ -4479,7 +4482,7 @@
       <c r="R53" s="2"/>
       <c r="S53" s="2"/>
     </row>
-    <row r="54" spans="1:19" ht="18">
+    <row r="54" spans="1:19" ht="18.75">
       <c r="A54" s="13"/>
       <c r="B54" s="18" t="s">
         <v>23</v>
@@ -4510,7 +4513,7 @@
       <c r="R54" s="2"/>
       <c r="S54" s="2"/>
     </row>
-    <row r="55" spans="1:19" ht="18">
+    <row r="55" spans="1:19" ht="18.75">
       <c r="A55" s="8" t="s">
         <v>176</v>
       </c>
@@ -4547,7 +4550,7 @@
       <c r="R55" s="2"/>
       <c r="S55" s="2"/>
     </row>
-    <row r="56" spans="1:19" ht="18">
+    <row r="56" spans="1:19" ht="18.75">
       <c r="B56" s="14" t="s">
         <v>18</v>
       </c>
@@ -4577,7 +4580,7 @@
       <c r="R56" s="2"/>
       <c r="S56" s="2"/>
     </row>
-    <row r="57" spans="1:19" ht="18">
+    <row r="57" spans="1:19" ht="18.75">
       <c r="A57" s="13"/>
       <c r="B57" s="18" t="s">
         <v>23</v>
@@ -4608,7 +4611,7 @@
       <c r="R57" s="2"/>
       <c r="S57" s="2"/>
     </row>
-    <row r="58" spans="1:19" ht="20.399999999999999">
+    <row r="58" spans="1:19" ht="20.25">
       <c r="A58" s="13"/>
       <c r="B58" s="50" t="s">
         <v>180</v>
@@ -4639,7 +4642,7 @@
       <c r="R58" s="2"/>
       <c r="S58" s="2"/>
     </row>
-    <row r="59" spans="1:19" ht="18">
+    <row r="59" spans="1:19" ht="18.75">
       <c r="A59" s="13"/>
       <c r="B59" s="50" t="s">
         <v>23</v>
@@ -4701,7 +4704,7 @@
       <c r="R60" s="2"/>
       <c r="S60" s="2"/>
     </row>
-    <row r="61" spans="1:19" ht="18">
+    <row r="61" spans="1:19" ht="18.75">
       <c r="A61" s="8" t="s">
         <v>190</v>
       </c>
@@ -4738,7 +4741,7 @@
       <c r="R61" s="2"/>
       <c r="S61" s="2"/>
     </row>
-    <row r="62" spans="1:19" ht="18">
+    <row r="62" spans="1:19" ht="18.75">
       <c r="B62" s="14" t="s">
         <v>18</v>
       </c>
@@ -4768,7 +4771,7 @@
       <c r="R62" s="2"/>
       <c r="S62" s="2"/>
     </row>
-    <row r="63" spans="1:19" ht="18">
+    <row r="63" spans="1:19" ht="18.75">
       <c r="A63" s="2"/>
       <c r="B63" s="18" t="s">
         <v>23</v>
@@ -4799,7 +4802,7 @@
       <c r="R63" s="2"/>
       <c r="S63" s="2"/>
     </row>
-    <row r="64" spans="1:19" ht="18">
+    <row r="64" spans="1:19" ht="18.75">
       <c r="A64" s="13"/>
       <c r="B64" s="18" t="s">
         <v>23</v>
@@ -4830,7 +4833,7 @@
       <c r="R64" s="2"/>
       <c r="S64" s="2"/>
     </row>
-    <row r="65" spans="1:19" ht="18">
+    <row r="65" spans="1:19" ht="18.75">
       <c r="A65" s="8" t="s">
         <v>197</v>
       </c>
@@ -4873,7 +4876,7 @@
       <c r="R65" s="2"/>
       <c r="S65" s="2"/>
     </row>
-    <row r="66" spans="1:19" ht="18">
+    <row r="66" spans="1:19" ht="18.75">
       <c r="B66" s="14" t="s">
         <v>18</v>
       </c>
@@ -4905,7 +4908,7 @@
       <c r="R66" s="2"/>
       <c r="S66" s="2"/>
     </row>
-    <row r="67" spans="1:19" ht="18">
+    <row r="67" spans="1:19" ht="18.75">
       <c r="A67" s="13"/>
       <c r="B67" s="18" t="s">
         <v>23</v>
@@ -4936,7 +4939,7 @@
       <c r="R67" s="2"/>
       <c r="S67" s="2"/>
     </row>
-    <row r="68" spans="1:19" ht="18">
+    <row r="68" spans="1:19" ht="18.75">
       <c r="A68" s="13"/>
       <c r="B68" s="18" t="s">
         <v>23</v>
@@ -4967,7 +4970,7 @@
       <c r="R68" s="2"/>
       <c r="S68" s="2"/>
     </row>
-    <row r="69" spans="1:19" ht="18">
+    <row r="69" spans="1:19" ht="18.75">
       <c r="A69" s="13"/>
       <c r="B69" s="18" t="s">
         <v>23</v>
@@ -4998,7 +5001,7 @@
       <c r="R69" s="2"/>
       <c r="S69" s="2"/>
     </row>
-    <row r="70" spans="1:19" ht="18">
+    <row r="70" spans="1:19" ht="18.75">
       <c r="A70" s="2"/>
       <c r="B70" s="18" t="s">
         <v>23</v>
@@ -5029,7 +5032,7 @@
       <c r="R70" s="2"/>
       <c r="S70" s="2"/>
     </row>
-    <row r="71" spans="1:19" ht="18">
+    <row r="71" spans="1:19" ht="18.75">
       <c r="A71" s="2"/>
       <c r="B71" s="18" t="s">
         <v>23</v>
@@ -5058,7 +5061,7 @@
       <c r="R71" s="2"/>
       <c r="S71" s="2"/>
     </row>
-    <row r="72" spans="1:19" ht="18">
+    <row r="72" spans="1:19" ht="18.75">
       <c r="A72" s="2"/>
       <c r="B72" s="18" t="s">
         <v>23</v>
@@ -5089,7 +5092,7 @@
       <c r="R72" s="2"/>
       <c r="S72" s="2"/>
     </row>
-    <row r="73" spans="1:19" ht="18">
+    <row r="73" spans="1:19" ht="18.75">
       <c r="A73" s="2"/>
       <c r="B73" s="18" t="s">
         <v>23</v>
@@ -5120,7 +5123,7 @@
       <c r="R73" s="2"/>
       <c r="S73" s="2"/>
     </row>
-    <row r="74" spans="1:19" ht="13.2">
+    <row r="74" spans="1:19" ht="12.75">
       <c r="A74" s="2"/>
       <c r="B74" s="2"/>
       <c r="D74" s="2"/>
@@ -5140,7 +5143,7 @@
       <c r="R74" s="2"/>
       <c r="S74" s="2"/>
     </row>
-    <row r="75" spans="1:19" ht="13.2">
+    <row r="75" spans="1:19" ht="12.75">
       <c r="A75" s="2"/>
       <c r="D75" s="2"/>
       <c r="E75" s="2"/>
@@ -5159,7 +5162,7 @@
       <c r="R75" s="2"/>
       <c r="S75" s="2"/>
     </row>
-    <row r="76" spans="1:19" ht="13.2">
+    <row r="76" spans="1:19" ht="12.75">
       <c r="A76" s="2"/>
       <c r="D76" s="2"/>
       <c r="E76" s="2"/>
@@ -5178,7 +5181,7 @@
       <c r="R76" s="2"/>
       <c r="S76" s="2"/>
     </row>
-    <row r="77" spans="1:19" ht="13.2">
+    <row r="77" spans="1:19" ht="12.75">
       <c r="A77" s="2"/>
       <c r="B77" s="2"/>
       <c r="D77" s="2"/>
@@ -5198,7 +5201,7 @@
       <c r="R77" s="2"/>
       <c r="S77" s="2"/>
     </row>
-    <row r="78" spans="1:19" ht="13.2">
+    <row r="78" spans="1:19" ht="12.75">
       <c r="A78" s="2"/>
       <c r="B78" s="2"/>
       <c r="D78" s="2"/>
@@ -5218,7 +5221,7 @@
       <c r="R78" s="2"/>
       <c r="S78" s="2"/>
     </row>
-    <row r="79" spans="1:19" ht="13.2">
+    <row r="79" spans="1:19" ht="12.75">
       <c r="A79" s="2"/>
       <c r="B79" s="2"/>
       <c r="C79" s="2"/>
@@ -5239,7 +5242,7 @@
       <c r="R79" s="2"/>
       <c r="S79" s="2"/>
     </row>
-    <row r="80" spans="1:19" ht="13.2">
+    <row r="80" spans="1:19" ht="12.75">
       <c r="A80" s="2"/>
       <c r="B80" s="2"/>
       <c r="C80" s="2"/>
@@ -5260,7 +5263,7 @@
       <c r="R80" s="2"/>
       <c r="S80" s="2"/>
     </row>
-    <row r="81" spans="1:19" ht="13.2">
+    <row r="81" spans="1:19" ht="12.75">
       <c r="A81" s="2"/>
       <c r="B81" s="2"/>
       <c r="C81" s="2"/>
@@ -5281,7 +5284,7 @@
       <c r="R81" s="2"/>
       <c r="S81" s="2"/>
     </row>
-    <row r="82" spans="1:19" ht="13.2">
+    <row r="82" spans="1:19" ht="12.75">
       <c r="A82" s="2"/>
       <c r="B82" s="2"/>
       <c r="C82" s="2"/>
@@ -5302,7 +5305,7 @@
       <c r="R82" s="2"/>
       <c r="S82" s="2"/>
     </row>
-    <row r="83" spans="1:19" ht="13.2">
+    <row r="83" spans="1:19" ht="12.75">
       <c r="A83" s="2"/>
       <c r="B83" s="2"/>
       <c r="C83" s="2"/>
@@ -5323,7 +5326,7 @@
       <c r="R83" s="2"/>
       <c r="S83" s="2"/>
     </row>
-    <row r="84" spans="1:19" ht="13.2">
+    <row r="84" spans="1:19" ht="12.75">
       <c r="A84" s="2"/>
       <c r="B84" s="2"/>
       <c r="C84" s="2"/>
@@ -5344,7 +5347,7 @@
       <c r="R84" s="2"/>
       <c r="S84" s="2"/>
     </row>
-    <row r="85" spans="1:19" ht="13.2">
+    <row r="85" spans="1:19" ht="12.75">
       <c r="A85" s="2"/>
       <c r="B85" s="2"/>
       <c r="C85" s="2"/>
@@ -5365,7 +5368,7 @@
       <c r="R85" s="2"/>
       <c r="S85" s="2"/>
     </row>
-    <row r="86" spans="1:19" ht="13.2">
+    <row r="86" spans="1:19" ht="12.75">
       <c r="A86" s="2"/>
       <c r="B86" s="2"/>
       <c r="C86" s="2"/>
@@ -5386,7 +5389,7 @@
       <c r="R86" s="2"/>
       <c r="S86" s="2"/>
     </row>
-    <row r="87" spans="1:19" ht="13.2">
+    <row r="87" spans="1:19" ht="12.75">
       <c r="A87" s="2"/>
       <c r="B87" s="2"/>
       <c r="C87" s="2"/>
@@ -5407,7 +5410,7 @@
       <c r="R87" s="2"/>
       <c r="S87" s="2"/>
     </row>
-    <row r="88" spans="1:19" ht="13.2">
+    <row r="88" spans="1:19" ht="12.75">
       <c r="A88" s="2"/>
       <c r="B88" s="2"/>
       <c r="C88" s="2"/>
@@ -5428,7 +5431,7 @@
       <c r="R88" s="2"/>
       <c r="S88" s="2"/>
     </row>
-    <row r="89" spans="1:19" ht="13.2">
+    <row r="89" spans="1:19" ht="12.75">
       <c r="A89" s="2"/>
       <c r="B89" s="2"/>
       <c r="C89" s="2"/>
@@ -5449,7 +5452,7 @@
       <c r="R89" s="2"/>
       <c r="S89" s="2"/>
     </row>
-    <row r="90" spans="1:19" ht="13.2">
+    <row r="90" spans="1:19" ht="12.75">
       <c r="A90" s="2"/>
       <c r="B90" s="2"/>
       <c r="C90" s="2"/>
@@ -5470,7 +5473,7 @@
       <c r="R90" s="2"/>
       <c r="S90" s="2"/>
     </row>
-    <row r="91" spans="1:19" ht="13.2">
+    <row r="91" spans="1:19" ht="12.75">
       <c r="A91" s="2"/>
       <c r="B91" s="2"/>
       <c r="C91" s="2"/>
@@ -5491,7 +5494,7 @@
       <c r="R91" s="2"/>
       <c r="S91" s="2"/>
     </row>
-    <row r="92" spans="1:19" ht="13.2">
+    <row r="92" spans="1:19" ht="12.75">
       <c r="A92" s="2"/>
       <c r="B92" s="2"/>
       <c r="C92" s="2"/>
@@ -5512,7 +5515,7 @@
       <c r="R92" s="2"/>
       <c r="S92" s="2"/>
     </row>
-    <row r="93" spans="1:19" ht="13.2">
+    <row r="93" spans="1:19" ht="12.75">
       <c r="A93" s="2"/>
       <c r="B93" s="2"/>
       <c r="C93" s="2"/>
@@ -5533,7 +5536,7 @@
       <c r="R93" s="2"/>
       <c r="S93" s="2"/>
     </row>
-    <row r="94" spans="1:19" ht="13.2">
+    <row r="94" spans="1:19" ht="12.75">
       <c r="A94" s="2"/>
       <c r="B94" s="2"/>
       <c r="C94" s="2"/>
@@ -5554,7 +5557,7 @@
       <c r="R94" s="2"/>
       <c r="S94" s="2"/>
     </row>
-    <row r="95" spans="1:19" ht="13.2">
+    <row r="95" spans="1:19" ht="12.75">
       <c r="A95" s="2"/>
       <c r="B95" s="2"/>
       <c r="C95" s="2"/>
@@ -5575,7 +5578,7 @@
       <c r="R95" s="2"/>
       <c r="S95" s="2"/>
     </row>
-    <row r="96" spans="1:19" ht="13.2">
+    <row r="96" spans="1:19" ht="12.75">
       <c r="A96" s="2"/>
       <c r="B96" s="2"/>
       <c r="C96" s="2"/>
@@ -5596,7 +5599,7 @@
       <c r="R96" s="2"/>
       <c r="S96" s="2"/>
     </row>
-    <row r="97" spans="1:19" ht="13.2">
+    <row r="97" spans="1:19" ht="12.75">
       <c r="A97" s="2"/>
       <c r="B97" s="2"/>
       <c r="C97" s="2"/>
@@ -5617,7 +5620,7 @@
       <c r="R97" s="2"/>
       <c r="S97" s="2"/>
     </row>
-    <row r="98" spans="1:19" ht="13.2">
+    <row r="98" spans="1:19" ht="12.75">
       <c r="A98" s="2"/>
       <c r="B98" s="2"/>
       <c r="C98" s="2"/>
@@ -5638,7 +5641,7 @@
       <c r="R98" s="2"/>
       <c r="S98" s="2"/>
     </row>
-    <row r="99" spans="1:19" ht="13.2">
+    <row r="99" spans="1:19" ht="12.75">
       <c r="A99" s="2"/>
       <c r="B99" s="2"/>
       <c r="C99" s="2"/>
@@ -5659,7 +5662,7 @@
       <c r="R99" s="2"/>
       <c r="S99" s="2"/>
     </row>
-    <row r="100" spans="1:19" ht="13.2">
+    <row r="100" spans="1:19" ht="12.75">
       <c r="A100" s="2"/>
       <c r="B100" s="2"/>
       <c r="C100" s="2"/>
@@ -5680,7 +5683,7 @@
       <c r="R100" s="2"/>
       <c r="S100" s="2"/>
     </row>
-    <row r="101" spans="1:19" ht="13.2">
+    <row r="101" spans="1:19" ht="12.75">
       <c r="A101" s="2"/>
       <c r="B101" s="2"/>
       <c r="C101" s="2"/>
@@ -5701,7 +5704,7 @@
       <c r="R101" s="2"/>
       <c r="S101" s="2"/>
     </row>
-    <row r="102" spans="1:19" ht="13.2">
+    <row r="102" spans="1:19" ht="12.75">
       <c r="A102" s="2"/>
       <c r="B102" s="2"/>
       <c r="C102" s="2"/>
@@ -5722,7 +5725,7 @@
       <c r="R102" s="2"/>
       <c r="S102" s="2"/>
     </row>
-    <row r="103" spans="1:19" ht="13.2">
+    <row r="103" spans="1:19" ht="12.75">
       <c r="A103" s="2"/>
       <c r="B103" s="2"/>
       <c r="C103" s="2"/>
@@ -5743,7 +5746,7 @@
       <c r="R103" s="2"/>
       <c r="S103" s="2"/>
     </row>
-    <row r="104" spans="1:19" ht="13.2">
+    <row r="104" spans="1:19" ht="12.75">
       <c r="A104" s="2"/>
       <c r="B104" s="2"/>
       <c r="C104" s="2"/>
@@ -5764,7 +5767,7 @@
       <c r="R104" s="2"/>
       <c r="S104" s="2"/>
     </row>
-    <row r="105" spans="1:19" ht="13.2">
+    <row r="105" spans="1:19" ht="12.75">
       <c r="A105" s="2"/>
       <c r="B105" s="2"/>
       <c r="C105" s="2"/>
@@ -5785,7 +5788,7 @@
       <c r="R105" s="2"/>
       <c r="S105" s="2"/>
     </row>
-    <row r="106" spans="1:19" ht="13.2">
+    <row r="106" spans="1:19" ht="12.75">
       <c r="A106" s="2"/>
       <c r="B106" s="2"/>
       <c r="C106" s="2"/>
@@ -5806,7 +5809,7 @@
       <c r="R106" s="2"/>
       <c r="S106" s="2"/>
     </row>
-    <row r="107" spans="1:19" ht="13.2">
+    <row r="107" spans="1:19" ht="12.75">
       <c r="A107" s="2"/>
       <c r="B107" s="2"/>
       <c r="C107" s="2"/>
@@ -5827,7 +5830,7 @@
       <c r="R107" s="2"/>
       <c r="S107" s="2"/>
     </row>
-    <row r="108" spans="1:19" ht="13.2">
+    <row r="108" spans="1:19" ht="12.75">
       <c r="A108" s="2"/>
       <c r="B108" s="2"/>
       <c r="C108" s="2"/>
@@ -5848,7 +5851,7 @@
       <c r="R108" s="2"/>
       <c r="S108" s="2"/>
     </row>
-    <row r="109" spans="1:19" ht="13.2">
+    <row r="109" spans="1:19" ht="12.75">
       <c r="A109" s="2"/>
       <c r="B109" s="2"/>
       <c r="C109" s="2"/>
@@ -5869,7 +5872,7 @@
       <c r="R109" s="2"/>
       <c r="S109" s="2"/>
     </row>
-    <row r="110" spans="1:19" ht="13.2">
+    <row r="110" spans="1:19" ht="12.75">
       <c r="A110" s="2"/>
       <c r="B110" s="2"/>
       <c r="C110" s="2"/>
@@ -5890,7 +5893,7 @@
       <c r="R110" s="2"/>
       <c r="S110" s="2"/>
     </row>
-    <row r="111" spans="1:19" ht="13.2">
+    <row r="111" spans="1:19" ht="12.75">
       <c r="A111" s="2"/>
       <c r="B111" s="2"/>
       <c r="C111" s="2"/>
@@ -5911,7 +5914,7 @@
       <c r="R111" s="2"/>
       <c r="S111" s="2"/>
     </row>
-    <row r="112" spans="1:19" ht="13.2">
+    <row r="112" spans="1:19" ht="12.75">
       <c r="A112" s="2"/>
       <c r="B112" s="2"/>
       <c r="C112" s="2"/>
@@ -5932,7 +5935,7 @@
       <c r="R112" s="2"/>
       <c r="S112" s="2"/>
     </row>
-    <row r="113" spans="1:19" ht="13.2">
+    <row r="113" spans="1:19" ht="12.75">
       <c r="A113" s="2"/>
       <c r="B113" s="2"/>
       <c r="C113" s="2"/>
@@ -5953,7 +5956,7 @@
       <c r="R113" s="2"/>
       <c r="S113" s="2"/>
     </row>
-    <row r="114" spans="1:19" ht="13.2">
+    <row r="114" spans="1:19" ht="12.75">
       <c r="A114" s="2"/>
       <c r="B114" s="2"/>
       <c r="C114" s="2"/>
@@ -5974,7 +5977,7 @@
       <c r="R114" s="2"/>
       <c r="S114" s="2"/>
     </row>
-    <row r="115" spans="1:19" ht="13.2">
+    <row r="115" spans="1:19" ht="12.75">
       <c r="A115" s="2"/>
       <c r="B115" s="2"/>
       <c r="C115" s="2"/>
@@ -5995,7 +5998,7 @@
       <c r="R115" s="2"/>
       <c r="S115" s="2"/>
     </row>
-    <row r="116" spans="1:19" ht="13.2">
+    <row r="116" spans="1:19" ht="12.75">
       <c r="A116" s="2"/>
       <c r="B116" s="2"/>
       <c r="C116" s="2"/>
@@ -6016,7 +6019,7 @@
       <c r="R116" s="2"/>
       <c r="S116" s="2"/>
     </row>
-    <row r="117" spans="1:19" ht="13.2">
+    <row r="117" spans="1:19" ht="12.75">
       <c r="A117" s="2"/>
       <c r="B117" s="2"/>
       <c r="C117" s="2"/>
@@ -6037,7 +6040,7 @@
       <c r="R117" s="2"/>
       <c r="S117" s="2"/>
     </row>
-    <row r="118" spans="1:19" ht="13.2">
+    <row r="118" spans="1:19" ht="12.75">
       <c r="A118" s="2"/>
       <c r="B118" s="2"/>
       <c r="C118" s="2"/>
@@ -6058,7 +6061,7 @@
       <c r="R118" s="2"/>
       <c r="S118" s="2"/>
     </row>
-    <row r="119" spans="1:19" ht="13.2">
+    <row r="119" spans="1:19" ht="12.75">
       <c r="A119" s="2"/>
       <c r="B119" s="2"/>
       <c r="C119" s="2"/>
@@ -6079,7 +6082,7 @@
       <c r="R119" s="2"/>
       <c r="S119" s="2"/>
     </row>
-    <row r="120" spans="1:19" ht="13.2">
+    <row r="120" spans="1:19" ht="12.75">
       <c r="A120" s="2"/>
       <c r="B120" s="2"/>
       <c r="C120" s="2"/>
@@ -6100,7 +6103,7 @@
       <c r="R120" s="2"/>
       <c r="S120" s="2"/>
     </row>
-    <row r="121" spans="1:19" ht="13.2">
+    <row r="121" spans="1:19" ht="12.75">
       <c r="A121" s="2"/>
       <c r="B121" s="2"/>
       <c r="C121" s="2"/>
@@ -6121,7 +6124,7 @@
       <c r="R121" s="2"/>
       <c r="S121" s="2"/>
     </row>
-    <row r="122" spans="1:19" ht="13.2">
+    <row r="122" spans="1:19" ht="12.75">
       <c r="A122" s="2"/>
       <c r="B122" s="2"/>
       <c r="C122" s="2"/>
@@ -6142,7 +6145,7 @@
       <c r="R122" s="2"/>
       <c r="S122" s="2"/>
     </row>
-    <row r="123" spans="1:19" ht="13.2">
+    <row r="123" spans="1:19" ht="12.75">
       <c r="A123" s="2"/>
       <c r="B123" s="2"/>
       <c r="C123" s="2"/>
@@ -6163,7 +6166,7 @@
       <c r="R123" s="2"/>
       <c r="S123" s="2"/>
     </row>
-    <row r="124" spans="1:19" ht="13.2">
+    <row r="124" spans="1:19" ht="12.75">
       <c r="A124" s="2"/>
       <c r="B124" s="2"/>
       <c r="C124" s="2"/>
@@ -6184,7 +6187,7 @@
       <c r="R124" s="2"/>
       <c r="S124" s="2"/>
     </row>
-    <row r="125" spans="1:19" ht="13.2">
+    <row r="125" spans="1:19" ht="12.75">
       <c r="A125" s="2"/>
       <c r="B125" s="2"/>
       <c r="C125" s="2"/>
@@ -6205,7 +6208,7 @@
       <c r="R125" s="2"/>
       <c r="S125" s="2"/>
     </row>
-    <row r="126" spans="1:19" ht="13.2">
+    <row r="126" spans="1:19" ht="12.75">
       <c r="A126" s="2"/>
       <c r="B126" s="2"/>
       <c r="C126" s="2"/>
@@ -6226,7 +6229,7 @@
       <c r="R126" s="2"/>
       <c r="S126" s="2"/>
     </row>
-    <row r="127" spans="1:19" ht="13.2">
+    <row r="127" spans="1:19" ht="12.75">
       <c r="A127" s="2"/>
       <c r="B127" s="2"/>
       <c r="C127" s="2"/>
@@ -6247,7 +6250,7 @@
       <c r="R127" s="2"/>
       <c r="S127" s="2"/>
     </row>
-    <row r="128" spans="1:19" ht="13.2">
+    <row r="128" spans="1:19" ht="12.75">
       <c r="A128" s="2"/>
       <c r="B128" s="2"/>
       <c r="C128" s="2"/>
@@ -6268,7 +6271,7 @@
       <c r="R128" s="2"/>
       <c r="S128" s="2"/>
     </row>
-    <row r="129" spans="1:19" ht="13.2">
+    <row r="129" spans="1:19" ht="12.75">
       <c r="A129" s="2"/>
       <c r="B129" s="2"/>
       <c r="C129" s="2"/>
@@ -6289,7 +6292,7 @@
       <c r="R129" s="2"/>
       <c r="S129" s="2"/>
     </row>
-    <row r="130" spans="1:19" ht="13.2">
+    <row r="130" spans="1:19" ht="12.75">
       <c r="A130" s="2"/>
       <c r="B130" s="2"/>
       <c r="C130" s="2"/>
@@ -6310,7 +6313,7 @@
       <c r="R130" s="2"/>
       <c r="S130" s="2"/>
     </row>
-    <row r="131" spans="1:19" ht="13.2">
+    <row r="131" spans="1:19" ht="12.75">
       <c r="A131" s="2"/>
       <c r="B131" s="2"/>
       <c r="C131" s="2"/>
@@ -6331,7 +6334,7 @@
       <c r="R131" s="2"/>
       <c r="S131" s="2"/>
     </row>
-    <row r="132" spans="1:19" ht="13.2">
+    <row r="132" spans="1:19" ht="12.75">
       <c r="A132" s="2"/>
       <c r="B132" s="2"/>
       <c r="C132" s="2"/>
@@ -6352,7 +6355,7 @@
       <c r="R132" s="2"/>
       <c r="S132" s="2"/>
     </row>
-    <row r="133" spans="1:19" ht="13.2">
+    <row r="133" spans="1:19" ht="12.75">
       <c r="A133" s="2"/>
       <c r="B133" s="2"/>
       <c r="C133" s="2"/>
@@ -6373,7 +6376,7 @@
       <c r="R133" s="2"/>
       <c r="S133" s="2"/>
     </row>
-    <row r="134" spans="1:19" ht="13.2">
+    <row r="134" spans="1:19" ht="12.75">
       <c r="A134" s="2"/>
       <c r="B134" s="2"/>
       <c r="C134" s="2"/>
@@ -6394,7 +6397,7 @@
       <c r="R134" s="2"/>
       <c r="S134" s="2"/>
     </row>
-    <row r="135" spans="1:19" ht="13.2">
+    <row r="135" spans="1:19" ht="12.75">
       <c r="A135" s="2"/>
       <c r="B135" s="2"/>
       <c r="C135" s="2"/>
@@ -6415,7 +6418,7 @@
       <c r="R135" s="2"/>
       <c r="S135" s="2"/>
     </row>
-    <row r="136" spans="1:19" ht="13.2">
+    <row r="136" spans="1:19" ht="12.75">
       <c r="A136" s="2"/>
       <c r="B136" s="2"/>
       <c r="C136" s="2"/>
@@ -6436,7 +6439,7 @@
       <c r="R136" s="2"/>
       <c r="S136" s="2"/>
     </row>
-    <row r="137" spans="1:19" ht="13.2">
+    <row r="137" spans="1:19" ht="12.75">
       <c r="A137" s="2"/>
       <c r="B137" s="2"/>
       <c r="C137" s="2"/>
@@ -6457,7 +6460,7 @@
       <c r="R137" s="2"/>
       <c r="S137" s="2"/>
     </row>
-    <row r="138" spans="1:19" ht="13.2">
+    <row r="138" spans="1:19" ht="12.75">
       <c r="A138" s="2"/>
       <c r="B138" s="2"/>
       <c r="C138" s="2"/>
@@ -6478,7 +6481,7 @@
       <c r="R138" s="2"/>
       <c r="S138" s="2"/>
     </row>
-    <row r="139" spans="1:19" ht="13.2">
+    <row r="139" spans="1:19" ht="12.75">
       <c r="A139" s="2"/>
       <c r="B139" s="2"/>
       <c r="C139" s="2"/>
@@ -6499,7 +6502,7 @@
       <c r="R139" s="2"/>
       <c r="S139" s="2"/>
     </row>
-    <row r="140" spans="1:19" ht="13.2">
+    <row r="140" spans="1:19" ht="12.75">
       <c r="A140" s="2"/>
       <c r="B140" s="2"/>
       <c r="C140" s="2"/>
@@ -6520,7 +6523,7 @@
       <c r="R140" s="2"/>
       <c r="S140" s="2"/>
     </row>
-    <row r="141" spans="1:19" ht="13.2">
+    <row r="141" spans="1:19" ht="12.75">
       <c r="A141" s="2"/>
       <c r="B141" s="2"/>
       <c r="C141" s="2"/>
@@ -6541,7 +6544,7 @@
       <c r="R141" s="2"/>
       <c r="S141" s="2"/>
     </row>
-    <row r="142" spans="1:19" ht="13.2">
+    <row r="142" spans="1:19" ht="12.75">
       <c r="A142" s="2"/>
       <c r="B142" s="2"/>
       <c r="C142" s="2"/>
@@ -6562,7 +6565,7 @@
       <c r="R142" s="2"/>
       <c r="S142" s="2"/>
     </row>
-    <row r="143" spans="1:19" ht="13.2">
+    <row r="143" spans="1:19" ht="12.75">
       <c r="A143" s="2"/>
       <c r="B143" s="2"/>
       <c r="C143" s="2"/>
@@ -6583,7 +6586,7 @@
       <c r="R143" s="2"/>
       <c r="S143" s="2"/>
     </row>
-    <row r="144" spans="1:19" ht="13.2">
+    <row r="144" spans="1:19" ht="12.75">
       <c r="A144" s="2"/>
       <c r="B144" s="2"/>
       <c r="C144" s="2"/>
@@ -6604,7 +6607,7 @@
       <c r="R144" s="2"/>
       <c r="S144" s="2"/>
     </row>
-    <row r="145" spans="1:19" ht="13.2">
+    <row r="145" spans="1:19" ht="12.75">
       <c r="A145" s="2"/>
       <c r="B145" s="2"/>
       <c r="C145" s="2"/>
@@ -6625,7 +6628,7 @@
       <c r="R145" s="2"/>
       <c r="S145" s="2"/>
     </row>
-    <row r="146" spans="1:19" ht="13.2">
+    <row r="146" spans="1:19" ht="12.75">
       <c r="A146" s="2"/>
       <c r="B146" s="2"/>
       <c r="C146" s="2"/>
@@ -6646,7 +6649,7 @@
       <c r="R146" s="2"/>
       <c r="S146" s="2"/>
     </row>
-    <row r="147" spans="1:19" ht="13.2">
+    <row r="147" spans="1:19" ht="12.75">
       <c r="A147" s="2"/>
       <c r="B147" s="2"/>
       <c r="C147" s="2"/>
@@ -6667,7 +6670,7 @@
       <c r="R147" s="2"/>
       <c r="S147" s="2"/>
     </row>
-    <row r="148" spans="1:19" ht="13.2">
+    <row r="148" spans="1:19" ht="12.75">
       <c r="A148" s="2"/>
       <c r="B148" s="2"/>
       <c r="C148" s="2"/>
@@ -6688,7 +6691,7 @@
       <c r="R148" s="2"/>
       <c r="S148" s="2"/>
     </row>
-    <row r="149" spans="1:19" ht="13.2">
+    <row r="149" spans="1:19" ht="12.75">
       <c r="A149" s="2"/>
       <c r="B149" s="2"/>
       <c r="C149" s="2"/>
@@ -6709,7 +6712,7 @@
       <c r="R149" s="2"/>
       <c r="S149" s="2"/>
     </row>
-    <row r="150" spans="1:19" ht="13.2">
+    <row r="150" spans="1:19" ht="12.75">
       <c r="A150" s="2"/>
       <c r="B150" s="2"/>
       <c r="C150" s="2"/>
@@ -6730,7 +6733,7 @@
       <c r="R150" s="2"/>
       <c r="S150" s="2"/>
     </row>
-    <row r="151" spans="1:19" ht="13.2">
+    <row r="151" spans="1:19" ht="12.75">
       <c r="A151" s="2"/>
       <c r="B151" s="2"/>
       <c r="C151" s="2"/>
@@ -6751,7 +6754,7 @@
       <c r="R151" s="2"/>
       <c r="S151" s="2"/>
     </row>
-    <row r="152" spans="1:19" ht="13.2">
+    <row r="152" spans="1:19" ht="12.75">
       <c r="A152" s="2"/>
       <c r="B152" s="2"/>
       <c r="C152" s="2"/>
@@ -6772,7 +6775,7 @@
       <c r="R152" s="2"/>
       <c r="S152" s="2"/>
     </row>
-    <row r="153" spans="1:19" ht="13.2">
+    <row r="153" spans="1:19" ht="12.75">
       <c r="A153" s="2"/>
       <c r="B153" s="2"/>
       <c r="C153" s="2"/>
@@ -6793,7 +6796,7 @@
       <c r="R153" s="2"/>
       <c r="S153" s="2"/>
     </row>
-    <row r="154" spans="1:19" ht="13.2">
+    <row r="154" spans="1:19" ht="12.75">
       <c r="A154" s="2"/>
       <c r="B154" s="2"/>
       <c r="C154" s="2"/>
@@ -6814,7 +6817,7 @@
       <c r="R154" s="2"/>
       <c r="S154" s="2"/>
     </row>
-    <row r="155" spans="1:19" ht="13.2">
+    <row r="155" spans="1:19" ht="12.75">
       <c r="A155" s="2"/>
       <c r="B155" s="2"/>
       <c r="C155" s="2"/>
@@ -6835,7 +6838,7 @@
       <c r="R155" s="2"/>
       <c r="S155" s="2"/>
     </row>
-    <row r="156" spans="1:19" ht="13.2">
+    <row r="156" spans="1:19" ht="12.75">
       <c r="A156" s="2"/>
       <c r="B156" s="2"/>
       <c r="C156" s="2"/>
@@ -6856,7 +6859,7 @@
       <c r="R156" s="2"/>
       <c r="S156" s="2"/>
     </row>
-    <row r="157" spans="1:19" ht="13.2">
+    <row r="157" spans="1:19" ht="12.75">
       <c r="A157" s="2"/>
       <c r="B157" s="2"/>
       <c r="C157" s="2"/>
@@ -6877,7 +6880,7 @@
       <c r="R157" s="2"/>
       <c r="S157" s="2"/>
     </row>
-    <row r="158" spans="1:19" ht="13.2">
+    <row r="158" spans="1:19" ht="12.75">
       <c r="A158" s="2"/>
       <c r="B158" s="2"/>
       <c r="C158" s="2"/>
@@ -6898,7 +6901,7 @@
       <c r="R158" s="2"/>
       <c r="S158" s="2"/>
     </row>
-    <row r="159" spans="1:19" ht="13.2">
+    <row r="159" spans="1:19" ht="12.75">
       <c r="A159" s="2"/>
       <c r="B159" s="2"/>
       <c r="C159" s="2"/>
@@ -6919,7 +6922,7 @@
       <c r="R159" s="2"/>
       <c r="S159" s="2"/>
     </row>
-    <row r="160" spans="1:19" ht="13.2">
+    <row r="160" spans="1:19" ht="12.75">
       <c r="A160" s="2"/>
       <c r="B160" s="2"/>
       <c r="C160" s="2"/>
@@ -6940,7 +6943,7 @@
       <c r="R160" s="2"/>
       <c r="S160" s="2"/>
     </row>
-    <row r="161" spans="1:19" ht="13.2">
+    <row r="161" spans="1:19" ht="12.75">
       <c r="A161" s="2"/>
       <c r="B161" s="2"/>
       <c r="C161" s="2"/>
@@ -6961,7 +6964,7 @@
       <c r="R161" s="2"/>
       <c r="S161" s="2"/>
     </row>
-    <row r="162" spans="1:19" ht="13.2">
+    <row r="162" spans="1:19" ht="12.75">
       <c r="A162" s="2"/>
       <c r="B162" s="2"/>
       <c r="C162" s="2"/>
@@ -6982,7 +6985,7 @@
       <c r="R162" s="2"/>
       <c r="S162" s="2"/>
     </row>
-    <row r="163" spans="1:19" ht="13.2">
+    <row r="163" spans="1:19" ht="12.75">
       <c r="A163" s="2"/>
       <c r="B163" s="2"/>
       <c r="C163" s="2"/>
@@ -7003,7 +7006,7 @@
       <c r="R163" s="2"/>
       <c r="S163" s="2"/>
     </row>
-    <row r="164" spans="1:19" ht="13.2">
+    <row r="164" spans="1:19" ht="12.75">
       <c r="A164" s="2"/>
       <c r="B164" s="2"/>
       <c r="C164" s="2"/>
@@ -7024,7 +7027,7 @@
       <c r="R164" s="2"/>
       <c r="S164" s="2"/>
     </row>
-    <row r="165" spans="1:19" ht="13.2">
+    <row r="165" spans="1:19" ht="12.75">
       <c r="A165" s="2"/>
       <c r="B165" s="2"/>
       <c r="C165" s="2"/>
@@ -7045,7 +7048,7 @@
       <c r="R165" s="2"/>
       <c r="S165" s="2"/>
     </row>
-    <row r="166" spans="1:19" ht="13.2">
+    <row r="166" spans="1:19" ht="12.75">
       <c r="A166" s="2"/>
       <c r="B166" s="2"/>
       <c r="C166" s="2"/>
@@ -7066,7 +7069,7 @@
       <c r="R166" s="2"/>
       <c r="S166" s="2"/>
     </row>
-    <row r="167" spans="1:19" ht="13.2">
+    <row r="167" spans="1:19" ht="12.75">
       <c r="A167" s="2"/>
       <c r="B167" s="2"/>
       <c r="C167" s="2"/>
@@ -7087,7 +7090,7 @@
       <c r="R167" s="2"/>
       <c r="S167" s="2"/>
     </row>
-    <row r="168" spans="1:19" ht="13.2">
+    <row r="168" spans="1:19" ht="12.75">
       <c r="A168" s="2"/>
       <c r="B168" s="2"/>
       <c r="C168" s="2"/>
@@ -7108,7 +7111,7 @@
       <c r="R168" s="2"/>
       <c r="S168" s="2"/>
     </row>
-    <row r="169" spans="1:19" ht="13.2">
+    <row r="169" spans="1:19" ht="12.75">
       <c r="A169" s="2"/>
       <c r="B169" s="2"/>
       <c r="C169" s="2"/>
@@ -7129,7 +7132,7 @@
       <c r="R169" s="2"/>
       <c r="S169" s="2"/>
     </row>
-    <row r="170" spans="1:19" ht="13.2">
+    <row r="170" spans="1:19" ht="12.75">
       <c r="A170" s="2"/>
       <c r="B170" s="2"/>
       <c r="C170" s="2"/>
@@ -7150,7 +7153,7 @@
       <c r="R170" s="2"/>
       <c r="S170" s="2"/>
     </row>
-    <row r="171" spans="1:19" ht="13.2">
+    <row r="171" spans="1:19" ht="12.75">
       <c r="A171" s="2"/>
       <c r="B171" s="2"/>
       <c r="C171" s="2"/>
@@ -7171,7 +7174,7 @@
       <c r="R171" s="2"/>
       <c r="S171" s="2"/>
     </row>
-    <row r="172" spans="1:19" ht="13.2">
+    <row r="172" spans="1:19" ht="12.75">
       <c r="A172" s="2"/>
       <c r="B172" s="2"/>
       <c r="C172" s="2"/>
@@ -7192,7 +7195,7 @@
       <c r="R172" s="2"/>
       <c r="S172" s="2"/>
     </row>
-    <row r="173" spans="1:19" ht="13.2">
+    <row r="173" spans="1:19" ht="12.75">
       <c r="A173" s="2"/>
       <c r="B173" s="2"/>
       <c r="C173" s="2"/>
@@ -7213,7 +7216,7 @@
       <c r="R173" s="2"/>
       <c r="S173" s="2"/>
     </row>
-    <row r="174" spans="1:19" ht="13.2">
+    <row r="174" spans="1:19" ht="12.75">
       <c r="A174" s="2"/>
       <c r="B174" s="2"/>
       <c r="C174" s="2"/>
@@ -7234,7 +7237,7 @@
       <c r="R174" s="2"/>
       <c r="S174" s="2"/>
     </row>
-    <row r="175" spans="1:19" ht="13.2">
+    <row r="175" spans="1:19" ht="12.75">
       <c r="A175" s="2"/>
       <c r="B175" s="2"/>
       <c r="C175" s="2"/>
@@ -7255,7 +7258,7 @@
       <c r="R175" s="2"/>
       <c r="S175" s="2"/>
     </row>
-    <row r="176" spans="1:19" ht="13.2">
+    <row r="176" spans="1:19" ht="12.75">
       <c r="A176" s="2"/>
       <c r="B176" s="2"/>
       <c r="C176" s="2"/>
@@ -7276,7 +7279,7 @@
       <c r="R176" s="2"/>
       <c r="S176" s="2"/>
     </row>
-    <row r="177" spans="1:19" ht="13.2">
+    <row r="177" spans="1:19" ht="12.75">
       <c r="A177" s="2"/>
       <c r="B177" s="2"/>
       <c r="C177" s="2"/>
@@ -7297,7 +7300,7 @@
       <c r="R177" s="2"/>
       <c r="S177" s="2"/>
     </row>
-    <row r="178" spans="1:19" ht="13.2">
+    <row r="178" spans="1:19" ht="12.75">
       <c r="A178" s="2"/>
       <c r="B178" s="2"/>
       <c r="C178" s="2"/>
@@ -7318,7 +7321,7 @@
       <c r="R178" s="2"/>
       <c r="S178" s="2"/>
     </row>
-    <row r="179" spans="1:19" ht="13.2">
+    <row r="179" spans="1:19" ht="12.75">
       <c r="A179" s="2"/>
       <c r="B179" s="2"/>
       <c r="C179" s="2"/>
@@ -7339,7 +7342,7 @@
       <c r="R179" s="2"/>
       <c r="S179" s="2"/>
     </row>
-    <row r="180" spans="1:19" ht="13.2">
+    <row r="180" spans="1:19" ht="12.75">
       <c r="A180" s="2"/>
       <c r="B180" s="2"/>
       <c r="C180" s="2"/>
@@ -7360,7 +7363,7 @@
       <c r="R180" s="2"/>
       <c r="S180" s="2"/>
     </row>
-    <row r="181" spans="1:19" ht="13.2">
+    <row r="181" spans="1:19" ht="12.75">
       <c r="A181" s="2"/>
       <c r="B181" s="2"/>
       <c r="C181" s="2"/>
@@ -7381,7 +7384,7 @@
       <c r="R181" s="2"/>
       <c r="S181" s="2"/>
     </row>
-    <row r="182" spans="1:19" ht="13.2">
+    <row r="182" spans="1:19" ht="12.75">
       <c r="A182" s="2"/>
       <c r="B182" s="2"/>
       <c r="C182" s="2"/>
@@ -7402,7 +7405,7 @@
       <c r="R182" s="2"/>
       <c r="S182" s="2"/>
     </row>
-    <row r="183" spans="1:19" ht="13.2">
+    <row r="183" spans="1:19" ht="12.75">
       <c r="A183" s="2"/>
       <c r="B183" s="2"/>
       <c r="C183" s="2"/>
@@ -7423,7 +7426,7 @@
       <c r="R183" s="2"/>
       <c r="S183" s="2"/>
     </row>
-    <row r="184" spans="1:19" ht="13.2">
+    <row r="184" spans="1:19" ht="12.75">
       <c r="A184" s="2"/>
       <c r="B184" s="2"/>
       <c r="C184" s="2"/>
@@ -7444,7 +7447,7 @@
       <c r="R184" s="2"/>
       <c r="S184" s="2"/>
     </row>
-    <row r="185" spans="1:19" ht="13.2">
+    <row r="185" spans="1:19" ht="12.75">
       <c r="A185" s="2"/>
       <c r="B185" s="2"/>
       <c r="C185" s="2"/>
@@ -7465,7 +7468,7 @@
       <c r="R185" s="2"/>
       <c r="S185" s="2"/>
     </row>
-    <row r="186" spans="1:19" ht="13.2">
+    <row r="186" spans="1:19" ht="12.75">
       <c r="A186" s="2"/>
       <c r="B186" s="2"/>
       <c r="C186" s="2"/>
@@ -7486,7 +7489,7 @@
       <c r="R186" s="2"/>
       <c r="S186" s="2"/>
     </row>
-    <row r="187" spans="1:19" ht="13.2">
+    <row r="187" spans="1:19" ht="12.75">
       <c r="A187" s="2"/>
       <c r="B187" s="2"/>
       <c r="C187" s="2"/>
@@ -7507,7 +7510,7 @@
       <c r="R187" s="2"/>
       <c r="S187" s="2"/>
     </row>
-    <row r="188" spans="1:19" ht="13.2">
+    <row r="188" spans="1:19" ht="12.75">
       <c r="A188" s="2"/>
       <c r="B188" s="2"/>
       <c r="C188" s="2"/>
@@ -7528,7 +7531,7 @@
       <c r="R188" s="2"/>
       <c r="S188" s="2"/>
     </row>
-    <row r="189" spans="1:19" ht="13.2">
+    <row r="189" spans="1:19" ht="12.75">
       <c r="A189" s="2"/>
       <c r="B189" s="2"/>
       <c r="C189" s="2"/>
@@ -7549,7 +7552,7 @@
       <c r="R189" s="2"/>
       <c r="S189" s="2"/>
     </row>
-    <row r="190" spans="1:19" ht="13.2">
+    <row r="190" spans="1:19" ht="12.75">
       <c r="A190" s="2"/>
       <c r="B190" s="2"/>
       <c r="C190" s="2"/>
@@ -7570,7 +7573,7 @@
       <c r="R190" s="2"/>
       <c r="S190" s="2"/>
     </row>
-    <row r="191" spans="1:19" ht="13.2">
+    <row r="191" spans="1:19" ht="12.75">
       <c r="A191" s="2"/>
       <c r="B191" s="2"/>
       <c r="C191" s="2"/>
@@ -7591,7 +7594,7 @@
       <c r="R191" s="2"/>
       <c r="S191" s="2"/>
     </row>
-    <row r="192" spans="1:19" ht="13.2">
+    <row r="192" spans="1:19" ht="12.75">
       <c r="A192" s="2"/>
       <c r="B192" s="2"/>
       <c r="C192" s="2"/>
@@ -7612,7 +7615,7 @@
       <c r="R192" s="2"/>
       <c r="S192" s="2"/>
     </row>
-    <row r="193" spans="1:19" ht="13.2">
+    <row r="193" spans="1:19" ht="12.75">
       <c r="A193" s="2"/>
       <c r="B193" s="2"/>
       <c r="C193" s="2"/>
@@ -7633,7 +7636,7 @@
       <c r="R193" s="2"/>
       <c r="S193" s="2"/>
     </row>
-    <row r="194" spans="1:19" ht="13.2">
+    <row r="194" spans="1:19" ht="12.75">
       <c r="A194" s="2"/>
       <c r="B194" s="2"/>
       <c r="C194" s="2"/>
@@ -7654,7 +7657,7 @@
       <c r="R194" s="2"/>
       <c r="S194" s="2"/>
     </row>
-    <row r="195" spans="1:19" ht="13.2">
+    <row r="195" spans="1:19" ht="12.75">
       <c r="A195" s="2"/>
       <c r="B195" s="2"/>
       <c r="C195" s="2"/>
@@ -7675,7 +7678,7 @@
       <c r="R195" s="2"/>
       <c r="S195" s="2"/>
     </row>
-    <row r="196" spans="1:19" ht="13.2">
+    <row r="196" spans="1:19" ht="12.75">
       <c r="A196" s="2"/>
       <c r="B196" s="2"/>
       <c r="C196" s="2"/>
@@ -7696,7 +7699,7 @@
       <c r="R196" s="2"/>
       <c r="S196" s="2"/>
     </row>
-    <row r="197" spans="1:19" ht="13.2">
+    <row r="197" spans="1:19" ht="12.75">
       <c r="A197" s="2"/>
       <c r="B197" s="2"/>
       <c r="C197" s="2"/>
@@ -7717,7 +7720,7 @@
       <c r="R197" s="2"/>
       <c r="S197" s="2"/>
     </row>
-    <row r="198" spans="1:19" ht="13.2">
+    <row r="198" spans="1:19" ht="12.75">
       <c r="A198" s="2"/>
       <c r="B198" s="2"/>
       <c r="C198" s="2"/>
@@ -7738,7 +7741,7 @@
       <c r="R198" s="2"/>
       <c r="S198" s="2"/>
     </row>
-    <row r="199" spans="1:19" ht="13.2">
+    <row r="199" spans="1:19" ht="12.75">
       <c r="A199" s="2"/>
       <c r="B199" s="2"/>
       <c r="C199" s="2"/>
@@ -7759,7 +7762,7 @@
       <c r="R199" s="2"/>
       <c r="S199" s="2"/>
     </row>
-    <row r="200" spans="1:19" ht="13.2">
+    <row r="200" spans="1:19" ht="12.75">
       <c r="A200" s="2"/>
       <c r="B200" s="2"/>
       <c r="C200" s="2"/>
@@ -7780,7 +7783,7 @@
       <c r="R200" s="2"/>
       <c r="S200" s="2"/>
     </row>
-    <row r="201" spans="1:19" ht="13.2">
+    <row r="201" spans="1:19" ht="12.75">
       <c r="A201" s="2"/>
       <c r="B201" s="2"/>
       <c r="C201" s="2"/>
@@ -7801,7 +7804,7 @@
       <c r="R201" s="2"/>
       <c r="S201" s="2"/>
     </row>
-    <row r="202" spans="1:19" ht="13.2">
+    <row r="202" spans="1:19" ht="12.75">
       <c r="A202" s="2"/>
       <c r="B202" s="2"/>
       <c r="C202" s="2"/>
@@ -7822,7 +7825,7 @@
       <c r="R202" s="2"/>
       <c r="S202" s="2"/>
     </row>
-    <row r="203" spans="1:19" ht="13.2">
+    <row r="203" spans="1:19" ht="12.75">
       <c r="A203" s="2"/>
       <c r="B203" s="2"/>
       <c r="C203" s="2"/>
@@ -7843,7 +7846,7 @@
       <c r="R203" s="2"/>
       <c r="S203" s="2"/>
     </row>
-    <row r="204" spans="1:19" ht="13.2">
+    <row r="204" spans="1:19" ht="12.75">
       <c r="A204" s="2"/>
       <c r="B204" s="2"/>
       <c r="C204" s="2"/>
@@ -7864,7 +7867,7 @@
       <c r="R204" s="2"/>
       <c r="S204" s="2"/>
     </row>
-    <row r="205" spans="1:19" ht="13.2">
+    <row r="205" spans="1:19" ht="12.75">
       <c r="A205" s="2"/>
       <c r="B205" s="2"/>
       <c r="C205" s="2"/>
@@ -7885,7 +7888,7 @@
       <c r="R205" s="2"/>
       <c r="S205" s="2"/>
     </row>
-    <row r="206" spans="1:19" ht="13.2">
+    <row r="206" spans="1:19" ht="12.75">
       <c r="A206" s="2"/>
       <c r="B206" s="2"/>
       <c r="C206" s="2"/>
@@ -7906,7 +7909,7 @@
       <c r="R206" s="2"/>
       <c r="S206" s="2"/>
     </row>
-    <row r="207" spans="1:19" ht="13.2">
+    <row r="207" spans="1:19" ht="12.75">
       <c r="A207" s="2"/>
       <c r="B207" s="2"/>
       <c r="C207" s="2"/>
@@ -7927,7 +7930,7 @@
       <c r="R207" s="2"/>
       <c r="S207" s="2"/>
     </row>
-    <row r="208" spans="1:19" ht="13.2">
+    <row r="208" spans="1:19" ht="12.75">
       <c r="A208" s="2"/>
       <c r="B208" s="2"/>
       <c r="C208" s="2"/>
@@ -7948,7 +7951,7 @@
       <c r="R208" s="2"/>
       <c r="S208" s="2"/>
     </row>
-    <row r="209" spans="1:19" ht="13.2">
+    <row r="209" spans="1:19" ht="12.75">
       <c r="A209" s="2"/>
       <c r="B209" s="2"/>
       <c r="C209" s="2"/>
@@ -7969,7 +7972,7 @@
       <c r="R209" s="2"/>
       <c r="S209" s="2"/>
     </row>
-    <row r="210" spans="1:19" ht="13.2">
+    <row r="210" spans="1:19" ht="12.75">
       <c r="A210" s="2"/>
       <c r="B210" s="2"/>
       <c r="C210" s="2"/>
@@ -7990,7 +7993,7 @@
       <c r="R210" s="2"/>
       <c r="S210" s="2"/>
     </row>
-    <row r="211" spans="1:19" ht="13.2">
+    <row r="211" spans="1:19" ht="12.75">
       <c r="A211" s="2"/>
       <c r="B211" s="2"/>
       <c r="C211" s="2"/>
@@ -8011,7 +8014,7 @@
       <c r="R211" s="2"/>
       <c r="S211" s="2"/>
     </row>
-    <row r="212" spans="1:19" ht="13.2">
+    <row r="212" spans="1:19" ht="12.75">
       <c r="A212" s="2"/>
       <c r="B212" s="2"/>
       <c r="C212" s="2"/>
@@ -8032,7 +8035,7 @@
       <c r="R212" s="2"/>
       <c r="S212" s="2"/>
     </row>
-    <row r="213" spans="1:19" ht="13.2">
+    <row r="213" spans="1:19" ht="12.75">
       <c r="A213" s="2"/>
       <c r="B213" s="2"/>
       <c r="C213" s="2"/>
@@ -8053,7 +8056,7 @@
       <c r="R213" s="2"/>
       <c r="S213" s="2"/>
     </row>
-    <row r="214" spans="1:19" ht="13.2">
+    <row r="214" spans="1:19" ht="12.75">
       <c r="A214" s="2"/>
       <c r="B214" s="2"/>
       <c r="C214" s="2"/>
@@ -8074,7 +8077,7 @@
       <c r="R214" s="2"/>
       <c r="S214" s="2"/>
     </row>
-    <row r="215" spans="1:19" ht="13.2">
+    <row r="215" spans="1:19" ht="12.75">
       <c r="A215" s="2"/>
       <c r="B215" s="2"/>
       <c r="C215" s="2"/>
@@ -8095,7 +8098,7 @@
       <c r="R215" s="2"/>
       <c r="S215" s="2"/>
     </row>
-    <row r="216" spans="1:19" ht="13.2">
+    <row r="216" spans="1:19" ht="12.75">
       <c r="A216" s="2"/>
       <c r="B216" s="2"/>
       <c r="C216" s="2"/>
@@ -8116,7 +8119,7 @@
       <c r="R216" s="2"/>
       <c r="S216" s="2"/>
     </row>
-    <row r="217" spans="1:19" ht="13.2">
+    <row r="217" spans="1:19" ht="12.75">
       <c r="A217" s="2"/>
       <c r="B217" s="2"/>
       <c r="C217" s="2"/>
@@ -8137,7 +8140,7 @@
       <c r="R217" s="2"/>
       <c r="S217" s="2"/>
     </row>
-    <row r="218" spans="1:19" ht="13.2">
+    <row r="218" spans="1:19" ht="12.75">
       <c r="A218" s="2"/>
       <c r="B218" s="2"/>
       <c r="C218" s="2"/>
@@ -8158,7 +8161,7 @@
       <c r="R218" s="2"/>
       <c r="S218" s="2"/>
     </row>
-    <row r="219" spans="1:19" ht="13.2">
+    <row r="219" spans="1:19" ht="12.75">
       <c r="A219" s="2"/>
       <c r="B219" s="2"/>
       <c r="C219" s="2"/>
@@ -8179,7 +8182,7 @@
       <c r="R219" s="2"/>
       <c r="S219" s="2"/>
     </row>
-    <row r="220" spans="1:19" ht="13.2">
+    <row r="220" spans="1:19" ht="12.75">
       <c r="A220" s="2"/>
       <c r="B220" s="2"/>
       <c r="C220" s="2"/>
@@ -8200,7 +8203,7 @@
       <c r="R220" s="2"/>
       <c r="S220" s="2"/>
     </row>
-    <row r="221" spans="1:19" ht="13.2">
+    <row r="221" spans="1:19" ht="12.75">
       <c r="A221" s="2"/>
       <c r="B221" s="2"/>
       <c r="C221" s="2"/>
@@ -8221,7 +8224,7 @@
       <c r="R221" s="2"/>
       <c r="S221" s="2"/>
     </row>
-    <row r="222" spans="1:19" ht="13.2">
+    <row r="222" spans="1:19" ht="12.75">
       <c r="A222" s="2"/>
       <c r="B222" s="2"/>
       <c r="C222" s="2"/>
@@ -8242,7 +8245,7 @@
       <c r="R222" s="2"/>
       <c r="S222" s="2"/>
     </row>
-    <row r="223" spans="1:19" ht="13.2">
+    <row r="223" spans="1:19" ht="12.75">
       <c r="A223" s="2"/>
       <c r="B223" s="2"/>
       <c r="C223" s="2"/>
@@ -8263,7 +8266,7 @@
       <c r="R223" s="2"/>
       <c r="S223" s="2"/>
     </row>
-    <row r="224" spans="1:19" ht="13.2">
+    <row r="224" spans="1:19" ht="12.75">
       <c r="A224" s="2"/>
       <c r="B224" s="2"/>
       <c r="C224" s="2"/>
@@ -8284,7 +8287,7 @@
       <c r="R224" s="2"/>
       <c r="S224" s="2"/>
     </row>
-    <row r="225" spans="1:19" ht="13.2">
+    <row r="225" spans="1:19" ht="12.75">
       <c r="A225" s="2"/>
       <c r="B225" s="2"/>
       <c r="C225" s="2"/>
@@ -8305,7 +8308,7 @@
       <c r="R225" s="2"/>
       <c r="S225" s="2"/>
     </row>
-    <row r="226" spans="1:19" ht="13.2">
+    <row r="226" spans="1:19" ht="12.75">
       <c r="A226" s="2"/>
       <c r="B226" s="2"/>
       <c r="C226" s="2"/>
@@ -8326,7 +8329,7 @@
       <c r="R226" s="2"/>
       <c r="S226" s="2"/>
     </row>
-    <row r="227" spans="1:19" ht="13.2">
+    <row r="227" spans="1:19" ht="12.75">
       <c r="A227" s="2"/>
       <c r="B227" s="2"/>
       <c r="C227" s="2"/>
@@ -8347,7 +8350,7 @@
       <c r="R227" s="2"/>
       <c r="S227" s="2"/>
     </row>
-    <row r="228" spans="1:19" ht="13.2">
+    <row r="228" spans="1:19" ht="12.75">
       <c r="A228" s="2"/>
       <c r="B228" s="2"/>
       <c r="C228" s="2"/>
@@ -8368,7 +8371,7 @@
       <c r="R228" s="2"/>
       <c r="S228" s="2"/>
     </row>
-    <row r="229" spans="1:19" ht="13.2">
+    <row r="229" spans="1:19" ht="12.75">
       <c r="A229" s="2"/>
       <c r="B229" s="2"/>
       <c r="C229" s="2"/>
@@ -8389,7 +8392,7 @@
       <c r="R229" s="2"/>
       <c r="S229" s="2"/>
     </row>
-    <row r="230" spans="1:19" ht="13.2">
+    <row r="230" spans="1:19" ht="12.75">
       <c r="A230" s="2"/>
       <c r="B230" s="2"/>
       <c r="C230" s="2"/>
@@ -8410,7 +8413,7 @@
       <c r="R230" s="2"/>
       <c r="S230" s="2"/>
     </row>
-    <row r="231" spans="1:19" ht="13.2">
+    <row r="231" spans="1:19" ht="12.75">
       <c r="A231" s="2"/>
       <c r="B231" s="2"/>
       <c r="C231" s="2"/>
@@ -8431,7 +8434,7 @@
       <c r="R231" s="2"/>
       <c r="S231" s="2"/>
     </row>
-    <row r="232" spans="1:19" ht="13.2">
+    <row r="232" spans="1:19" ht="12.75">
       <c r="A232" s="2"/>
       <c r="B232" s="2"/>
       <c r="C232" s="2"/>
@@ -8452,7 +8455,7 @@
       <c r="R232" s="2"/>
       <c r="S232" s="2"/>
     </row>
-    <row r="233" spans="1:19" ht="13.2">
+    <row r="233" spans="1:19" ht="12.75">
       <c r="A233" s="2"/>
       <c r="B233" s="2"/>
       <c r="C233" s="2"/>
@@ -8473,7 +8476,7 @@
       <c r="R233" s="2"/>
       <c r="S233" s="2"/>
     </row>
-    <row r="234" spans="1:19" ht="13.2">
+    <row r="234" spans="1:19" ht="12.75">
       <c r="A234" s="2"/>
       <c r="B234" s="2"/>
       <c r="C234" s="2"/>
@@ -8494,7 +8497,7 @@
       <c r="R234" s="2"/>
       <c r="S234" s="2"/>
     </row>
-    <row r="235" spans="1:19" ht="13.2">
+    <row r="235" spans="1:19" ht="12.75">
       <c r="A235" s="2"/>
       <c r="B235" s="2"/>
       <c r="C235" s="2"/>
@@ -8515,7 +8518,7 @@
       <c r="R235" s="2"/>
       <c r="S235" s="2"/>
     </row>
-    <row r="236" spans="1:19" ht="13.2">
+    <row r="236" spans="1:19" ht="12.75">
       <c r="A236" s="2"/>
       <c r="B236" s="2"/>
       <c r="C236" s="2"/>
@@ -8536,7 +8539,7 @@
       <c r="R236" s="2"/>
       <c r="S236" s="2"/>
     </row>
-    <row r="237" spans="1:19" ht="13.2">
+    <row r="237" spans="1:19" ht="12.75">
       <c r="A237" s="2"/>
       <c r="B237" s="2"/>
       <c r="C237" s="2"/>
@@ -8557,7 +8560,7 @@
       <c r="R237" s="2"/>
       <c r="S237" s="2"/>
     </row>
-    <row r="238" spans="1:19" ht="13.2">
+    <row r="238" spans="1:19" ht="12.75">
       <c r="A238" s="2"/>
       <c r="B238" s="2"/>
       <c r="C238" s="2"/>
@@ -8578,7 +8581,7 @@
       <c r="R238" s="2"/>
       <c r="S238" s="2"/>
     </row>
-    <row r="239" spans="1:19" ht="13.2">
+    <row r="239" spans="1:19" ht="12.75">
       <c r="A239" s="2"/>
       <c r="B239" s="2"/>
       <c r="C239" s="2"/>
@@ -8599,7 +8602,7 @@
       <c r="R239" s="2"/>
       <c r="S239" s="2"/>
     </row>
-    <row r="240" spans="1:19" ht="13.2">
+    <row r="240" spans="1:19" ht="12.75">
       <c r="A240" s="2"/>
       <c r="B240" s="2"/>
       <c r="C240" s="2"/>
@@ -8620,7 +8623,7 @@
       <c r="R240" s="2"/>
       <c r="S240" s="2"/>
     </row>
-    <row r="241" spans="1:19" ht="13.2">
+    <row r="241" spans="1:19" ht="12.75">
       <c r="A241" s="2"/>
       <c r="B241" s="2"/>
       <c r="C241" s="2"/>
@@ -8641,7 +8644,7 @@
       <c r="R241" s="2"/>
       <c r="S241" s="2"/>
     </row>
-    <row r="242" spans="1:19" ht="13.2">
+    <row r="242" spans="1:19" ht="12.75">
       <c r="A242" s="2"/>
       <c r="B242" s="2"/>
       <c r="C242" s="2"/>
@@ -8662,7 +8665,7 @@
       <c r="R242" s="2"/>
       <c r="S242" s="2"/>
     </row>
-    <row r="243" spans="1:19" ht="13.2">
+    <row r="243" spans="1:19" ht="12.75">
       <c r="A243" s="2"/>
       <c r="B243" s="2"/>
       <c r="C243" s="2"/>
@@ -8683,7 +8686,7 @@
       <c r="R243" s="2"/>
       <c r="S243" s="2"/>
     </row>
-    <row r="244" spans="1:19" ht="13.2">
+    <row r="244" spans="1:19" ht="12.75">
       <c r="A244" s="2"/>
       <c r="B244" s="2"/>
       <c r="C244" s="2"/>
@@ -8704,7 +8707,7 @@
       <c r="R244" s="2"/>
       <c r="S244" s="2"/>
     </row>
-    <row r="245" spans="1:19" ht="13.2">
+    <row r="245" spans="1:19" ht="12.75">
       <c r="A245" s="2"/>
       <c r="B245" s="2"/>
       <c r="C245" s="2"/>
@@ -8725,7 +8728,7 @@
       <c r="R245" s="2"/>
       <c r="S245" s="2"/>
     </row>
-    <row r="246" spans="1:19" ht="13.2">
+    <row r="246" spans="1:19" ht="12.75">
       <c r="A246" s="2"/>
       <c r="B246" s="2"/>
       <c r="C246" s="2"/>
@@ -8746,7 +8749,7 @@
       <c r="R246" s="2"/>
       <c r="S246" s="2"/>
     </row>
-    <row r="247" spans="1:19" ht="13.2">
+    <row r="247" spans="1:19" ht="12.75">
       <c r="A247" s="2"/>
       <c r="B247" s="2"/>
       <c r="C247" s="2"/>
@@ -8767,7 +8770,7 @@
       <c r="R247" s="2"/>
       <c r="S247" s="2"/>
     </row>
-    <row r="248" spans="1:19" ht="13.2">
+    <row r="248" spans="1:19" ht="12.75">
       <c r="A248" s="2"/>
       <c r="B248" s="2"/>
       <c r="C248" s="2"/>
@@ -8788,7 +8791,7 @@
       <c r="R248" s="2"/>
       <c r="S248" s="2"/>
     </row>
-    <row r="249" spans="1:19" ht="13.2">
+    <row r="249" spans="1:19" ht="12.75">
       <c r="A249" s="2"/>
       <c r="B249" s="2"/>
       <c r="C249" s="2"/>
@@ -8809,7 +8812,7 @@
       <c r="R249" s="2"/>
       <c r="S249" s="2"/>
     </row>
-    <row r="250" spans="1:19" ht="13.2">
+    <row r="250" spans="1:19" ht="12.75">
       <c r="A250" s="2"/>
       <c r="B250" s="2"/>
       <c r="C250" s="2"/>
@@ -8830,7 +8833,7 @@
       <c r="R250" s="2"/>
       <c r="S250" s="2"/>
     </row>
-    <row r="251" spans="1:19" ht="13.2">
+    <row r="251" spans="1:19" ht="12.75">
       <c r="A251" s="2"/>
       <c r="B251" s="2"/>
       <c r="C251" s="2"/>
@@ -8851,7 +8854,7 @@
       <c r="R251" s="2"/>
       <c r="S251" s="2"/>
     </row>
-    <row r="252" spans="1:19" ht="13.2">
+    <row r="252" spans="1:19" ht="12.75">
       <c r="A252" s="2"/>
       <c r="B252" s="2"/>
       <c r="C252" s="2"/>
@@ -8872,7 +8875,7 @@
       <c r="R252" s="2"/>
       <c r="S252" s="2"/>
     </row>
-    <row r="253" spans="1:19" ht="13.2">
+    <row r="253" spans="1:19" ht="12.75">
       <c r="A253" s="2"/>
       <c r="B253" s="2"/>
       <c r="C253" s="2"/>
@@ -8893,7 +8896,7 @@
       <c r="R253" s="2"/>
       <c r="S253" s="2"/>
     </row>
-    <row r="254" spans="1:19" ht="13.2">
+    <row r="254" spans="1:19" ht="12.75">
       <c r="A254" s="2"/>
       <c r="B254" s="2"/>
       <c r="C254" s="2"/>
@@ -8914,7 +8917,7 @@
       <c r="R254" s="2"/>
       <c r="S254" s="2"/>
     </row>
-    <row r="255" spans="1:19" ht="13.2">
+    <row r="255" spans="1:19" ht="12.75">
       <c r="A255" s="2"/>
       <c r="B255" s="2"/>
       <c r="C255" s="2"/>
@@ -8935,7 +8938,7 @@
       <c r="R255" s="2"/>
       <c r="S255" s="2"/>
     </row>
-    <row r="256" spans="1:19" ht="13.2">
+    <row r="256" spans="1:19" ht="12.75">
       <c r="A256" s="2"/>
       <c r="B256" s="2"/>
       <c r="C256" s="2"/>
@@ -8956,7 +8959,7 @@
       <c r="R256" s="2"/>
       <c r="S256" s="2"/>
     </row>
-    <row r="257" spans="1:19" ht="13.2">
+    <row r="257" spans="1:19" ht="12.75">
       <c r="A257" s="2"/>
       <c r="B257" s="2"/>
       <c r="C257" s="2"/>
@@ -8977,7 +8980,7 @@
       <c r="R257" s="2"/>
       <c r="S257" s="2"/>
     </row>
-    <row r="258" spans="1:19" ht="13.2">
+    <row r="258" spans="1:19" ht="12.75">
       <c r="A258" s="2"/>
       <c r="B258" s="2"/>
       <c r="C258" s="2"/>
@@ -8998,7 +9001,7 @@
       <c r="R258" s="2"/>
       <c r="S258" s="2"/>
     </row>
-    <row r="259" spans="1:19" ht="13.2">
+    <row r="259" spans="1:19" ht="12.75">
       <c r="A259" s="2"/>
       <c r="B259" s="2"/>
       <c r="C259" s="2"/>
@@ -9019,7 +9022,7 @@
       <c r="R259" s="2"/>
       <c r="S259" s="2"/>
     </row>
-    <row r="260" spans="1:19" ht="13.2">
+    <row r="260" spans="1:19" ht="12.75">
       <c r="A260" s="2"/>
       <c r="B260" s="2"/>
       <c r="C260" s="2"/>
@@ -9040,7 +9043,7 @@
       <c r="R260" s="2"/>
       <c r="S260" s="2"/>
     </row>
-    <row r="261" spans="1:19" ht="13.2">
+    <row r="261" spans="1:19" ht="12.75">
       <c r="A261" s="2"/>
       <c r="B261" s="2"/>
       <c r="C261" s="2"/>
@@ -9061,7 +9064,7 @@
       <c r="R261" s="2"/>
       <c r="S261" s="2"/>
     </row>
-    <row r="262" spans="1:19" ht="13.2">
+    <row r="262" spans="1:19" ht="12.75">
       <c r="A262" s="2"/>
       <c r="B262" s="2"/>
       <c r="C262" s="2"/>
@@ -9082,7 +9085,7 @@
       <c r="R262" s="2"/>
       <c r="S262" s="2"/>
     </row>
-    <row r="263" spans="1:19" ht="13.2">
+    <row r="263" spans="1:19" ht="12.75">
       <c r="A263" s="2"/>
       <c r="B263" s="2"/>
       <c r="C263" s="2"/>
@@ -9103,7 +9106,7 @@
       <c r="R263" s="2"/>
       <c r="S263" s="2"/>
     </row>
-    <row r="264" spans="1:19" ht="13.2">
+    <row r="264" spans="1:19" ht="12.75">
       <c r="A264" s="2"/>
       <c r="B264" s="2"/>
       <c r="C264" s="2"/>
@@ -9124,7 +9127,7 @@
       <c r="R264" s="2"/>
       <c r="S264" s="2"/>
     </row>
-    <row r="265" spans="1:19" ht="13.2">
+    <row r="265" spans="1:19" ht="12.75">
       <c r="A265" s="2"/>
       <c r="B265" s="2"/>
       <c r="C265" s="2"/>
@@ -9145,7 +9148,7 @@
       <c r="R265" s="2"/>
       <c r="S265" s="2"/>
     </row>
-    <row r="266" spans="1:19" ht="13.2">
+    <row r="266" spans="1:19" ht="12.75">
       <c r="A266" s="2"/>
       <c r="B266" s="2"/>
       <c r="C266" s="2"/>
@@ -9166,7 +9169,7 @@
       <c r="R266" s="2"/>
       <c r="S266" s="2"/>
     </row>
-    <row r="267" spans="1:19" ht="13.2">
+    <row r="267" spans="1:19" ht="12.75">
       <c r="A267" s="2"/>
       <c r="B267" s="2"/>
       <c r="C267" s="2"/>
@@ -9187,7 +9190,7 @@
       <c r="R267" s="2"/>
       <c r="S267" s="2"/>
     </row>
-    <row r="268" spans="1:19" ht="13.2">
+    <row r="268" spans="1:19" ht="12.75">
       <c r="A268" s="2"/>
       <c r="B268" s="2"/>
       <c r="C268" s="2"/>
@@ -9208,7 +9211,7 @@
       <c r="R268" s="2"/>
       <c r="S268" s="2"/>
     </row>
-    <row r="269" spans="1:19" ht="13.2">
+    <row r="269" spans="1:19" ht="12.75">
       <c r="A269" s="2"/>
       <c r="B269" s="2"/>
       <c r="C269" s="2"/>
@@ -9229,7 +9232,7 @@
       <c r="R269" s="2"/>
       <c r="S269" s="2"/>
     </row>
-    <row r="270" spans="1:19" ht="13.2">
+    <row r="270" spans="1:19" ht="12.75">
       <c r="A270" s="2"/>
       <c r="B270" s="2"/>
       <c r="C270" s="2"/>
@@ -9250,7 +9253,7 @@
       <c r="R270" s="2"/>
       <c r="S270" s="2"/>
     </row>
-    <row r="271" spans="1:19" ht="13.2">
+    <row r="271" spans="1:19" ht="12.75">
       <c r="A271" s="2"/>
       <c r="B271" s="2"/>
       <c r="C271" s="2"/>
@@ -9271,7 +9274,7 @@
       <c r="R271" s="2"/>
       <c r="S271" s="2"/>
     </row>
-    <row r="272" spans="1:19" ht="13.2">
+    <row r="272" spans="1:19" ht="12.75">
       <c r="A272" s="2"/>
       <c r="B272" s="2"/>
       <c r="C272" s="2"/>
@@ -9292,7 +9295,7 @@
       <c r="R272" s="2"/>
       <c r="S272" s="2"/>
     </row>
-    <row r="273" spans="1:19" ht="13.2">
+    <row r="273" spans="1:19" ht="12.75">
       <c r="A273" s="2"/>
       <c r="B273" s="2"/>
       <c r="C273" s="2"/>
@@ -9313,7 +9316,7 @@
       <c r="R273" s="2"/>
       <c r="S273" s="2"/>
     </row>
-    <row r="274" spans="1:19" ht="13.2">
+    <row r="274" spans="1:19" ht="12.75">
       <c r="A274" s="2"/>
       <c r="B274" s="2"/>
       <c r="C274" s="2"/>
@@ -9334,7 +9337,7 @@
       <c r="R274" s="2"/>
       <c r="S274" s="2"/>
     </row>
-    <row r="275" spans="1:19" ht="13.2">
+    <row r="275" spans="1:19" ht="12.75">
       <c r="A275" s="2"/>
       <c r="B275" s="2"/>
       <c r="C275" s="2"/>
@@ -9355,7 +9358,7 @@
       <c r="R275" s="2"/>
       <c r="S275" s="2"/>
     </row>
-    <row r="276" spans="1:19" ht="13.2">
+    <row r="276" spans="1:19" ht="12.75">
       <c r="A276" s="2"/>
       <c r="B276" s="2"/>
       <c r="C276" s="2"/>
@@ -9376,7 +9379,7 @@
       <c r="R276" s="2"/>
       <c r="S276" s="2"/>
     </row>
-    <row r="277" spans="1:19" ht="13.2">
+    <row r="277" spans="1:19" ht="12.75">
       <c r="A277" s="2"/>
       <c r="B277" s="2"/>
       <c r="C277" s="2"/>
@@ -9397,7 +9400,7 @@
       <c r="R277" s="2"/>
       <c r="S277" s="2"/>
     </row>
-    <row r="278" spans="1:19" ht="13.2">
+    <row r="278" spans="1:19" ht="12.75">
       <c r="A278" s="2"/>
       <c r="B278" s="2"/>
       <c r="C278" s="2"/>
@@ -9418,7 +9421,7 @@
       <c r="R278" s="2"/>
       <c r="S278" s="2"/>
     </row>
-    <row r="279" spans="1:19" ht="13.2">
+    <row r="279" spans="1:19" ht="12.75">
       <c r="A279" s="2"/>
       <c r="B279" s="2"/>
       <c r="C279" s="2"/>
@@ -9439,7 +9442,7 @@
       <c r="R279" s="2"/>
       <c r="S279" s="2"/>
     </row>
-    <row r="280" spans="1:19" ht="13.2">
+    <row r="280" spans="1:19" ht="12.75">
       <c r="A280" s="2"/>
       <c r="B280" s="2"/>
       <c r="C280" s="2"/>
@@ -9460,7 +9463,7 @@
       <c r="R280" s="2"/>
       <c r="S280" s="2"/>
     </row>
-    <row r="281" spans="1:19" ht="13.2">
+    <row r="281" spans="1:19" ht="12.75">
       <c r="A281" s="2"/>
       <c r="B281" s="2"/>
       <c r="C281" s="2"/>
@@ -9481,7 +9484,7 @@
       <c r="R281" s="2"/>
       <c r="S281" s="2"/>
     </row>
-    <row r="282" spans="1:19" ht="13.2">
+    <row r="282" spans="1:19" ht="12.75">
       <c r="A282" s="2"/>
       <c r="B282" s="2"/>
       <c r="C282" s="2"/>
@@ -9502,7 +9505,7 @@
       <c r="R282" s="2"/>
       <c r="S282" s="2"/>
     </row>
-    <row r="283" spans="1:19" ht="13.2">
+    <row r="283" spans="1:19" ht="12.75">
       <c r="A283" s="2"/>
       <c r="B283" s="2"/>
       <c r="C283" s="2"/>
@@ -9523,7 +9526,7 @@
       <c r="R283" s="2"/>
       <c r="S283" s="2"/>
     </row>
-    <row r="284" spans="1:19" ht="13.2">
+    <row r="284" spans="1:19" ht="12.75">
       <c r="A284" s="2"/>
       <c r="B284" s="2"/>
       <c r="C284" s="2"/>
@@ -9544,7 +9547,7 @@
       <c r="R284" s="2"/>
       <c r="S284" s="2"/>
     </row>
-    <row r="285" spans="1:19" ht="13.2">
+    <row r="285" spans="1:19" ht="12.75">
       <c r="A285" s="2"/>
       <c r="B285" s="2"/>
       <c r="C285" s="2"/>
@@ -9565,7 +9568,7 @@
       <c r="R285" s="2"/>
       <c r="S285" s="2"/>
     </row>
-    <row r="286" spans="1:19" ht="13.2">
+    <row r="286" spans="1:19" ht="12.75">
       <c r="A286" s="2"/>
       <c r="B286" s="2"/>
       <c r="C286" s="2"/>
@@ -9586,7 +9589,7 @@
       <c r="R286" s="2"/>
       <c r="S286" s="2"/>
     </row>
-    <row r="287" spans="1:19" ht="13.2">
+    <row r="287" spans="1:19" ht="12.75">
       <c r="A287" s="2"/>
       <c r="B287" s="2"/>
       <c r="C287" s="2"/>
@@ -9607,7 +9610,7 @@
       <c r="R287" s="2"/>
       <c r="S287" s="2"/>
     </row>
-    <row r="288" spans="1:19" ht="13.2">
+    <row r="288" spans="1:19" ht="12.75">
       <c r="A288" s="2"/>
       <c r="B288" s="2"/>
       <c r="C288" s="2"/>
@@ -9628,7 +9631,7 @@
       <c r="R288" s="2"/>
       <c r="S288" s="2"/>
     </row>
-    <row r="289" spans="1:19" ht="13.2">
+    <row r="289" spans="1:19" ht="12.75">
       <c r="A289" s="2"/>
       <c r="B289" s="2"/>
       <c r="C289" s="2"/>
@@ -9649,7 +9652,7 @@
       <c r="R289" s="2"/>
       <c r="S289" s="2"/>
     </row>
-    <row r="290" spans="1:19" ht="13.2">
+    <row r="290" spans="1:19" ht="12.75">
       <c r="A290" s="2"/>
       <c r="B290" s="2"/>
       <c r="C290" s="2"/>
@@ -9670,7 +9673,7 @@
       <c r="R290" s="2"/>
       <c r="S290" s="2"/>
     </row>
-    <row r="291" spans="1:19" ht="13.2">
+    <row r="291" spans="1:19" ht="12.75">
       <c r="A291" s="2"/>
       <c r="B291" s="2"/>
       <c r="C291" s="2"/>
@@ -9691,7 +9694,7 @@
       <c r="R291" s="2"/>
       <c r="S291" s="2"/>
     </row>
-    <row r="292" spans="1:19" ht="13.2">
+    <row r="292" spans="1:19" ht="12.75">
       <c r="A292" s="2"/>
       <c r="B292" s="2"/>
       <c r="C292" s="2"/>
@@ -9712,7 +9715,7 @@
       <c r="R292" s="2"/>
       <c r="S292" s="2"/>
     </row>
-    <row r="293" spans="1:19" ht="13.2">
+    <row r="293" spans="1:19" ht="12.75">
       <c r="A293" s="2"/>
       <c r="B293" s="2"/>
       <c r="C293" s="2"/>
@@ -9733,7 +9736,7 @@
       <c r="R293" s="2"/>
       <c r="S293" s="2"/>
     </row>
-    <row r="294" spans="1:19" ht="13.2">
+    <row r="294" spans="1:19" ht="12.75">
       <c r="A294" s="2"/>
       <c r="B294" s="2"/>
       <c r="C294" s="2"/>
@@ -9754,7 +9757,7 @@
       <c r="R294" s="2"/>
       <c r="S294" s="2"/>
     </row>
-    <row r="295" spans="1:19" ht="13.2">
+    <row r="295" spans="1:19" ht="12.75">
       <c r="A295" s="2"/>
       <c r="B295" s="2"/>
       <c r="C295" s="2"/>
@@ -9775,7 +9778,7 @@
       <c r="R295" s="2"/>
       <c r="S295" s="2"/>
     </row>
-    <row r="296" spans="1:19" ht="13.2">
+    <row r="296" spans="1:19" ht="12.75">
       <c r="A296" s="2"/>
       <c r="B296" s="2"/>
       <c r="C296" s="2"/>
@@ -9796,7 +9799,7 @@
       <c r="R296" s="2"/>
       <c r="S296" s="2"/>
     </row>
-    <row r="297" spans="1:19" ht="13.2">
+    <row r="297" spans="1:19" ht="12.75">
       <c r="A297" s="2"/>
       <c r="B297" s="2"/>
       <c r="C297" s="2"/>
@@ -9817,7 +9820,7 @@
       <c r="R297" s="2"/>
       <c r="S297" s="2"/>
     </row>
-    <row r="298" spans="1:19" ht="13.2">
+    <row r="298" spans="1:19" ht="12.75">
       <c r="A298" s="2"/>
       <c r="B298" s="2"/>
       <c r="C298" s="2"/>
@@ -9838,7 +9841,7 @@
       <c r="R298" s="2"/>
       <c r="S298" s="2"/>
     </row>
-    <row r="299" spans="1:19" ht="13.2">
+    <row r="299" spans="1:19" ht="12.75">
       <c r="A299" s="2"/>
       <c r="B299" s="2"/>
       <c r="C299" s="2"/>
@@ -9859,7 +9862,7 @@
       <c r="R299" s="2"/>
       <c r="S299" s="2"/>
     </row>
-    <row r="300" spans="1:19" ht="13.2">
+    <row r="300" spans="1:19" ht="12.75">
       <c r="A300" s="2"/>
       <c r="B300" s="2"/>
       <c r="C300" s="2"/>
@@ -9880,7 +9883,7 @@
       <c r="R300" s="2"/>
       <c r="S300" s="2"/>
     </row>
-    <row r="301" spans="1:19" ht="13.2">
+    <row r="301" spans="1:19" ht="12.75">
       <c r="A301" s="2"/>
       <c r="B301" s="2"/>
       <c r="C301" s="2"/>
@@ -9901,7 +9904,7 @@
       <c r="R301" s="2"/>
       <c r="S301" s="2"/>
     </row>
-    <row r="302" spans="1:19" ht="13.2">
+    <row r="302" spans="1:19" ht="12.75">
       <c r="A302" s="2"/>
       <c r="B302" s="2"/>
       <c r="C302" s="2"/>
@@ -9922,7 +9925,7 @@
       <c r="R302" s="2"/>
       <c r="S302" s="2"/>
     </row>
-    <row r="303" spans="1:19" ht="13.2">
+    <row r="303" spans="1:19" ht="12.75">
       <c r="A303" s="2"/>
       <c r="B303" s="2"/>
       <c r="C303" s="2"/>
@@ -9943,7 +9946,7 @@
       <c r="R303" s="2"/>
       <c r="S303" s="2"/>
     </row>
-    <row r="304" spans="1:19" ht="13.2">
+    <row r="304" spans="1:19" ht="12.75">
       <c r="A304" s="2"/>
       <c r="B304" s="2"/>
       <c r="C304" s="2"/>
@@ -9964,7 +9967,7 @@
       <c r="R304" s="2"/>
       <c r="S304" s="2"/>
     </row>
-    <row r="305" spans="1:19" ht="13.2">
+    <row r="305" spans="1:19" ht="12.75">
       <c r="A305" s="2"/>
       <c r="B305" s="2"/>
       <c r="C305" s="2"/>
@@ -9985,7 +9988,7 @@
       <c r="R305" s="2"/>
       <c r="S305" s="2"/>
     </row>
-    <row r="306" spans="1:19" ht="13.2">
+    <row r="306" spans="1:19" ht="12.75">
       <c r="A306" s="2"/>
       <c r="B306" s="2"/>
       <c r="C306" s="2"/>
@@ -10006,7 +10009,7 @@
       <c r="R306" s="2"/>
       <c r="S306" s="2"/>
     </row>
-    <row r="307" spans="1:19" ht="13.2">
+    <row r="307" spans="1:19" ht="12.75">
       <c r="A307" s="2"/>
       <c r="B307" s="2"/>
       <c r="C307" s="2"/>
@@ -10027,7 +10030,7 @@
       <c r="R307" s="2"/>
       <c r="S307" s="2"/>
     </row>
-    <row r="308" spans="1:19" ht="13.2">
+    <row r="308" spans="1:19" ht="12.75">
       <c r="A308" s="2"/>
       <c r="B308" s="2"/>
       <c r="C308" s="2"/>
@@ -10048,7 +10051,7 @@
       <c r="R308" s="2"/>
       <c r="S308" s="2"/>
     </row>
-    <row r="309" spans="1:19" ht="13.2">
+    <row r="309" spans="1:19" ht="12.75">
       <c r="A309" s="2"/>
       <c r="B309" s="2"/>
       <c r="C309" s="2"/>
@@ -10069,7 +10072,7 @@
       <c r="R309" s="2"/>
       <c r="S309" s="2"/>
     </row>
-    <row r="310" spans="1:19" ht="13.2">
+    <row r="310" spans="1:19" ht="12.75">
       <c r="A310" s="2"/>
       <c r="B310" s="2"/>
       <c r="C310" s="2"/>
@@ -10090,7 +10093,7 @@
       <c r="R310" s="2"/>
       <c r="S310" s="2"/>
     </row>
-    <row r="311" spans="1:19" ht="13.2">
+    <row r="311" spans="1:19" ht="12.75">
       <c r="A311" s="2"/>
       <c r="B311" s="2"/>
       <c r="C311" s="2"/>
@@ -10111,7 +10114,7 @@
       <c r="R311" s="2"/>
       <c r="S311" s="2"/>
     </row>
-    <row r="312" spans="1:19" ht="13.2">
+    <row r="312" spans="1:19" ht="12.75">
       <c r="A312" s="2"/>
       <c r="B312" s="2"/>
       <c r="C312" s="2"/>
@@ -10132,7 +10135,7 @@
       <c r="R312" s="2"/>
       <c r="S312" s="2"/>
     </row>
-    <row r="313" spans="1:19" ht="13.2">
+    <row r="313" spans="1:19" ht="12.75">
       <c r="A313" s="2"/>
       <c r="B313" s="2"/>
       <c r="C313" s="2"/>
@@ -10153,7 +10156,7 @@
       <c r="R313" s="2"/>
       <c r="S313" s="2"/>
     </row>
-    <row r="314" spans="1:19" ht="13.2">
+    <row r="314" spans="1:19" ht="12.75">
       <c r="A314" s="2"/>
       <c r="B314" s="2"/>
       <c r="C314" s="2"/>
@@ -10174,7 +10177,7 @@
       <c r="R314" s="2"/>
       <c r="S314" s="2"/>
     </row>
-    <row r="315" spans="1:19" ht="13.2">
+    <row r="315" spans="1:19" ht="12.75">
       <c r="A315" s="2"/>
       <c r="B315" s="2"/>
       <c r="C315" s="2"/>
@@ -10195,7 +10198,7 @@
       <c r="R315" s="2"/>
       <c r="S315" s="2"/>
     </row>
-    <row r="316" spans="1:19" ht="13.2">
+    <row r="316" spans="1:19" ht="12.75">
       <c r="A316" s="2"/>
       <c r="B316" s="2"/>
       <c r="C316" s="2"/>
@@ -10216,7 +10219,7 @@
       <c r="R316" s="2"/>
       <c r="S316" s="2"/>
     </row>
-    <row r="317" spans="1:19" ht="13.2">
+    <row r="317" spans="1:19" ht="12.75">
       <c r="A317" s="2"/>
       <c r="B317" s="2"/>
       <c r="C317" s="2"/>
@@ -10237,7 +10240,7 @@
       <c r="R317" s="2"/>
       <c r="S317" s="2"/>
     </row>
-    <row r="318" spans="1:19" ht="13.2">
+    <row r="318" spans="1:19" ht="12.75">
       <c r="A318" s="2"/>
       <c r="B318" s="2"/>
       <c r="C318" s="2"/>
@@ -10258,7 +10261,7 @@
       <c r="R318" s="2"/>
       <c r="S318" s="2"/>
     </row>
-    <row r="319" spans="1:19" ht="13.2">
+    <row r="319" spans="1:19" ht="12.75">
       <c r="A319" s="2"/>
       <c r="B319" s="2"/>
       <c r="C319" s="2"/>
@@ -10279,7 +10282,7 @@
       <c r="R319" s="2"/>
       <c r="S319" s="2"/>
     </row>
-    <row r="320" spans="1:19" ht="13.2">
+    <row r="320" spans="1:19" ht="12.75">
       <c r="A320" s="2"/>
       <c r="B320" s="2"/>
       <c r="C320" s="2"/>
@@ -10300,7 +10303,7 @@
       <c r="R320" s="2"/>
       <c r="S320" s="2"/>
     </row>
-    <row r="321" spans="1:19" ht="13.2">
+    <row r="321" spans="1:19" ht="12.75">
       <c r="A321" s="2"/>
       <c r="B321" s="2"/>
       <c r="C321" s="2"/>
@@ -10321,7 +10324,7 @@
       <c r="R321" s="2"/>
       <c r="S321" s="2"/>
     </row>
-    <row r="322" spans="1:19" ht="13.2">
+    <row r="322" spans="1:19" ht="12.75">
       <c r="A322" s="2"/>
       <c r="B322" s="2"/>
       <c r="C322" s="2"/>
@@ -10342,7 +10345,7 @@
       <c r="R322" s="2"/>
       <c r="S322" s="2"/>
     </row>
-    <row r="323" spans="1:19" ht="13.2">
+    <row r="323" spans="1:19" ht="12.75">
       <c r="A323" s="2"/>
       <c r="B323" s="2"/>
       <c r="C323" s="2"/>
@@ -10363,7 +10366,7 @@
       <c r="R323" s="2"/>
       <c r="S323" s="2"/>
     </row>
-    <row r="324" spans="1:19" ht="13.2">
+    <row r="324" spans="1:19" ht="12.75">
       <c r="A324" s="2"/>
       <c r="B324" s="2"/>
       <c r="C324" s="2"/>
@@ -10384,7 +10387,7 @@
       <c r="R324" s="2"/>
       <c r="S324" s="2"/>
     </row>
-    <row r="325" spans="1:19" ht="13.2">
+    <row r="325" spans="1:19" ht="12.75">
       <c r="A325" s="2"/>
       <c r="B325" s="2"/>
       <c r="C325" s="2"/>
@@ -10405,7 +10408,7 @@
       <c r="R325" s="2"/>
       <c r="S325" s="2"/>
     </row>
-    <row r="326" spans="1:19" ht="13.2">
+    <row r="326" spans="1:19" ht="12.75">
       <c r="A326" s="2"/>
       <c r="B326" s="2"/>
       <c r="C326" s="2"/>
@@ -10426,7 +10429,7 @@
       <c r="R326" s="2"/>
       <c r="S326" s="2"/>
     </row>
-    <row r="327" spans="1:19" ht="13.2">
+    <row r="327" spans="1:19" ht="12.75">
       <c r="A327" s="2"/>
       <c r="B327" s="2"/>
       <c r="C327" s="2"/>
@@ -10447,7 +10450,7 @@
       <c r="R327" s="2"/>
       <c r="S327" s="2"/>
     </row>
-    <row r="328" spans="1:19" ht="13.2">
+    <row r="328" spans="1:19" ht="12.75">
       <c r="A328" s="2"/>
       <c r="B328" s="2"/>
       <c r="C328" s="2"/>
@@ -10468,7 +10471,7 @@
       <c r="R328" s="2"/>
       <c r="S328" s="2"/>
     </row>
-    <row r="329" spans="1:19" ht="13.2">
+    <row r="329" spans="1:19" ht="12.75">
       <c r="A329" s="2"/>
       <c r="B329" s="2"/>
       <c r="C329" s="2"/>
@@ -10489,7 +10492,7 @@
       <c r="R329" s="2"/>
       <c r="S329" s="2"/>
     </row>
-    <row r="330" spans="1:19" ht="13.2">
+    <row r="330" spans="1:19" ht="12.75">
       <c r="A330" s="2"/>
       <c r="B330" s="2"/>
       <c r="C330" s="2"/>
@@ -10510,7 +10513,7 @@
       <c r="R330" s="2"/>
       <c r="S330" s="2"/>
     </row>
-    <row r="331" spans="1:19" ht="13.2">
+    <row r="331" spans="1:19" ht="12.75">
       <c r="A331" s="2"/>
       <c r="B331" s="2"/>
       <c r="C331" s="2"/>
@@ -10531,7 +10534,7 @@
       <c r="R331" s="2"/>
       <c r="S331" s="2"/>
     </row>
-    <row r="332" spans="1:19" ht="13.2">
+    <row r="332" spans="1:19" ht="12.75">
       <c r="A332" s="2"/>
       <c r="B332" s="2"/>
       <c r="C332" s="2"/>
@@ -10552,7 +10555,7 @@
       <c r="R332" s="2"/>
       <c r="S332" s="2"/>
     </row>
-    <row r="333" spans="1:19" ht="13.2">
+    <row r="333" spans="1:19" ht="12.75">
       <c r="A333" s="2"/>
       <c r="B333" s="2"/>
       <c r="C333" s="2"/>
@@ -10573,7 +10576,7 @@
       <c r="R333" s="2"/>
       <c r="S333" s="2"/>
     </row>
-    <row r="334" spans="1:19" ht="13.2">
+    <row r="334" spans="1:19" ht="12.75">
       <c r="A334" s="2"/>
       <c r="B334" s="2"/>
       <c r="C334" s="2"/>
@@ -10594,7 +10597,7 @@
       <c r="R334" s="2"/>
       <c r="S334" s="2"/>
     </row>
-    <row r="335" spans="1:19" ht="13.2">
+    <row r="335" spans="1:19" ht="12.75">
       <c r="A335" s="2"/>
       <c r="B335" s="2"/>
       <c r="C335" s="2"/>
@@ -10615,7 +10618,7 @@
       <c r="R335" s="2"/>
       <c r="S335" s="2"/>
     </row>
-    <row r="336" spans="1:19" ht="13.2">
+    <row r="336" spans="1:19" ht="12.75">
       <c r="A336" s="2"/>
       <c r="B336" s="2"/>
       <c r="C336" s="2"/>
@@ -10636,7 +10639,7 @@
       <c r="R336" s="2"/>
       <c r="S336" s="2"/>
     </row>
-    <row r="337" spans="1:19" ht="13.2">
+    <row r="337" spans="1:19" ht="12.75">
       <c r="A337" s="2"/>
       <c r="B337" s="2"/>
       <c r="C337" s="2"/>
@@ -10657,7 +10660,7 @@
       <c r="R337" s="2"/>
       <c r="S337" s="2"/>
     </row>
-    <row r="338" spans="1:19" ht="13.2">
+    <row r="338" spans="1:19" ht="12.75">
       <c r="A338" s="2"/>
       <c r="B338" s="2"/>
       <c r="C338" s="2"/>
@@ -10678,7 +10681,7 @@
       <c r="R338" s="2"/>
       <c r="S338" s="2"/>
     </row>
-    <row r="339" spans="1:19" ht="13.2">
+    <row r="339" spans="1:19" ht="12.75">
       <c r="A339" s="2"/>
       <c r="B339" s="2"/>
       <c r="C339" s="2"/>
@@ -10699,7 +10702,7 @@
       <c r="R339" s="2"/>
       <c r="S339" s="2"/>
     </row>
-    <row r="340" spans="1:19" ht="13.2">
+    <row r="340" spans="1:19" ht="12.75">
       <c r="A340" s="2"/>
       <c r="B340" s="2"/>
       <c r="C340" s="2"/>
@@ -10720,7 +10723,7 @@
       <c r="R340" s="2"/>
       <c r="S340" s="2"/>
     </row>
-    <row r="341" spans="1:19" ht="13.2">
+    <row r="341" spans="1:19" ht="12.75">
       <c r="A341" s="2"/>
       <c r="B341" s="2"/>
       <c r="C341" s="2"/>
@@ -10741,7 +10744,7 @@
       <c r="R341" s="2"/>
       <c r="S341" s="2"/>
     </row>
-    <row r="342" spans="1:19" ht="13.2">
+    <row r="342" spans="1:19" ht="12.75">
       <c r="A342" s="2"/>
       <c r="B342" s="2"/>
       <c r="C342" s="2"/>
@@ -10762,7 +10765,7 @@
       <c r="R342" s="2"/>
       <c r="S342" s="2"/>
     </row>
-    <row r="343" spans="1:19" ht="13.2">
+    <row r="343" spans="1:19" ht="12.75">
       <c r="A343" s="2"/>
       <c r="B343" s="2"/>
       <c r="C343" s="2"/>
@@ -10783,7 +10786,7 @@
       <c r="R343" s="2"/>
       <c r="S343" s="2"/>
     </row>
-    <row r="344" spans="1:19" ht="13.2">
+    <row r="344" spans="1:19" ht="12.75">
       <c r="A344" s="2"/>
       <c r="B344" s="2"/>
       <c r="C344" s="2"/>
@@ -10804,7 +10807,7 @@
       <c r="R344" s="2"/>
       <c r="S344" s="2"/>
     </row>
-    <row r="345" spans="1:19" ht="13.2">
+    <row r="345" spans="1:19" ht="12.75">
       <c r="A345" s="2"/>
       <c r="B345" s="2"/>
       <c r="C345" s="2"/>
@@ -10825,7 +10828,7 @@
       <c r="R345" s="2"/>
       <c r="S345" s="2"/>
     </row>
-    <row r="346" spans="1:19" ht="13.2">
+    <row r="346" spans="1:19" ht="12.75">
       <c r="A346" s="2"/>
       <c r="B346" s="2"/>
       <c r="C346" s="2"/>
@@ -10846,7 +10849,7 @@
       <c r="R346" s="2"/>
       <c r="S346" s="2"/>
     </row>
-    <row r="347" spans="1:19" ht="13.2">
+    <row r="347" spans="1:19" ht="12.75">
       <c r="A347" s="2"/>
       <c r="B347" s="2"/>
       <c r="C347" s="2"/>
@@ -10867,7 +10870,7 @@
       <c r="R347" s="2"/>
       <c r="S347" s="2"/>
     </row>
-    <row r="348" spans="1:19" ht="13.2">
+    <row r="348" spans="1:19" ht="12.75">
       <c r="A348" s="2"/>
       <c r="B348" s="2"/>
       <c r="C348" s="2"/>
@@ -10888,7 +10891,7 @@
       <c r="R348" s="2"/>
       <c r="S348" s="2"/>
     </row>
-    <row r="349" spans="1:19" ht="13.2">
+    <row r="349" spans="1:19" ht="12.75">
       <c r="A349" s="2"/>
       <c r="B349" s="2"/>
       <c r="C349" s="2"/>
@@ -10909,7 +10912,7 @@
       <c r="R349" s="2"/>
       <c r="S349" s="2"/>
     </row>
-    <row r="350" spans="1:19" ht="13.2">
+    <row r="350" spans="1:19" ht="12.75">
       <c r="A350" s="2"/>
       <c r="B350" s="2"/>
       <c r="C350" s="2"/>
@@ -10930,7 +10933,7 @@
       <c r="R350" s="2"/>
       <c r="S350" s="2"/>
     </row>
-    <row r="351" spans="1:19" ht="13.2">
+    <row r="351" spans="1:19" ht="12.75">
       <c r="A351" s="2"/>
       <c r="B351" s="2"/>
       <c r="C351" s="2"/>
@@ -10951,7 +10954,7 @@
       <c r="R351" s="2"/>
       <c r="S351" s="2"/>
     </row>
-    <row r="352" spans="1:19" ht="13.2">
+    <row r="352" spans="1:19" ht="12.75">
       <c r="A352" s="2"/>
       <c r="B352" s="2"/>
       <c r="C352" s="2"/>
@@ -10972,7 +10975,7 @@
       <c r="R352" s="2"/>
       <c r="S352" s="2"/>
     </row>
-    <row r="353" spans="1:19" ht="13.2">
+    <row r="353" spans="1:19" ht="12.75">
       <c r="A353" s="2"/>
       <c r="B353" s="2"/>
       <c r="C353" s="2"/>
@@ -10993,7 +10996,7 @@
       <c r="R353" s="2"/>
       <c r="S353" s="2"/>
     </row>
-    <row r="354" spans="1:19" ht="13.2">
+    <row r="354" spans="1:19" ht="12.75">
       <c r="A354" s="2"/>
       <c r="B354" s="2"/>
       <c r="C354" s="2"/>
@@ -11014,7 +11017,7 @@
       <c r="R354" s="2"/>
       <c r="S354" s="2"/>
     </row>
-    <row r="355" spans="1:19" ht="13.2">
+    <row r="355" spans="1:19" ht="12.75">
       <c r="A355" s="2"/>
       <c r="B355" s="2"/>
       <c r="C355" s="2"/>
@@ -11035,7 +11038,7 @@
       <c r="R355" s="2"/>
       <c r="S355" s="2"/>
     </row>
-    <row r="356" spans="1:19" ht="13.2">
+    <row r="356" spans="1:19" ht="12.75">
       <c r="A356" s="2"/>
       <c r="B356" s="2"/>
       <c r="C356" s="2"/>
@@ -11056,7 +11059,7 @@
       <c r="R356" s="2"/>
       <c r="S356" s="2"/>
     </row>
-    <row r="357" spans="1:19" ht="13.2">
+    <row r="357" spans="1:19" ht="12.75">
       <c r="A357" s="2"/>
       <c r="B357" s="2"/>
       <c r="C357" s="2"/>
@@ -11077,7 +11080,7 @@
       <c r="R357" s="2"/>
       <c r="S357" s="2"/>
     </row>
-    <row r="358" spans="1:19" ht="13.2">
+    <row r="358" spans="1:19" ht="12.75">
       <c r="A358" s="2"/>
       <c r="B358" s="2"/>
       <c r="C358" s="2"/>
@@ -11098,7 +11101,7 @@
       <c r="R358" s="2"/>
       <c r="S358" s="2"/>
     </row>
-    <row r="359" spans="1:19" ht="13.2">
+    <row r="359" spans="1:19" ht="12.75">
       <c r="A359" s="2"/>
       <c r="B359" s="2"/>
       <c r="C359" s="2"/>
@@ -11119,7 +11122,7 @@
       <c r="R359" s="2"/>
       <c r="S359" s="2"/>
     </row>
-    <row r="360" spans="1:19" ht="13.2">
+    <row r="360" spans="1:19" ht="12.75">
       <c r="A360" s="2"/>
       <c r="B360" s="2"/>
       <c r="C360" s="2"/>
@@ -11140,7 +11143,7 @@
       <c r="R360" s="2"/>
       <c r="S360" s="2"/>
     </row>
-    <row r="361" spans="1:19" ht="13.2">
+    <row r="361" spans="1:19" ht="12.75">
       <c r="A361" s="2"/>
       <c r="B361" s="2"/>
       <c r="C361" s="2"/>
@@ -11161,7 +11164,7 @@
       <c r="R361" s="2"/>
       <c r="S361" s="2"/>
     </row>
-    <row r="362" spans="1:19" ht="13.2">
+    <row r="362" spans="1:19" ht="12.75">
       <c r="A362" s="2"/>
       <c r="B362" s="2"/>
       <c r="C362" s="2"/>
@@ -11182,7 +11185,7 @@
       <c r="R362" s="2"/>
       <c r="S362" s="2"/>
     </row>
-    <row r="363" spans="1:19" ht="13.2">
+    <row r="363" spans="1:19" ht="12.75">
       <c r="A363" s="2"/>
       <c r="B363" s="2"/>
       <c r="C363" s="2"/>
@@ -11203,7 +11206,7 @@
       <c r="R363" s="2"/>
       <c r="S363" s="2"/>
     </row>
-    <row r="364" spans="1:19" ht="13.2">
+    <row r="364" spans="1:19" ht="12.75">
       <c r="A364" s="2"/>
       <c r="B364" s="2"/>
       <c r="C364" s="2"/>
@@ -11224,7 +11227,7 @@
       <c r="R364" s="2"/>
       <c r="S364" s="2"/>
     </row>
-    <row r="365" spans="1:19" ht="13.2">
+    <row r="365" spans="1:19" ht="12.75">
       <c r="A365" s="2"/>
       <c r="B365" s="2"/>
       <c r="C365" s="2"/>
@@ -11245,7 +11248,7 @@
       <c r="R365" s="2"/>
       <c r="S365" s="2"/>
     </row>
-    <row r="366" spans="1:19" ht="13.2">
+    <row r="366" spans="1:19" ht="12.75">
       <c r="A366" s="2"/>
       <c r="B366" s="2"/>
       <c r="C366" s="2"/>
@@ -11266,7 +11269,7 @@
       <c r="R366" s="2"/>
       <c r="S366" s="2"/>
     </row>
-    <row r="367" spans="1:19" ht="13.2">
+    <row r="367" spans="1:19" ht="12.75">
       <c r="A367" s="2"/>
       <c r="B367" s="2"/>
       <c r="C367" s="2"/>
@@ -11287,7 +11290,7 @@
       <c r="R367" s="2"/>
       <c r="S367" s="2"/>
     </row>
-    <row r="368" spans="1:19" ht="13.2">
+    <row r="368" spans="1:19" ht="12.75">
       <c r="A368" s="2"/>
       <c r="B368" s="2"/>
       <c r="C368" s="2"/>
@@ -11308,7 +11311,7 @@
       <c r="R368" s="2"/>
       <c r="S368" s="2"/>
     </row>
-    <row r="369" spans="1:19" ht="13.2">
+    <row r="369" spans="1:19" ht="12.75">
       <c r="A369" s="2"/>
       <c r="B369" s="2"/>
       <c r="C369" s="2"/>
@@ -11329,7 +11332,7 @@
       <c r="R369" s="2"/>
       <c r="S369" s="2"/>
     </row>
-    <row r="370" spans="1:19" ht="13.2">
+    <row r="370" spans="1:19" ht="12.75">
       <c r="A370" s="2"/>
       <c r="B370" s="2"/>
       <c r="C370" s="2"/>
@@ -11350,7 +11353,7 @@
       <c r="R370" s="2"/>
       <c r="S370" s="2"/>
     </row>
-    <row r="371" spans="1:19" ht="13.2">
+    <row r="371" spans="1:19" ht="12.75">
       <c r="A371" s="2"/>
       <c r="B371" s="2"/>
       <c r="C371" s="2"/>
@@ -11371,7 +11374,7 @@
       <c r="R371" s="2"/>
       <c r="S371" s="2"/>
     </row>
-    <row r="372" spans="1:19" ht="13.2">
+    <row r="372" spans="1:19" ht="12.75">
       <c r="A372" s="2"/>
       <c r="B372" s="2"/>
       <c r="C372" s="2"/>
@@ -11392,7 +11395,7 @@
       <c r="R372" s="2"/>
       <c r="S372" s="2"/>
     </row>
-    <row r="373" spans="1:19" ht="13.2">
+    <row r="373" spans="1:19" ht="12.75">
       <c r="A373" s="2"/>
       <c r="B373" s="2"/>
       <c r="C373" s="2"/>
@@ -11413,7 +11416,7 @@
       <c r="R373" s="2"/>
       <c r="S373" s="2"/>
     </row>
-    <row r="374" spans="1:19" ht="13.2">
+    <row r="374" spans="1:19" ht="12.75">
       <c r="A374" s="2"/>
       <c r="B374" s="2"/>
       <c r="C374" s="2"/>
@@ -11434,7 +11437,7 @@
       <c r="R374" s="2"/>
       <c r="S374" s="2"/>
     </row>
-    <row r="375" spans="1:19" ht="13.2">
+    <row r="375" spans="1:19" ht="12.75">
       <c r="A375" s="2"/>
       <c r="B375" s="2"/>
       <c r="C375" s="2"/>
@@ -11455,7 +11458,7 @@
       <c r="R375" s="2"/>
       <c r="S375" s="2"/>
     </row>
-    <row r="376" spans="1:19" ht="13.2">
+    <row r="376" spans="1:19" ht="12.75">
       <c r="A376" s="2"/>
       <c r="B376" s="2"/>
       <c r="C376" s="2"/>
@@ -11476,7 +11479,7 @@
       <c r="R376" s="2"/>
       <c r="S376" s="2"/>
     </row>
-    <row r="377" spans="1:19" ht="13.2">
+    <row r="377" spans="1:19" ht="12.75">
       <c r="A377" s="2"/>
       <c r="B377" s="2"/>
       <c r="C377" s="2"/>
@@ -11497,7 +11500,7 @@
       <c r="R377" s="2"/>
       <c r="S377" s="2"/>
     </row>
-    <row r="378" spans="1:19" ht="13.2">
+    <row r="378" spans="1:19" ht="12.75">
       <c r="A378" s="2"/>
       <c r="B378" s="2"/>
       <c r="C378" s="2"/>
@@ -11518,7 +11521,7 @@
       <c r="R378" s="2"/>
       <c r="S378" s="2"/>
     </row>
-    <row r="379" spans="1:19" ht="13.2">
+    <row r="379" spans="1:19" ht="12.75">
       <c r="A379" s="2"/>
       <c r="B379" s="2"/>
       <c r="C379" s="2"/>
@@ -11539,7 +11542,7 @@
       <c r="R379" s="2"/>
       <c r="S379" s="2"/>
     </row>
-    <row r="380" spans="1:19" ht="13.2">
+    <row r="380" spans="1:19" ht="12.75">
       <c r="A380" s="2"/>
       <c r="B380" s="2"/>
       <c r="C380" s="2"/>
@@ -11560,7 +11563,7 @@
       <c r="R380" s="2"/>
       <c r="S380" s="2"/>
     </row>
-    <row r="381" spans="1:19" ht="13.2">
+    <row r="381" spans="1:19" ht="12.75">
       <c r="A381" s="2"/>
       <c r="B381" s="2"/>
       <c r="C381" s="2"/>
@@ -11581,7 +11584,7 @@
       <c r="R381" s="2"/>
       <c r="S381" s="2"/>
     </row>
-    <row r="382" spans="1:19" ht="13.2">
+    <row r="382" spans="1:19" ht="12.75">
       <c r="A382" s="2"/>
       <c r="B382" s="2"/>
       <c r="C382" s="2"/>
@@ -11602,7 +11605,7 @@
       <c r="R382" s="2"/>
       <c r="S382" s="2"/>
     </row>
-    <row r="383" spans="1:19" ht="13.2">
+    <row r="383" spans="1:19" ht="12.75">
       <c r="A383" s="2"/>
       <c r="B383" s="2"/>
       <c r="C383" s="2"/>
@@ -11623,7 +11626,7 @@
       <c r="R383" s="2"/>
       <c r="S383" s="2"/>
     </row>
-    <row r="384" spans="1:19" ht="13.2">
+    <row r="384" spans="1:19" ht="12.75">
       <c r="A384" s="2"/>
       <c r="B384" s="2"/>
       <c r="C384" s="2"/>
@@ -11644,7 +11647,7 @@
       <c r="R384" s="2"/>
       <c r="S384" s="2"/>
     </row>
-    <row r="385" spans="1:19" ht="13.2">
+    <row r="385" spans="1:19" ht="12.75">
       <c r="A385" s="2"/>
       <c r="B385" s="2"/>
       <c r="C385" s="2"/>
@@ -11665,7 +11668,7 @@
       <c r="R385" s="2"/>
       <c r="S385" s="2"/>
     </row>
-    <row r="386" spans="1:19" ht="13.2">
+    <row r="386" spans="1:19" ht="12.75">
       <c r="A386" s="2"/>
       <c r="B386" s="2"/>
       <c r="C386" s="2"/>
@@ -11686,7 +11689,7 @@
       <c r="R386" s="2"/>
       <c r="S386" s="2"/>
     </row>
-    <row r="387" spans="1:19" ht="13.2">
+    <row r="387" spans="1:19" ht="12.75">
       <c r="A387" s="2"/>
       <c r="B387" s="2"/>
       <c r="C387" s="2"/>
@@ -11707,7 +11710,7 @@
       <c r="R387" s="2"/>
       <c r="S387" s="2"/>
     </row>
-    <row r="388" spans="1:19" ht="13.2">
+    <row r="388" spans="1:19" ht="12.75">
       <c r="A388" s="2"/>
       <c r="B388" s="2"/>
       <c r="C388" s="2"/>
@@ -11728,7 +11731,7 @@
       <c r="R388" s="2"/>
       <c r="S388" s="2"/>
     </row>
-    <row r="389" spans="1:19" ht="13.2">
+    <row r="389" spans="1:19" ht="12.75">
       <c r="A389" s="2"/>
       <c r="B389" s="2"/>
       <c r="C389" s="2"/>
@@ -11749,7 +11752,7 @@
       <c r="R389" s="2"/>
       <c r="S389" s="2"/>
     </row>
-    <row r="390" spans="1:19" ht="13.2">
+    <row r="390" spans="1:19" ht="12.75">
       <c r="A390" s="2"/>
       <c r="B390" s="2"/>
       <c r="C390" s="2"/>
@@ -11770,7 +11773,7 @@
       <c r="R390" s="2"/>
       <c r="S390" s="2"/>
     </row>
-    <row r="391" spans="1:19" ht="13.2">
+    <row r="391" spans="1:19" ht="12.75">
       <c r="A391" s="2"/>
       <c r="B391" s="2"/>
       <c r="C391" s="2"/>
@@ -11791,7 +11794,7 @@
       <c r="R391" s="2"/>
       <c r="S391" s="2"/>
     </row>
-    <row r="392" spans="1:19" ht="13.2">
+    <row r="392" spans="1:19" ht="12.75">
       <c r="A392" s="2"/>
       <c r="B392" s="2"/>
       <c r="C392" s="2"/>
@@ -11812,7 +11815,7 @@
       <c r="R392" s="2"/>
       <c r="S392" s="2"/>
     </row>
-    <row r="393" spans="1:19" ht="13.2">
+    <row r="393" spans="1:19" ht="12.75">
       <c r="A393" s="2"/>
       <c r="B393" s="2"/>
       <c r="C393" s="2"/>
@@ -11833,7 +11836,7 @@
       <c r="R393" s="2"/>
       <c r="S393" s="2"/>
     </row>
-    <row r="394" spans="1:19" ht="13.2">
+    <row r="394" spans="1:19" ht="12.75">
       <c r="A394" s="2"/>
       <c r="B394" s="2"/>
       <c r="C394" s="2"/>
@@ -11854,7 +11857,7 @@
       <c r="R394" s="2"/>
       <c r="S394" s="2"/>
     </row>
-    <row r="395" spans="1:19" ht="13.2">
+    <row r="395" spans="1:19" ht="12.75">
       <c r="A395" s="2"/>
       <c r="B395" s="2"/>
       <c r="C395" s="2"/>
@@ -11875,7 +11878,7 @@
       <c r="R395" s="2"/>
       <c r="S395" s="2"/>
     </row>
-    <row r="396" spans="1:19" ht="13.2">
+    <row r="396" spans="1:19" ht="12.75">
       <c r="A396" s="2"/>
       <c r="B396" s="2"/>
       <c r="C396" s="2"/>
@@ -11896,7 +11899,7 @@
       <c r="R396" s="2"/>
       <c r="S396" s="2"/>
     </row>
-    <row r="397" spans="1:19" ht="13.2">
+    <row r="397" spans="1:19" ht="12.75">
       <c r="A397" s="2"/>
       <c r="B397" s="2"/>
       <c r="C397" s="2"/>
@@ -11917,7 +11920,7 @@
       <c r="R397" s="2"/>
       <c r="S397" s="2"/>
     </row>
-    <row r="398" spans="1:19" ht="13.2">
+    <row r="398" spans="1:19" ht="12.75">
       <c r="A398" s="2"/>
       <c r="B398" s="2"/>
       <c r="C398" s="2"/>
@@ -11938,7 +11941,7 @@
       <c r="R398" s="2"/>
       <c r="S398" s="2"/>
     </row>
-    <row r="399" spans="1:19" ht="13.2">
+    <row r="399" spans="1:19" ht="12.75">
       <c r="A399" s="2"/>
       <c r="B399" s="2"/>
       <c r="C399" s="2"/>
@@ -11959,7 +11962,7 @@
       <c r="R399" s="2"/>
       <c r="S399" s="2"/>
     </row>
-    <row r="400" spans="1:19" ht="13.2">
+    <row r="400" spans="1:19" ht="12.75">
       <c r="A400" s="2"/>
       <c r="B400" s="2"/>
       <c r="C400" s="2"/>
@@ -11980,7 +11983,7 @@
       <c r="R400" s="2"/>
       <c r="S400" s="2"/>
     </row>
-    <row r="401" spans="1:19" ht="13.2">
+    <row r="401" spans="1:19" ht="12.75">
       <c r="A401" s="2"/>
       <c r="B401" s="2"/>
       <c r="C401" s="2"/>
@@ -12001,7 +12004,7 @@
       <c r="R401" s="2"/>
       <c r="S401" s="2"/>
     </row>
-    <row r="402" spans="1:19" ht="13.2">
+    <row r="402" spans="1:19" ht="12.75">
       <c r="A402" s="2"/>
       <c r="B402" s="2"/>
       <c r="C402" s="2"/>
@@ -12022,7 +12025,7 @@
       <c r="R402" s="2"/>
       <c r="S402" s="2"/>
     </row>
-    <row r="403" spans="1:19" ht="13.2">
+    <row r="403" spans="1:19" ht="12.75">
       <c r="A403" s="2"/>
       <c r="B403" s="2"/>
       <c r="C403" s="2"/>
@@ -12043,7 +12046,7 @@
       <c r="R403" s="2"/>
       <c r="S403" s="2"/>
     </row>
-    <row r="404" spans="1:19" ht="13.2">
+    <row r="404" spans="1:19" ht="12.75">
       <c r="A404" s="2"/>
       <c r="B404" s="2"/>
       <c r="C404" s="2"/>
@@ -12064,7 +12067,7 @@
       <c r="R404" s="2"/>
       <c r="S404" s="2"/>
     </row>
-    <row r="405" spans="1:19" ht="13.2">
+    <row r="405" spans="1:19" ht="12.75">
       <c r="A405" s="2"/>
       <c r="B405" s="2"/>
       <c r="C405" s="2"/>
@@ -12085,7 +12088,7 @@
       <c r="R405" s="2"/>
       <c r="S405" s="2"/>
     </row>
-    <row r="406" spans="1:19" ht="13.2">
+    <row r="406" spans="1:19" ht="12.75">
       <c r="A406" s="2"/>
       <c r="B406" s="2"/>
       <c r="C406" s="2"/>
@@ -12106,7 +12109,7 @@
       <c r="R406" s="2"/>
       <c r="S406" s="2"/>
     </row>
-    <row r="407" spans="1:19" ht="13.2">
+    <row r="407" spans="1:19" ht="12.75">
       <c r="A407" s="2"/>
       <c r="B407" s="2"/>
       <c r="C407" s="2"/>
@@ -12127,7 +12130,7 @@
       <c r="R407" s="2"/>
       <c r="S407" s="2"/>
     </row>
-    <row r="408" spans="1:19" ht="13.2">
+    <row r="408" spans="1:19" ht="12.75">
       <c r="A408" s="2"/>
       <c r="B408" s="2"/>
       <c r="C408" s="2"/>
@@ -12148,7 +12151,7 @@
       <c r="R408" s="2"/>
       <c r="S408" s="2"/>
     </row>
-    <row r="409" spans="1:19" ht="13.2">
+    <row r="409" spans="1:19" ht="12.75">
       <c r="A409" s="2"/>
       <c r="B409" s="2"/>
       <c r="C409" s="2"/>
@@ -12169,7 +12172,7 @@
       <c r="R409" s="2"/>
       <c r="S409" s="2"/>
     </row>
-    <row r="410" spans="1:19" ht="13.2">
+    <row r="410" spans="1:19" ht="12.75">
       <c r="A410" s="2"/>
       <c r="B410" s="2"/>
       <c r="C410" s="2"/>
@@ -12190,7 +12193,7 @@
       <c r="R410" s="2"/>
       <c r="S410" s="2"/>
     </row>
-    <row r="411" spans="1:19" ht="13.2">
+    <row r="411" spans="1:19" ht="12.75">
       <c r="A411" s="2"/>
       <c r="B411" s="2"/>
       <c r="C411" s="2"/>
@@ -12211,7 +12214,7 @@
       <c r="R411" s="2"/>
       <c r="S411" s="2"/>
     </row>
-    <row r="412" spans="1:19" ht="13.2">
+    <row r="412" spans="1:19" ht="12.75">
       <c r="A412" s="2"/>
       <c r="B412" s="2"/>
       <c r="C412" s="2"/>
@@ -12232,7 +12235,7 @@
       <c r="R412" s="2"/>
       <c r="S412" s="2"/>
     </row>
-    <row r="413" spans="1:19" ht="13.2">
+    <row r="413" spans="1:19" ht="12.75">
       <c r="A413" s="2"/>
       <c r="B413" s="2"/>
       <c r="C413" s="2"/>
@@ -12253,7 +12256,7 @@
       <c r="R413" s="2"/>
       <c r="S413" s="2"/>
     </row>
-    <row r="414" spans="1:19" ht="13.2">
+    <row r="414" spans="1:19" ht="12.75">
       <c r="A414" s="2"/>
       <c r="B414" s="2"/>
       <c r="C414" s="2"/>
@@ -12274,7 +12277,7 @@
       <c r="R414" s="2"/>
       <c r="S414" s="2"/>
     </row>
-    <row r="415" spans="1:19" ht="13.2">
+    <row r="415" spans="1:19" ht="12.75">
       <c r="A415" s="2"/>
       <c r="B415" s="2"/>
       <c r="C415" s="2"/>
@@ -12295,7 +12298,7 @@
       <c r="R415" s="2"/>
       <c r="S415" s="2"/>
     </row>
-    <row r="416" spans="1:19" ht="13.2">
+    <row r="416" spans="1:19" ht="12.75">
       <c r="A416" s="2"/>
       <c r="B416" s="2"/>
       <c r="C416" s="2"/>
@@ -12316,7 +12319,7 @@
       <c r="R416" s="2"/>
       <c r="S416" s="2"/>
     </row>
-    <row r="417" spans="1:19" ht="13.2">
+    <row r="417" spans="1:19" ht="12.75">
       <c r="A417" s="2"/>
       <c r="B417" s="2"/>
       <c r="C417" s="2"/>
@@ -12337,7 +12340,7 @@
       <c r="R417" s="2"/>
       <c r="S417" s="2"/>
     </row>
-    <row r="418" spans="1:19" ht="13.2">
+    <row r="418" spans="1:19" ht="12.75">
       <c r="A418" s="2"/>
       <c r="B418" s="2"/>
       <c r="C418" s="2"/>
@@ -12358,7 +12361,7 @@
       <c r="R418" s="2"/>
       <c r="S418" s="2"/>
     </row>
-    <row r="419" spans="1:19" ht="13.2">
+    <row r="419" spans="1:19" ht="12.75">
       <c r="A419" s="2"/>
       <c r="B419" s="2"/>
       <c r="C419" s="2"/>
@@ -12379,7 +12382,7 @@
       <c r="R419" s="2"/>
       <c r="S419" s="2"/>
     </row>
-    <row r="420" spans="1:19" ht="13.2">
+    <row r="420" spans="1:19" ht="12.75">
       <c r="A420" s="2"/>
       <c r="B420" s="2"/>
       <c r="C420" s="2"/>
@@ -12400,7 +12403,7 @@
       <c r="R420" s="2"/>
       <c r="S420" s="2"/>
     </row>
-    <row r="421" spans="1:19" ht="13.2">
+    <row r="421" spans="1:19" ht="12.75">
       <c r="A421" s="2"/>
       <c r="B421" s="2"/>
       <c r="C421" s="2"/>
@@ -12421,7 +12424,7 @@
       <c r="R421" s="2"/>
       <c r="S421" s="2"/>
     </row>
-    <row r="422" spans="1:19" ht="13.2">
+    <row r="422" spans="1:19" ht="12.75">
       <c r="A422" s="2"/>
       <c r="B422" s="2"/>
       <c r="C422" s="2"/>
@@ -12442,7 +12445,7 @@
       <c r="R422" s="2"/>
       <c r="S422" s="2"/>
     </row>
-    <row r="423" spans="1:19" ht="13.2">
+    <row r="423" spans="1:19" ht="12.75">
       <c r="A423" s="2"/>
       <c r="B423" s="2"/>
       <c r="C423" s="2"/>
@@ -12463,7 +12466,7 @@
       <c r="R423" s="2"/>
       <c r="S423" s="2"/>
     </row>
-    <row r="424" spans="1:19" ht="13.2">
+    <row r="424" spans="1:19" ht="12.75">
       <c r="A424" s="2"/>
       <c r="B424" s="2"/>
       <c r="C424" s="2"/>
@@ -12484,7 +12487,7 @@
       <c r="R424" s="2"/>
       <c r="S424" s="2"/>
     </row>
-    <row r="425" spans="1:19" ht="13.2">
+    <row r="425" spans="1:19" ht="12.75">
       <c r="A425" s="2"/>
       <c r="B425" s="2"/>
       <c r="C425" s="2"/>
@@ -12505,7 +12508,7 @@
       <c r="R425" s="2"/>
       <c r="S425" s="2"/>
     </row>
-    <row r="426" spans="1:19" ht="13.2">
+    <row r="426" spans="1:19" ht="12.75">
       <c r="A426" s="2"/>
       <c r="B426" s="2"/>
       <c r="C426" s="2"/>
@@ -12526,7 +12529,7 @@
       <c r="R426" s="2"/>
       <c r="S426" s="2"/>
     </row>
-    <row r="427" spans="1:19" ht="13.2">
+    <row r="427" spans="1:19" ht="12.75">
       <c r="A427" s="2"/>
       <c r="B427" s="2"/>
       <c r="C427" s="2"/>
@@ -12547,7 +12550,7 @@
       <c r="R427" s="2"/>
       <c r="S427" s="2"/>
     </row>
-    <row r="428" spans="1:19" ht="13.2">
+    <row r="428" spans="1:19" ht="12.75">
       <c r="A428" s="2"/>
       <c r="B428" s="2"/>
       <c r="C428" s="2"/>
@@ -12568,7 +12571,7 @@
       <c r="R428" s="2"/>
       <c r="S428" s="2"/>
     </row>
-    <row r="429" spans="1:19" ht="13.2">
+    <row r="429" spans="1:19" ht="12.75">
       <c r="A429" s="2"/>
       <c r="B429" s="2"/>
       <c r="C429" s="2"/>
@@ -12589,7 +12592,7 @@
       <c r="R429" s="2"/>
       <c r="S429" s="2"/>
     </row>
-    <row r="430" spans="1:19" ht="13.2">
+    <row r="430" spans="1:19" ht="12.75">
       <c r="A430" s="2"/>
       <c r="B430" s="2"/>
       <c r="C430" s="2"/>
@@ -12610,7 +12613,7 @@
       <c r="R430" s="2"/>
       <c r="S430" s="2"/>
     </row>
-    <row r="431" spans="1:19" ht="13.2">
+    <row r="431" spans="1:19" ht="12.75">
       <c r="A431" s="2"/>
       <c r="B431" s="2"/>
       <c r="C431" s="2"/>
@@ -12631,7 +12634,7 @@
       <c r="R431" s="2"/>
       <c r="S431" s="2"/>
     </row>
-    <row r="432" spans="1:19" ht="13.2">
+    <row r="432" spans="1:19" ht="12.75">
       <c r="A432" s="2"/>
       <c r="B432" s="2"/>
       <c r="C432" s="2"/>
@@ -12652,7 +12655,7 @@
       <c r="R432" s="2"/>
       <c r="S432" s="2"/>
     </row>
-    <row r="433" spans="1:19" ht="13.2">
+    <row r="433" spans="1:19" ht="12.75">
       <c r="A433" s="2"/>
       <c r="B433" s="2"/>
       <c r="C433" s="2"/>
@@ -12673,7 +12676,7 @@
       <c r="R433" s="2"/>
       <c r="S433" s="2"/>
     </row>
-    <row r="434" spans="1:19" ht="13.2">
+    <row r="434" spans="1:19" ht="12.75">
       <c r="A434" s="2"/>
       <c r="B434" s="2"/>
       <c r="C434" s="2"/>
@@ -12694,7 +12697,7 @@
       <c r="R434" s="2"/>
       <c r="S434" s="2"/>
     </row>
-    <row r="435" spans="1:19" ht="13.2">
+    <row r="435" spans="1:19" ht="12.75">
       <c r="A435" s="2"/>
       <c r="B435" s="2"/>
       <c r="C435" s="2"/>
@@ -12715,7 +12718,7 @@
       <c r="R435" s="2"/>
       <c r="S435" s="2"/>
     </row>
-    <row r="436" spans="1:19" ht="13.2">
+    <row r="436" spans="1:19" ht="12.75">
       <c r="A436" s="2"/>
       <c r="B436" s="2"/>
       <c r="C436" s="2"/>
@@ -12736,7 +12739,7 @@
       <c r="R436" s="2"/>
       <c r="S436" s="2"/>
     </row>
-    <row r="437" spans="1:19" ht="13.2">
+    <row r="437" spans="1:19" ht="12.75">
       <c r="A437" s="2"/>
       <c r="B437" s="2"/>
       <c r="C437" s="2"/>
@@ -12757,7 +12760,7 @@
       <c r="R437" s="2"/>
       <c r="S437" s="2"/>
     </row>
-    <row r="438" spans="1:19" ht="13.2">
+    <row r="438" spans="1:19" ht="12.75">
       <c r="A438" s="2"/>
       <c r="B438" s="2"/>
       <c r="C438" s="2"/>
@@ -12778,7 +12781,7 @@
       <c r="R438" s="2"/>
       <c r="S438" s="2"/>
     </row>
-    <row r="439" spans="1:19" ht="13.2">
+    <row r="439" spans="1:19" ht="12.75">
       <c r="A439" s="2"/>
       <c r="B439" s="2"/>
       <c r="C439" s="2"/>
@@ -12799,7 +12802,7 @@
       <c r="R439" s="2"/>
       <c r="S439" s="2"/>
     </row>
-    <row r="440" spans="1:19" ht="13.2">
+    <row r="440" spans="1:19" ht="12.75">
       <c r="A440" s="2"/>
       <c r="B440" s="2"/>
       <c r="C440" s="2"/>
@@ -12820,7 +12823,7 @@
       <c r="R440" s="2"/>
       <c r="S440" s="2"/>
     </row>
-    <row r="441" spans="1:19" ht="13.2">
+    <row r="441" spans="1:19" ht="12.75">
       <c r="A441" s="2"/>
       <c r="B441" s="2"/>
       <c r="C441" s="2"/>
@@ -12841,7 +12844,7 @@
       <c r="R441" s="2"/>
       <c r="S441" s="2"/>
     </row>
-    <row r="442" spans="1:19" ht="13.2">
+    <row r="442" spans="1:19" ht="12.75">
       <c r="A442" s="2"/>
       <c r="B442" s="2"/>
       <c r="C442" s="2"/>
@@ -12862,7 +12865,7 @@
       <c r="R442" s="2"/>
       <c r="S442" s="2"/>
     </row>
-    <row r="443" spans="1:19" ht="13.2">
+    <row r="443" spans="1:19" ht="12.75">
       <c r="A443" s="2"/>
       <c r="B443" s="2"/>
       <c r="C443" s="2"/>
@@ -12883,7 +12886,7 @@
       <c r="R443" s="2"/>
       <c r="S443" s="2"/>
     </row>
-    <row r="444" spans="1:19" ht="13.2">
+    <row r="444" spans="1:19" ht="12.75">
       <c r="A444" s="2"/>
       <c r="B444" s="2"/>
       <c r="C444" s="2"/>
@@ -12904,7 +12907,7 @@
       <c r="R444" s="2"/>
       <c r="S444" s="2"/>
     </row>
-    <row r="445" spans="1:19" ht="13.2">
+    <row r="445" spans="1:19" ht="12.75">
       <c r="A445" s="2"/>
       <c r="B445" s="2"/>
       <c r="C445" s="2"/>
@@ -12925,7 +12928,7 @@
       <c r="R445" s="2"/>
       <c r="S445" s="2"/>
     </row>
-    <row r="446" spans="1:19" ht="13.2">
+    <row r="446" spans="1:19" ht="12.75">
       <c r="A446" s="2"/>
       <c r="B446" s="2"/>
       <c r="C446" s="2"/>
@@ -12946,7 +12949,7 @@
       <c r="R446" s="2"/>
       <c r="S446" s="2"/>
     </row>
-    <row r="447" spans="1:19" ht="13.2">
+    <row r="447" spans="1:19" ht="12.75">
       <c r="A447" s="2"/>
       <c r="B447" s="2"/>
       <c r="C447" s="2"/>
@@ -12967,7 +12970,7 @@
       <c r="R447" s="2"/>
       <c r="S447" s="2"/>
     </row>
-    <row r="448" spans="1:19" ht="13.2">
+    <row r="448" spans="1:19" ht="12.75">
       <c r="A448" s="2"/>
       <c r="B448" s="2"/>
       <c r="C448" s="2"/>
@@ -12988,7 +12991,7 @@
       <c r="R448" s="2"/>
       <c r="S448" s="2"/>
     </row>
-    <row r="449" spans="1:19" ht="13.2">
+    <row r="449" spans="1:19" ht="12.75">
       <c r="A449" s="2"/>
       <c r="B449" s="2"/>
       <c r="C449" s="2"/>
@@ -13009,7 +13012,7 @@
       <c r="R449" s="2"/>
       <c r="S449" s="2"/>
     </row>
-    <row r="450" spans="1:19" ht="13.2">
+    <row r="450" spans="1:19" ht="12.75">
       <c r="A450" s="2"/>
       <c r="B450" s="2"/>
       <c r="C450" s="2"/>
@@ -13030,7 +13033,7 @@
       <c r="R450" s="2"/>
       <c r="S450" s="2"/>
     </row>
-    <row r="451" spans="1:19" ht="13.2">
+    <row r="451" spans="1:19" ht="12.75">
       <c r="A451" s="2"/>
       <c r="B451" s="2"/>
       <c r="C451" s="2"/>
@@ -13051,7 +13054,7 @@
       <c r="R451" s="2"/>
       <c r="S451" s="2"/>
     </row>
-    <row r="452" spans="1:19" ht="13.2">
+    <row r="452" spans="1:19" ht="12.75">
       <c r="A452" s="2"/>
       <c r="B452" s="2"/>
       <c r="C452" s="2"/>
@@ -13072,7 +13075,7 @@
       <c r="R452" s="2"/>
       <c r="S452" s="2"/>
     </row>
-    <row r="453" spans="1:19" ht="13.2">
+    <row r="453" spans="1:19" ht="12.75">
       <c r="A453" s="2"/>
       <c r="B453" s="2"/>
       <c r="C453" s="2"/>
@@ -13093,7 +13096,7 @@
       <c r="R453" s="2"/>
       <c r="S453" s="2"/>
     </row>
-    <row r="454" spans="1:19" ht="13.2">
+    <row r="454" spans="1:19" ht="12.75">
       <c r="A454" s="2"/>
       <c r="B454" s="2"/>
       <c r="C454" s="2"/>
@@ -13114,7 +13117,7 @@
       <c r="R454" s="2"/>
       <c r="S454" s="2"/>
     </row>
-    <row r="455" spans="1:19" ht="13.2">
+    <row r="455" spans="1:19" ht="12.75">
       <c r="A455" s="2"/>
       <c r="B455" s="2"/>
       <c r="C455" s="2"/>
@@ -13135,7 +13138,7 @@
       <c r="R455" s="2"/>
       <c r="S455" s="2"/>
     </row>
-    <row r="456" spans="1:19" ht="13.2">
+    <row r="456" spans="1:19" ht="12.75">
       <c r="A456" s="2"/>
       <c r="B456" s="2"/>
       <c r="C456" s="2"/>
@@ -13156,7 +13159,7 @@
       <c r="R456" s="2"/>
       <c r="S456" s="2"/>
     </row>
-    <row r="457" spans="1:19" ht="13.2">
+    <row r="457" spans="1:19" ht="12.75">
       <c r="A457" s="2"/>
       <c r="B457" s="2"/>
       <c r="C457" s="2"/>
@@ -13177,7 +13180,7 @@
       <c r="R457" s="2"/>
       <c r="S457" s="2"/>
     </row>
-    <row r="458" spans="1:19" ht="13.2">
+    <row r="458" spans="1:19" ht="12.75">
       <c r="A458" s="2"/>
       <c r="B458" s="2"/>
       <c r="C458" s="2"/>
@@ -13198,7 +13201,7 @@
       <c r="R458" s="2"/>
       <c r="S458" s="2"/>
     </row>
-    <row r="459" spans="1:19" ht="13.2">
+    <row r="459" spans="1:19" ht="12.75">
       <c r="A459" s="2"/>
       <c r="B459" s="2"/>
       <c r="C459" s="2"/>
@@ -13219,7 +13222,7 @@
       <c r="R459" s="2"/>
       <c r="S459" s="2"/>
     </row>
-    <row r="460" spans="1:19" ht="13.2">
+    <row r="460" spans="1:19" ht="12.75">
       <c r="A460" s="2"/>
       <c r="B460" s="2"/>
       <c r="C460" s="2"/>
@@ -13240,7 +13243,7 @@
       <c r="R460" s="2"/>
       <c r="S460" s="2"/>
     </row>
-    <row r="461" spans="1:19" ht="13.2">
+    <row r="461" spans="1:19" ht="12.75">
       <c r="A461" s="2"/>
       <c r="B461" s="2"/>
       <c r="C461" s="2"/>
@@ -13261,7 +13264,7 @@
       <c r="R461" s="2"/>
       <c r="S461" s="2"/>
     </row>
-    <row r="462" spans="1:19" ht="13.2">
+    <row r="462" spans="1:19" ht="12.75">
       <c r="A462" s="2"/>
       <c r="B462" s="2"/>
       <c r="C462" s="2"/>
@@ -13282,7 +13285,7 @@
       <c r="R462" s="2"/>
       <c r="S462" s="2"/>
     </row>
-    <row r="463" spans="1:19" ht="13.2">
+    <row r="463" spans="1:19" ht="12.75">
       <c r="A463" s="2"/>
       <c r="B463" s="2"/>
       <c r="C463" s="2"/>
@@ -13303,7 +13306,7 @@
       <c r="R463" s="2"/>
       <c r="S463" s="2"/>
     </row>
-    <row r="464" spans="1:19" ht="13.2">
+    <row r="464" spans="1:19" ht="12.75">
       <c r="A464" s="2"/>
       <c r="B464" s="2"/>
       <c r="C464" s="2"/>
@@ -13324,7 +13327,7 @@
       <c r="R464" s="2"/>
       <c r="S464" s="2"/>
     </row>
-    <row r="465" spans="1:19" ht="13.2">
+    <row r="465" spans="1:19" ht="12.75">
       <c r="A465" s="2"/>
       <c r="B465" s="2"/>
       <c r="C465" s="2"/>
@@ -13345,7 +13348,7 @@
       <c r="R465" s="2"/>
       <c r="S465" s="2"/>
     </row>
-    <row r="466" spans="1:19" ht="13.2">
+    <row r="466" spans="1:19" ht="12.75">
       <c r="A466" s="2"/>
       <c r="B466" s="2"/>
       <c r="C466" s="2"/>
@@ -13366,7 +13369,7 @@
       <c r="R466" s="2"/>
       <c r="S466" s="2"/>
     </row>
-    <row r="467" spans="1:19" ht="13.2">
+    <row r="467" spans="1:19" ht="12.75">
       <c r="A467" s="2"/>
       <c r="B467" s="2"/>
       <c r="C467" s="2"/>
@@ -13387,7 +13390,7 @@
       <c r="R467" s="2"/>
       <c r="S467" s="2"/>
     </row>
-    <row r="468" spans="1:19" ht="13.2">
+    <row r="468" spans="1:19" ht="12.75">
       <c r="A468" s="2"/>
       <c r="B468" s="2"/>
       <c r="C468" s="2"/>
@@ -13408,7 +13411,7 @@
       <c r="R468" s="2"/>
       <c r="S468" s="2"/>
     </row>
-    <row r="469" spans="1:19" ht="13.2">
+    <row r="469" spans="1:19" ht="12.75">
       <c r="A469" s="2"/>
       <c r="B469" s="2"/>
       <c r="C469" s="2"/>
@@ -13429,7 +13432,7 @@
       <c r="R469" s="2"/>
       <c r="S469" s="2"/>
     </row>
-    <row r="470" spans="1:19" ht="13.2">
+    <row r="470" spans="1:19" ht="12.75">
       <c r="A470" s="2"/>
       <c r="B470" s="2"/>
       <c r="C470" s="2"/>
@@ -13450,7 +13453,7 @@
       <c r="R470" s="2"/>
       <c r="S470" s="2"/>
     </row>
-    <row r="471" spans="1:19" ht="13.2">
+    <row r="471" spans="1:19" ht="12.75">
       <c r="A471" s="2"/>
       <c r="B471" s="2"/>
       <c r="C471" s="2"/>
@@ -13471,7 +13474,7 @@
       <c r="R471" s="2"/>
       <c r="S471" s="2"/>
     </row>
-    <row r="472" spans="1:19" ht="13.2">
+    <row r="472" spans="1:19" ht="12.75">
       <c r="A472" s="2"/>
       <c r="B472" s="2"/>
       <c r="C472" s="2"/>
@@ -13492,7 +13495,7 @@
       <c r="R472" s="2"/>
       <c r="S472" s="2"/>
     </row>
-    <row r="473" spans="1:19" ht="13.2">
+    <row r="473" spans="1:19" ht="12.75">
       <c r="A473" s="2"/>
       <c r="B473" s="2"/>
       <c r="C473" s="2"/>
@@ -13513,7 +13516,7 @@
       <c r="R473" s="2"/>
       <c r="S473" s="2"/>
     </row>
-    <row r="474" spans="1:19" ht="13.2">
+    <row r="474" spans="1:19" ht="12.75">
       <c r="A474" s="2"/>
       <c r="B474" s="2"/>
       <c r="C474" s="2"/>
@@ -13534,7 +13537,7 @@
       <c r="R474" s="2"/>
       <c r="S474" s="2"/>
     </row>
-    <row r="475" spans="1:19" ht="13.2">
+    <row r="475" spans="1:19" ht="12.75">
       <c r="A475" s="2"/>
       <c r="B475" s="2"/>
       <c r="C475" s="2"/>
@@ -13555,7 +13558,7 @@
       <c r="R475" s="2"/>
       <c r="S475" s="2"/>
     </row>
-    <row r="476" spans="1:19" ht="13.2">
+    <row r="476" spans="1:19" ht="12.75">
       <c r="A476" s="2"/>
       <c r="B476" s="2"/>
       <c r="C476" s="2"/>
@@ -13576,7 +13579,7 @@
       <c r="R476" s="2"/>
       <c r="S476" s="2"/>
     </row>
-    <row r="477" spans="1:19" ht="13.2">
+    <row r="477" spans="1:19" ht="12.75">
       <c r="A477" s="2"/>
       <c r="B477" s="2"/>
       <c r="C477" s="2"/>
@@ -13597,7 +13600,7 @@
       <c r="R477" s="2"/>
       <c r="S477" s="2"/>
     </row>
-    <row r="478" spans="1:19" ht="13.2">
+    <row r="478" spans="1:19" ht="12.75">
       <c r="A478" s="2"/>
       <c r="B478" s="2"/>
       <c r="C478" s="2"/>
@@ -13618,7 +13621,7 @@
       <c r="R478" s="2"/>
       <c r="S478" s="2"/>
     </row>
-    <row r="479" spans="1:19" ht="13.2">
+    <row r="479" spans="1:19" ht="12.75">
       <c r="A479" s="2"/>
       <c r="B479" s="2"/>
       <c r="C479" s="2"/>
@@ -13639,7 +13642,7 @@
       <c r="R479" s="2"/>
       <c r="S479" s="2"/>
     </row>
-    <row r="480" spans="1:19" ht="13.2">
+    <row r="480" spans="1:19" ht="12.75">
       <c r="A480" s="2"/>
       <c r="B480" s="2"/>
       <c r="C480" s="2"/>
@@ -13660,7 +13663,7 @@
       <c r="R480" s="2"/>
       <c r="S480" s="2"/>
     </row>
-    <row r="481" spans="1:19" ht="13.2">
+    <row r="481" spans="1:19" ht="12.75">
       <c r="A481" s="2"/>
       <c r="B481" s="2"/>
       <c r="C481" s="2"/>
@@ -13681,7 +13684,7 @@
       <c r="R481" s="2"/>
       <c r="S481" s="2"/>
     </row>
-    <row r="482" spans="1:19" ht="13.2">
+    <row r="482" spans="1:19" ht="12.75">
       <c r="A482" s="2"/>
       <c r="B482" s="2"/>
       <c r="C482" s="2"/>
@@ -13702,7 +13705,7 @@
       <c r="R482" s="2"/>
       <c r="S482" s="2"/>
     </row>
-    <row r="483" spans="1:19" ht="13.2">
+    <row r="483" spans="1:19" ht="12.75">
       <c r="A483" s="2"/>
       <c r="B483" s="2"/>
       <c r="C483" s="2"/>
@@ -13723,7 +13726,7 @@
       <c r="R483" s="2"/>
       <c r="S483" s="2"/>
     </row>
-    <row r="484" spans="1:19" ht="13.2">
+    <row r="484" spans="1:19" ht="12.75">
       <c r="A484" s="2"/>
       <c r="B484" s="2"/>
       <c r="C484" s="2"/>
@@ -13744,7 +13747,7 @@
       <c r="R484" s="2"/>
       <c r="S484" s="2"/>
     </row>
-    <row r="485" spans="1:19" ht="13.2">
+    <row r="485" spans="1:19" ht="12.75">
       <c r="A485" s="2"/>
       <c r="B485" s="2"/>
       <c r="C485" s="2"/>
@@ -13765,7 +13768,7 @@
       <c r="R485" s="2"/>
       <c r="S485" s="2"/>
     </row>
-    <row r="486" spans="1:19" ht="13.2">
+    <row r="486" spans="1:19" ht="12.75">
       <c r="A486" s="2"/>
       <c r="B486" s="2"/>
       <c r="C486" s="2"/>
@@ -13786,7 +13789,7 @@
       <c r="R486" s="2"/>
       <c r="S486" s="2"/>
     </row>
-    <row r="487" spans="1:19" ht="13.2">
+    <row r="487" spans="1:19" ht="12.75">
       <c r="A487" s="2"/>
       <c r="B487" s="2"/>
       <c r="C487" s="2"/>
@@ -13807,7 +13810,7 @@
       <c r="R487" s="2"/>
       <c r="S487" s="2"/>
     </row>
-    <row r="488" spans="1:19" ht="13.2">
+    <row r="488" spans="1:19" ht="12.75">
       <c r="A488" s="2"/>
       <c r="B488" s="2"/>
       <c r="C488" s="2"/>
@@ -13828,7 +13831,7 @@
       <c r="R488" s="2"/>
       <c r="S488" s="2"/>
     </row>
-    <row r="489" spans="1:19" ht="13.2">
+    <row r="489" spans="1:19" ht="12.75">
       <c r="A489" s="2"/>
       <c r="B489" s="2"/>
       <c r="C489" s="2"/>
@@ -13849,7 +13852,7 @@
       <c r="R489" s="2"/>
       <c r="S489" s="2"/>
     </row>
-    <row r="490" spans="1:19" ht="13.2">
+    <row r="490" spans="1:19" ht="12.75">
       <c r="A490" s="2"/>
       <c r="B490" s="2"/>
       <c r="C490" s="2"/>
@@ -13870,7 +13873,7 @@
       <c r="R490" s="2"/>
       <c r="S490" s="2"/>
     </row>
-    <row r="491" spans="1:19" ht="13.2">
+    <row r="491" spans="1:19" ht="12.75">
       <c r="A491" s="2"/>
       <c r="B491" s="2"/>
       <c r="C491" s="2"/>
@@ -13891,7 +13894,7 @@
       <c r="R491" s="2"/>
       <c r="S491" s="2"/>
     </row>
-    <row r="492" spans="1:19" ht="13.2">
+    <row r="492" spans="1:19" ht="12.75">
       <c r="A492" s="2"/>
       <c r="B492" s="2"/>
       <c r="C492" s="2"/>
@@ -13912,7 +13915,7 @@
       <c r="R492" s="2"/>
       <c r="S492" s="2"/>
     </row>
-    <row r="493" spans="1:19" ht="13.2">
+    <row r="493" spans="1:19" ht="12.75">
       <c r="A493" s="2"/>
       <c r="B493" s="2"/>
       <c r="C493" s="2"/>
@@ -13933,7 +13936,7 @@
       <c r="R493" s="2"/>
       <c r="S493" s="2"/>
     </row>
-    <row r="494" spans="1:19" ht="13.2">
+    <row r="494" spans="1:19" ht="12.75">
       <c r="A494" s="2"/>
       <c r="B494" s="2"/>
       <c r="C494" s="2"/>
@@ -13954,7 +13957,7 @@
       <c r="R494" s="2"/>
       <c r="S494" s="2"/>
     </row>
-    <row r="495" spans="1:19" ht="13.2">
+    <row r="495" spans="1:19" ht="12.75">
       <c r="A495" s="2"/>
       <c r="B495" s="2"/>
       <c r="C495" s="2"/>
@@ -13975,7 +13978,7 @@
       <c r="R495" s="2"/>
       <c r="S495" s="2"/>
     </row>
-    <row r="496" spans="1:19" ht="13.2">
+    <row r="496" spans="1:19" ht="12.75">
       <c r="A496" s="2"/>
       <c r="B496" s="2"/>
       <c r="C496" s="2"/>
@@ -13996,7 +13999,7 @@
       <c r="R496" s="2"/>
       <c r="S496" s="2"/>
     </row>
-    <row r="497" spans="1:19" ht="13.2">
+    <row r="497" spans="1:19" ht="12.75">
       <c r="A497" s="2"/>
       <c r="B497" s="2"/>
       <c r="C497" s="2"/>
@@ -14017,7 +14020,7 @@
       <c r="R497" s="2"/>
       <c r="S497" s="2"/>
     </row>
-    <row r="498" spans="1:19" ht="13.2">
+    <row r="498" spans="1:19" ht="12.75">
       <c r="A498" s="2"/>
       <c r="B498" s="2"/>
       <c r="C498" s="2"/>
@@ -14038,7 +14041,7 @@
       <c r="R498" s="2"/>
       <c r="S498" s="2"/>
     </row>
-    <row r="499" spans="1:19" ht="13.2">
+    <row r="499" spans="1:19" ht="12.75">
       <c r="A499" s="2"/>
       <c r="B499" s="2"/>
       <c r="C499" s="2"/>
@@ -14059,7 +14062,7 @@
       <c r="R499" s="2"/>
       <c r="S499" s="2"/>
     </row>
-    <row r="500" spans="1:19" ht="13.2">
+    <row r="500" spans="1:19" ht="12.75">
       <c r="A500" s="2"/>
       <c r="B500" s="2"/>
       <c r="C500" s="2"/>
@@ -14080,7 +14083,7 @@
       <c r="R500" s="2"/>
       <c r="S500" s="2"/>
     </row>
-    <row r="501" spans="1:19" ht="13.2">
+    <row r="501" spans="1:19" ht="12.75">
       <c r="A501" s="2"/>
       <c r="B501" s="2"/>
       <c r="C501" s="2"/>
@@ -14101,7 +14104,7 @@
       <c r="R501" s="2"/>
       <c r="S501" s="2"/>
     </row>
-    <row r="502" spans="1:19" ht="13.2">
+    <row r="502" spans="1:19" ht="12.75">
       <c r="A502" s="2"/>
       <c r="B502" s="2"/>
       <c r="C502" s="2"/>
@@ -14122,7 +14125,7 @@
       <c r="R502" s="2"/>
       <c r="S502" s="2"/>
     </row>
-    <row r="503" spans="1:19" ht="13.2">
+    <row r="503" spans="1:19" ht="12.75">
       <c r="A503" s="2"/>
       <c r="B503" s="2"/>
       <c r="C503" s="2"/>
@@ -14143,7 +14146,7 @@
       <c r="R503" s="2"/>
       <c r="S503" s="2"/>
     </row>
-    <row r="504" spans="1:19" ht="13.2">
+    <row r="504" spans="1:19" ht="12.75">
       <c r="A504" s="2"/>
       <c r="B504" s="2"/>
       <c r="C504" s="2"/>
@@ -14164,7 +14167,7 @@
       <c r="R504" s="2"/>
       <c r="S504" s="2"/>
     </row>
-    <row r="505" spans="1:19" ht="13.2">
+    <row r="505" spans="1:19" ht="12.75">
       <c r="A505" s="2"/>
       <c r="B505" s="2"/>
       <c r="C505" s="2"/>
@@ -14185,7 +14188,7 @@
       <c r="R505" s="2"/>
       <c r="S505" s="2"/>
     </row>
-    <row r="506" spans="1:19" ht="13.2">
+    <row r="506" spans="1:19" ht="12.75">
       <c r="A506" s="2"/>
       <c r="B506" s="2"/>
       <c r="C506" s="2"/>
@@ -14206,7 +14209,7 @@
       <c r="R506" s="2"/>
       <c r="S506" s="2"/>
     </row>
-    <row r="507" spans="1:19" ht="13.2">
+    <row r="507" spans="1:19" ht="12.75">
       <c r="A507" s="2"/>
       <c r="B507" s="2"/>
       <c r="C507" s="2"/>
@@ -14227,7 +14230,7 @@
       <c r="R507" s="2"/>
       <c r="S507" s="2"/>
     </row>
-    <row r="508" spans="1:19" ht="13.2">
+    <row r="508" spans="1:19" ht="12.75">
       <c r="A508" s="2"/>
       <c r="B508" s="2"/>
       <c r="C508" s="2"/>
@@ -14248,7 +14251,7 @@
       <c r="R508" s="2"/>
       <c r="S508" s="2"/>
     </row>
-    <row r="509" spans="1:19" ht="13.2">
+    <row r="509" spans="1:19" ht="12.75">
       <c r="A509" s="2"/>
       <c r="B509" s="2"/>
       <c r="C509" s="2"/>
@@ -14269,7 +14272,7 @@
       <c r="R509" s="2"/>
       <c r="S509" s="2"/>
     </row>
-    <row r="510" spans="1:19" ht="13.2">
+    <row r="510" spans="1:19" ht="12.75">
       <c r="A510" s="2"/>
       <c r="B510" s="2"/>
       <c r="C510" s="2"/>
@@ -14290,7 +14293,7 @@
       <c r="R510" s="2"/>
       <c r="S510" s="2"/>
     </row>
-    <row r="511" spans="1:19" ht="13.2">
+    <row r="511" spans="1:19" ht="12.75">
       <c r="A511" s="2"/>
       <c r="B511" s="2"/>
       <c r="C511" s="2"/>
@@ -14311,7 +14314,7 @@
       <c r="R511" s="2"/>
       <c r="S511" s="2"/>
     </row>
-    <row r="512" spans="1:19" ht="13.2">
+    <row r="512" spans="1:19" ht="12.75">
       <c r="A512" s="2"/>
       <c r="B512" s="2"/>
       <c r="C512" s="2"/>
@@ -14332,7 +14335,7 @@
       <c r="R512" s="2"/>
       <c r="S512" s="2"/>
     </row>
-    <row r="513" spans="1:19" ht="13.2">
+    <row r="513" spans="1:19" ht="12.75">
       <c r="A513" s="2"/>
       <c r="B513" s="2"/>
       <c r="C513" s="2"/>
@@ -14353,7 +14356,7 @@
       <c r="R513" s="2"/>
       <c r="S513" s="2"/>
     </row>
-    <row r="514" spans="1:19" ht="13.2">
+    <row r="514" spans="1:19" ht="12.75">
       <c r="A514" s="2"/>
       <c r="B514" s="2"/>
       <c r="C514" s="2"/>
@@ -14374,7 +14377,7 @@
       <c r="R514" s="2"/>
       <c r="S514" s="2"/>
     </row>
-    <row r="515" spans="1:19" ht="13.2">
+    <row r="515" spans="1:19" ht="12.75">
       <c r="A515" s="2"/>
       <c r="B515" s="2"/>
       <c r="C515" s="2"/>
@@ -14395,7 +14398,7 @@
       <c r="R515" s="2"/>
       <c r="S515" s="2"/>
     </row>
-    <row r="516" spans="1:19" ht="13.2">
+    <row r="516" spans="1:19" ht="12.75">
       <c r="A516" s="2"/>
       <c r="B516" s="2"/>
       <c r="C516" s="2"/>
@@ -14416,7 +14419,7 @@
       <c r="R516" s="2"/>
       <c r="S516" s="2"/>
     </row>
-    <row r="517" spans="1:19" ht="13.2">
+    <row r="517" spans="1:19" ht="12.75">
       <c r="A517" s="2"/>
       <c r="B517" s="2"/>
       <c r="C517" s="2"/>
@@ -14437,7 +14440,7 @@
       <c r="R517" s="2"/>
       <c r="S517" s="2"/>
     </row>
-    <row r="518" spans="1:19" ht="13.2">
+    <row r="518" spans="1:19" ht="12.75">
       <c r="A518" s="2"/>
       <c r="B518" s="2"/>
       <c r="C518" s="2"/>
@@ -14458,7 +14461,7 @@
       <c r="R518" s="2"/>
       <c r="S518" s="2"/>
     </row>
-    <row r="519" spans="1:19" ht="13.2">
+    <row r="519" spans="1:19" ht="12.75">
       <c r="A519" s="2"/>
       <c r="B519" s="2"/>
       <c r="C519" s="2"/>
@@ -14479,7 +14482,7 @@
       <c r="R519" s="2"/>
       <c r="S519" s="2"/>
     </row>
-    <row r="520" spans="1:19" ht="13.2">
+    <row r="520" spans="1:19" ht="12.75">
       <c r="A520" s="2"/>
       <c r="B520" s="2"/>
       <c r="C520" s="2"/>
@@ -14500,7 +14503,7 @@
       <c r="R520" s="2"/>
       <c r="S520" s="2"/>
     </row>
-    <row r="521" spans="1:19" ht="13.2">
+    <row r="521" spans="1:19" ht="12.75">
       <c r="A521" s="2"/>
       <c r="B521" s="2"/>
       <c r="C521" s="2"/>
@@ -14521,7 +14524,7 @@
       <c r="R521" s="2"/>
       <c r="S521" s="2"/>
     </row>
-    <row r="522" spans="1:19" ht="13.2">
+    <row r="522" spans="1:19" ht="12.75">
       <c r="A522" s="2"/>
       <c r="B522" s="2"/>
       <c r="C522" s="2"/>
@@ -14542,7 +14545,7 @@
       <c r="R522" s="2"/>
       <c r="S522" s="2"/>
     </row>
-    <row r="523" spans="1:19" ht="13.2">
+    <row r="523" spans="1:19" ht="12.75">
       <c r="A523" s="2"/>
       <c r="B523" s="2"/>
       <c r="C523" s="2"/>
@@ -14563,7 +14566,7 @@
       <c r="R523" s="2"/>
       <c r="S523" s="2"/>
     </row>
-    <row r="524" spans="1:19" ht="13.2">
+    <row r="524" spans="1:19" ht="12.75">
       <c r="A524" s="2"/>
       <c r="B524" s="2"/>
       <c r="C524" s="2"/>
@@ -14584,7 +14587,7 @@
       <c r="R524" s="2"/>
       <c r="S524" s="2"/>
     </row>
-    <row r="525" spans="1:19" ht="13.2">
+    <row r="525" spans="1:19" ht="12.75">
       <c r="A525" s="2"/>
       <c r="B525" s="2"/>
       <c r="C525" s="2"/>
@@ -14605,7 +14608,7 @@
       <c r="R525" s="2"/>
       <c r="S525" s="2"/>
     </row>
-    <row r="526" spans="1:19" ht="13.2">
+    <row r="526" spans="1:19" ht="12.75">
       <c r="A526" s="2"/>
       <c r="B526" s="2"/>
       <c r="C526" s="2"/>
@@ -14626,7 +14629,7 @@
       <c r="R526" s="2"/>
       <c r="S526" s="2"/>
     </row>
-    <row r="527" spans="1:19" ht="13.2">
+    <row r="527" spans="1:19" ht="12.75">
       <c r="A527" s="2"/>
       <c r="B527" s="2"/>
       <c r="C527" s="2"/>
@@ -14647,7 +14650,7 @@
       <c r="R527" s="2"/>
       <c r="S527" s="2"/>
     </row>
-    <row r="528" spans="1:19" ht="13.2">
+    <row r="528" spans="1:19" ht="12.75">
       <c r="A528" s="2"/>
       <c r="B528" s="2"/>
       <c r="C528" s="2"/>
@@ -14668,7 +14671,7 @@
       <c r="R528" s="2"/>
       <c r="S528" s="2"/>
     </row>
-    <row r="529" spans="1:19" ht="13.2">
+    <row r="529" spans="1:19" ht="12.75">
       <c r="A529" s="2"/>
       <c r="B529" s="2"/>
       <c r="C529" s="2"/>
@@ -14689,7 +14692,7 @@
       <c r="R529" s="2"/>
       <c r="S529" s="2"/>
     </row>
-    <row r="530" spans="1:19" ht="13.2">
+    <row r="530" spans="1:19" ht="12.75">
       <c r="A530" s="2"/>
       <c r="B530" s="2"/>
       <c r="C530" s="2"/>
@@ -14710,7 +14713,7 @@
       <c r="R530" s="2"/>
       <c r="S530" s="2"/>
     </row>
-    <row r="531" spans="1:19" ht="13.2">
+    <row r="531" spans="1:19" ht="12.75">
       <c r="A531" s="2"/>
       <c r="B531" s="2"/>
       <c r="C531" s="2"/>
@@ -14731,7 +14734,7 @@
       <c r="R531" s="2"/>
       <c r="S531" s="2"/>
     </row>
-    <row r="532" spans="1:19" ht="13.2">
+    <row r="532" spans="1:19" ht="12.75">
       <c r="A532" s="2"/>
       <c r="B532" s="2"/>
       <c r="C532" s="2"/>
@@ -14752,7 +14755,7 @@
       <c r="R532" s="2"/>
       <c r="S532" s="2"/>
     </row>
-    <row r="533" spans="1:19" ht="13.2">
+    <row r="533" spans="1:19" ht="12.75">
       <c r="A533" s="2"/>
       <c r="B533" s="2"/>
       <c r="C533" s="2"/>
@@ -14773,7 +14776,7 @@
       <c r="R533" s="2"/>
       <c r="S533" s="2"/>
     </row>
-    <row r="534" spans="1:19" ht="13.2">
+    <row r="534" spans="1:19" ht="12.75">
       <c r="A534" s="2"/>
       <c r="B534" s="2"/>
       <c r="C534" s="2"/>
@@ -14794,7 +14797,7 @@
       <c r="R534" s="2"/>
       <c r="S534" s="2"/>
     </row>
-    <row r="535" spans="1:19" ht="13.2">
+    <row r="535" spans="1:19" ht="12.75">
       <c r="A535" s="2"/>
       <c r="B535" s="2"/>
       <c r="C535" s="2"/>
@@ -14815,7 +14818,7 @@
       <c r="R535" s="2"/>
       <c r="S535" s="2"/>
     </row>
-    <row r="536" spans="1:19" ht="13.2">
+    <row r="536" spans="1:19" ht="12.75">
       <c r="A536" s="2"/>
       <c r="B536" s="2"/>
       <c r="C536" s="2"/>
@@ -14836,7 +14839,7 @@
       <c r="R536" s="2"/>
       <c r="S536" s="2"/>
     </row>
-    <row r="537" spans="1:19" ht="13.2">
+    <row r="537" spans="1:19" ht="12.75">
       <c r="A537" s="2"/>
       <c r="B537" s="2"/>
       <c r="C537" s="2"/>
@@ -14857,7 +14860,7 @@
       <c r="R537" s="2"/>
       <c r="S537" s="2"/>
     </row>
-    <row r="538" spans="1:19" ht="13.2">
+    <row r="538" spans="1:19" ht="12.75">
       <c r="A538" s="2"/>
       <c r="B538" s="2"/>
       <c r="C538" s="2"/>
@@ -14878,7 +14881,7 @@
       <c r="R538" s="2"/>
       <c r="S538" s="2"/>
     </row>
-    <row r="539" spans="1:19" ht="13.2">
+    <row r="539" spans="1:19" ht="12.75">
       <c r="A539" s="2"/>
       <c r="B539" s="2"/>
       <c r="C539" s="2"/>
@@ -14899,7 +14902,7 @@
       <c r="R539" s="2"/>
       <c r="S539" s="2"/>
     </row>
-    <row r="540" spans="1:19" ht="13.2">
+    <row r="540" spans="1:19" ht="12.75">
       <c r="A540" s="2"/>
       <c r="B540" s="2"/>
       <c r="C540" s="2"/>
@@ -14920,7 +14923,7 @@
       <c r="R540" s="2"/>
       <c r="S540" s="2"/>
     </row>
-    <row r="541" spans="1:19" ht="13.2">
+    <row r="541" spans="1:19" ht="12.75">
       <c r="A541" s="2"/>
       <c r="B541" s="2"/>
       <c r="C541" s="2"/>
@@ -14941,7 +14944,7 @@
       <c r="R541" s="2"/>
       <c r="S541" s="2"/>
     </row>
-    <row r="542" spans="1:19" ht="13.2">
+    <row r="542" spans="1:19" ht="12.75">
       <c r="A542" s="2"/>
       <c r="B542" s="2"/>
       <c r="C542" s="2"/>
@@ -14962,7 +14965,7 @@
       <c r="R542" s="2"/>
       <c r="S542" s="2"/>
     </row>
-    <row r="543" spans="1:19" ht="13.2">
+    <row r="543" spans="1:19" ht="12.75">
       <c r="A543" s="2"/>
       <c r="B543" s="2"/>
       <c r="C543" s="2"/>
@@ -14983,7 +14986,7 @@
       <c r="R543" s="2"/>
       <c r="S543" s="2"/>
     </row>
-    <row r="544" spans="1:19" ht="13.2">
+    <row r="544" spans="1:19" ht="12.75">
       <c r="A544" s="2"/>
       <c r="B544" s="2"/>
       <c r="C544" s="2"/>
@@ -15004,7 +15007,7 @@
       <c r="R544" s="2"/>
       <c r="S544" s="2"/>
     </row>
-    <row r="545" spans="1:19" ht="13.2">
+    <row r="545" spans="1:19" ht="12.75">
       <c r="A545" s="2"/>
       <c r="B545" s="2"/>
       <c r="C545" s="2"/>
@@ -15025,7 +15028,7 @@
       <c r="R545" s="2"/>
       <c r="S545" s="2"/>
     </row>
-    <row r="546" spans="1:19" ht="13.2">
+    <row r="546" spans="1:19" ht="12.75">
       <c r="A546" s="2"/>
       <c r="B546" s="2"/>
       <c r="C546" s="2"/>
@@ -15046,7 +15049,7 @@
       <c r="R546" s="2"/>
       <c r="S546" s="2"/>
     </row>
-    <row r="547" spans="1:19" ht="13.2">
+    <row r="547" spans="1:19" ht="12.75">
       <c r="A547" s="2"/>
       <c r="B547" s="2"/>
       <c r="C547" s="2"/>
@@ -15067,7 +15070,7 @@
       <c r="R547" s="2"/>
       <c r="S547" s="2"/>
     </row>
-    <row r="548" spans="1:19" ht="13.2">
+    <row r="548" spans="1:19" ht="12.75">
       <c r="A548" s="2"/>
       <c r="B548" s="2"/>
       <c r="C548" s="2"/>
@@ -15088,7 +15091,7 @@
       <c r="R548" s="2"/>
       <c r="S548" s="2"/>
     </row>
-    <row r="549" spans="1:19" ht="13.2">
+    <row r="549" spans="1:19" ht="12.75">
       <c r="A549" s="2"/>
       <c r="B549" s="2"/>
       <c r="C549" s="2"/>
@@ -15109,7 +15112,7 @@
       <c r="R549" s="2"/>
       <c r="S549" s="2"/>
     </row>
-    <row r="550" spans="1:19" ht="13.2">
+    <row r="550" spans="1:19" ht="12.75">
       <c r="A550" s="2"/>
       <c r="B550" s="2"/>
       <c r="C550" s="2"/>
@@ -15130,7 +15133,7 @@
       <c r="R550" s="2"/>
       <c r="S550" s="2"/>
     </row>
-    <row r="551" spans="1:19" ht="13.2">
+    <row r="551" spans="1:19" ht="12.75">
       <c r="A551" s="2"/>
       <c r="B551" s="2"/>
       <c r="C551" s="2"/>
@@ -15151,7 +15154,7 @@
       <c r="R551" s="2"/>
       <c r="S551" s="2"/>
     </row>
-    <row r="552" spans="1:19" ht="13.2">
+    <row r="552" spans="1:19" ht="12.75">
       <c r="A552" s="2"/>
       <c r="B552" s="2"/>
       <c r="C552" s="2"/>
@@ -15172,7 +15175,7 @@
       <c r="R552" s="2"/>
       <c r="S552" s="2"/>
     </row>
-    <row r="553" spans="1:19" ht="13.2">
+    <row r="553" spans="1:19" ht="12.75">
       <c r="A553" s="2"/>
       <c r="B553" s="2"/>
       <c r="C553" s="2"/>
@@ -15193,7 +15196,7 @@
       <c r="R553" s="2"/>
       <c r="S553" s="2"/>
     </row>
-    <row r="554" spans="1:19" ht="13.2">
+    <row r="554" spans="1:19" ht="12.75">
       <c r="A554" s="2"/>
       <c r="B554" s="2"/>
       <c r="C554" s="2"/>
@@ -15214,7 +15217,7 @@
       <c r="R554" s="2"/>
       <c r="S554" s="2"/>
     </row>
-    <row r="555" spans="1:19" ht="13.2">
+    <row r="555" spans="1:19" ht="12.75">
       <c r="A555" s="2"/>
       <c r="B555" s="2"/>
       <c r="C555" s="2"/>
@@ -15235,7 +15238,7 @@
       <c r="R555" s="2"/>
       <c r="S555" s="2"/>
     </row>
-    <row r="556" spans="1:19" ht="13.2">
+    <row r="556" spans="1:19" ht="12.75">
       <c r="A556" s="2"/>
       <c r="B556" s="2"/>
       <c r="C556" s="2"/>
@@ -15256,7 +15259,7 @@
       <c r="R556" s="2"/>
       <c r="S556" s="2"/>
     </row>
-    <row r="557" spans="1:19" ht="13.2">
+    <row r="557" spans="1:19" ht="12.75">
       <c r="A557" s="2"/>
       <c r="B557" s="2"/>
       <c r="C557" s="2"/>
@@ -15277,7 +15280,7 @@
       <c r="R557" s="2"/>
       <c r="S557" s="2"/>
     </row>
-    <row r="558" spans="1:19" ht="13.2">
+    <row r="558" spans="1:19" ht="12.75">
       <c r="A558" s="2"/>
       <c r="B558" s="2"/>
       <c r="C558" s="2"/>
@@ -15298,7 +15301,7 @@
       <c r="R558" s="2"/>
       <c r="S558" s="2"/>
     </row>
-    <row r="559" spans="1:19" ht="13.2">
+    <row r="559" spans="1:19" ht="12.75">
       <c r="A559" s="2"/>
       <c r="B559" s="2"/>
       <c r="C559" s="2"/>
@@ -15319,7 +15322,7 @@
       <c r="R559" s="2"/>
       <c r="S559" s="2"/>
     </row>
-    <row r="560" spans="1:19" ht="13.2">
+    <row r="560" spans="1:19" ht="12.75">
       <c r="A560" s="2"/>
       <c r="B560" s="2"/>
       <c r="C560" s="2"/>
@@ -15340,7 +15343,7 @@
       <c r="R560" s="2"/>
       <c r="S560" s="2"/>
     </row>
-    <row r="561" spans="1:19" ht="13.2">
+    <row r="561" spans="1:19" ht="12.75">
       <c r="A561" s="2"/>
       <c r="B561" s="2"/>
       <c r="C561" s="2"/>
@@ -15361,7 +15364,7 @@
       <c r="R561" s="2"/>
       <c r="S561" s="2"/>
     </row>
-    <row r="562" spans="1:19" ht="13.2">
+    <row r="562" spans="1:19" ht="12.75">
       <c r="A562" s="2"/>
       <c r="B562" s="2"/>
       <c r="C562" s="2"/>
@@ -15382,7 +15385,7 @@
       <c r="R562" s="2"/>
       <c r="S562" s="2"/>
     </row>
-    <row r="563" spans="1:19" ht="13.2">
+    <row r="563" spans="1:19" ht="12.75">
       <c r="A563" s="2"/>
       <c r="B563" s="2"/>
       <c r="C563" s="2"/>
@@ -15403,7 +15406,7 @@
       <c r="R563" s="2"/>
       <c r="S563" s="2"/>
     </row>
-    <row r="564" spans="1:19" ht="13.2">
+    <row r="564" spans="1:19" ht="12.75">
       <c r="A564" s="2"/>
       <c r="B564" s="2"/>
       <c r="C564" s="2"/>
@@ -15424,7 +15427,7 @@
       <c r="R564" s="2"/>
       <c r="S564" s="2"/>
     </row>
-    <row r="565" spans="1:19" ht="13.2">
+    <row r="565" spans="1:19" ht="12.75">
       <c r="A565" s="2"/>
       <c r="B565" s="2"/>
       <c r="C565" s="2"/>
@@ -15445,7 +15448,7 @@
       <c r="R565" s="2"/>
       <c r="S565" s="2"/>
     </row>
-    <row r="566" spans="1:19" ht="13.2">
+    <row r="566" spans="1:19" ht="12.75">
       <c r="A566" s="2"/>
       <c r="B566" s="2"/>
       <c r="C566" s="2"/>
@@ -15466,7 +15469,7 @@
       <c r="R566" s="2"/>
       <c r="S566" s="2"/>
     </row>
-    <row r="567" spans="1:19" ht="13.2">
+    <row r="567" spans="1:19" ht="12.75">
       <c r="A567" s="2"/>
       <c r="B567" s="2"/>
       <c r="C567" s="2"/>
@@ -15487,7 +15490,7 @@
       <c r="R567" s="2"/>
       <c r="S567" s="2"/>
     </row>
-    <row r="568" spans="1:19" ht="13.2">
+    <row r="568" spans="1:19" ht="12.75">
       <c r="A568" s="2"/>
       <c r="B568" s="2"/>
       <c r="C568" s="2"/>
@@ -15508,7 +15511,7 @@
       <c r="R568" s="2"/>
       <c r="S568" s="2"/>
     </row>
-    <row r="569" spans="1:19" ht="13.2">
+    <row r="569" spans="1:19" ht="12.75">
       <c r="A569" s="2"/>
       <c r="B569" s="2"/>
       <c r="C569" s="2"/>
@@ -15529,7 +15532,7 @@
       <c r="R569" s="2"/>
       <c r="S569" s="2"/>
     </row>
-    <row r="570" spans="1:19" ht="13.2">
+    <row r="570" spans="1:19" ht="12.75">
       <c r="A570" s="2"/>
       <c r="B570" s="2"/>
       <c r="C570" s="2"/>
@@ -15550,7 +15553,7 @@
       <c r="R570" s="2"/>
       <c r="S570" s="2"/>
     </row>
-    <row r="571" spans="1:19" ht="13.2">
+    <row r="571" spans="1:19" ht="12.75">
       <c r="A571" s="2"/>
       <c r="B571" s="2"/>
       <c r="C571" s="2"/>
@@ -15571,7 +15574,7 @@
       <c r="R571" s="2"/>
       <c r="S571" s="2"/>
     </row>
-    <row r="572" spans="1:19" ht="13.2">
+    <row r="572" spans="1:19" ht="12.75">
       <c r="A572" s="2"/>
       <c r="B572" s="2"/>
       <c r="C572" s="2"/>
@@ -15592,7 +15595,7 @@
       <c r="R572" s="2"/>
       <c r="S572" s="2"/>
     </row>
-    <row r="573" spans="1:19" ht="13.2">
+    <row r="573" spans="1:19" ht="12.75">
       <c r="A573" s="2"/>
       <c r="B573" s="2"/>
       <c r="C573" s="2"/>
@@ -15613,7 +15616,7 @@
       <c r="R573" s="2"/>
       <c r="S573" s="2"/>
     </row>
-    <row r="574" spans="1:19" ht="13.2">
+    <row r="574" spans="1:19" ht="12.75">
       <c r="A574" s="2"/>
       <c r="B574" s="2"/>
       <c r="C574" s="2"/>
@@ -15634,7 +15637,7 @@
       <c r="R574" s="2"/>
       <c r="S574" s="2"/>
     </row>
-    <row r="575" spans="1:19" ht="13.2">
+    <row r="575" spans="1:19" ht="12.75">
       <c r="A575" s="2"/>
       <c r="B575" s="2"/>
       <c r="C575" s="2"/>
@@ -15655,7 +15658,7 @@
       <c r="R575" s="2"/>
       <c r="S575" s="2"/>
     </row>
-    <row r="576" spans="1:19" ht="13.2">
+    <row r="576" spans="1:19" ht="12.75">
       <c r="A576" s="2"/>
       <c r="B576" s="2"/>
       <c r="C576" s="2"/>
@@ -15676,7 +15679,7 @@
       <c r="R576" s="2"/>
       <c r="S576" s="2"/>
     </row>
-    <row r="577" spans="1:19" ht="13.2">
+    <row r="577" spans="1:19" ht="12.75">
       <c r="A577" s="2"/>
       <c r="B577" s="2"/>
       <c r="C577" s="2"/>
@@ -15697,7 +15700,7 @@
       <c r="R577" s="2"/>
       <c r="S577" s="2"/>
     </row>
-    <row r="578" spans="1:19" ht="13.2">
+    <row r="578" spans="1:19" ht="12.75">
       <c r="A578" s="2"/>
       <c r="B578" s="2"/>
       <c r="C578" s="2"/>
@@ -15718,7 +15721,7 @@
       <c r="R578" s="2"/>
       <c r="S578" s="2"/>
     </row>
-    <row r="579" spans="1:19" ht="13.2">
+    <row r="579" spans="1:19" ht="12.75">
       <c r="A579" s="2"/>
       <c r="B579" s="2"/>
       <c r="C579" s="2"/>
@@ -15739,7 +15742,7 @@
       <c r="R579" s="2"/>
       <c r="S579" s="2"/>
     </row>
-    <row r="580" spans="1:19" ht="13.2">
+    <row r="580" spans="1:19" ht="12.75">
       <c r="A580" s="2"/>
       <c r="B580" s="2"/>
       <c r="C580" s="2"/>
@@ -15760,7 +15763,7 @@
       <c r="R580" s="2"/>
       <c r="S580" s="2"/>
     </row>
-    <row r="581" spans="1:19" ht="13.2">
+    <row r="581" spans="1:19" ht="12.75">
       <c r="A581" s="2"/>
       <c r="B581" s="2"/>
       <c r="C581" s="2"/>
@@ -15781,7 +15784,7 @@
       <c r="R581" s="2"/>
       <c r="S581" s="2"/>
     </row>
-    <row r="582" spans="1:19" ht="13.2">
+    <row r="582" spans="1:19" ht="12.75">
       <c r="A582" s="2"/>
       <c r="B582" s="2"/>
       <c r="C582" s="2"/>
@@ -15802,7 +15805,7 @@
       <c r="R582" s="2"/>
       <c r="S582" s="2"/>
     </row>
-    <row r="583" spans="1:19" ht="13.2">
+    <row r="583" spans="1:19" ht="12.75">
       <c r="A583" s="2"/>
       <c r="B583" s="2"/>
       <c r="C583" s="2"/>
@@ -15823,7 +15826,7 @@
       <c r="R583" s="2"/>
       <c r="S583" s="2"/>
     </row>
-    <row r="584" spans="1:19" ht="13.2">
+    <row r="584" spans="1:19" ht="12.75">
       <c r="A584" s="2"/>
       <c r="B584" s="2"/>
       <c r="C584" s="2"/>
@@ -15844,7 +15847,7 @@
       <c r="R584" s="2"/>
       <c r="S584" s="2"/>
     </row>
-    <row r="585" spans="1:19" ht="13.2">
+    <row r="585" spans="1:19" ht="12.75">
       <c r="A585" s="2"/>
       <c r="B585" s="2"/>
       <c r="C585" s="2"/>
@@ -15865,7 +15868,7 @@
       <c r="R585" s="2"/>
       <c r="S585" s="2"/>
     </row>
-    <row r="586" spans="1:19" ht="13.2">
+    <row r="586" spans="1:19" ht="12.75">
       <c r="A586" s="2"/>
       <c r="B586" s="2"/>
       <c r="C586" s="2"/>
@@ -15886,7 +15889,7 @@
       <c r="R586" s="2"/>
       <c r="S586" s="2"/>
     </row>
-    <row r="587" spans="1:19" ht="13.2">
+    <row r="587" spans="1:19" ht="12.75">
       <c r="A587" s="2"/>
       <c r="B587" s="2"/>
       <c r="C587" s="2"/>
@@ -15907,7 +15910,7 @@
       <c r="R587" s="2"/>
       <c r="S587" s="2"/>
     </row>
-    <row r="588" spans="1:19" ht="13.2">
+    <row r="588" spans="1:19" ht="12.75">
       <c r="A588" s="2"/>
       <c r="B588" s="2"/>
       <c r="C588" s="2"/>
@@ -15928,7 +15931,7 @@
       <c r="R588" s="2"/>
       <c r="S588" s="2"/>
     </row>
-    <row r="589" spans="1:19" ht="13.2">
+    <row r="589" spans="1:19" ht="12.75">
       <c r="A589" s="2"/>
       <c r="B589" s="2"/>
       <c r="C589" s="2"/>
@@ -15949,7 +15952,7 @@
       <c r="R589" s="2"/>
       <c r="S589" s="2"/>
     </row>
-    <row r="590" spans="1:19" ht="13.2">
+    <row r="590" spans="1:19" ht="12.75">
       <c r="A590" s="2"/>
       <c r="B590" s="2"/>
       <c r="C590" s="2"/>
@@ -15970,7 +15973,7 @@
       <c r="R590" s="2"/>
       <c r="S590" s="2"/>
     </row>
-    <row r="591" spans="1:19" ht="13.2">
+    <row r="591" spans="1:19" ht="12.75">
       <c r="A591" s="2"/>
       <c r="B591" s="2"/>
       <c r="C591" s="2"/>
@@ -15991,7 +15994,7 @@
       <c r="R591" s="2"/>
       <c r="S591" s="2"/>
     </row>
-    <row r="592" spans="1:19" ht="13.2">
+    <row r="592" spans="1:19" ht="12.75">
       <c r="A592" s="2"/>
       <c r="B592" s="2"/>
       <c r="C592" s="2"/>
@@ -16012,7 +16015,7 @@
       <c r="R592" s="2"/>
       <c r="S592" s="2"/>
     </row>
-    <row r="593" spans="1:19" ht="13.2">
+    <row r="593" spans="1:19" ht="12.75">
       <c r="A593" s="2"/>
       <c r="B593" s="2"/>
       <c r="C593" s="2"/>
@@ -16033,7 +16036,7 @@
       <c r="R593" s="2"/>
       <c r="S593" s="2"/>
     </row>
-    <row r="594" spans="1:19" ht="13.2">
+    <row r="594" spans="1:19" ht="12.75">
       <c r="A594" s="2"/>
       <c r="B594" s="2"/>
       <c r="C594" s="2"/>
@@ -16054,7 +16057,7 @@
       <c r="R594" s="2"/>
       <c r="S594" s="2"/>
     </row>
-    <row r="595" spans="1:19" ht="13.2">
+    <row r="595" spans="1:19" ht="12.75">
       <c r="A595" s="2"/>
       <c r="B595" s="2"/>
       <c r="C595" s="2"/>
@@ -16075,7 +16078,7 @@
       <c r="R595" s="2"/>
       <c r="S595" s="2"/>
     </row>
-    <row r="596" spans="1:19" ht="13.2">
+    <row r="596" spans="1:19" ht="12.75">
       <c r="A596" s="2"/>
       <c r="B596" s="2"/>
       <c r="C596" s="2"/>
@@ -16096,7 +16099,7 @@
       <c r="R596" s="2"/>
       <c r="S596" s="2"/>
     </row>
-    <row r="597" spans="1:19" ht="13.2">
+    <row r="597" spans="1:19" ht="12.75">
       <c r="A597" s="2"/>
       <c r="B597" s="2"/>
       <c r="C597" s="2"/>
@@ -16117,7 +16120,7 @@
       <c r="R597" s="2"/>
       <c r="S597" s="2"/>
     </row>
-    <row r="598" spans="1:19" ht="13.2">
+    <row r="598" spans="1:19" ht="12.75">
       <c r="A598" s="2"/>
       <c r="B598" s="2"/>
       <c r="C598" s="2"/>
@@ -16138,7 +16141,7 @@
       <c r="R598" s="2"/>
       <c r="S598" s="2"/>
     </row>
-    <row r="599" spans="1:19" ht="13.2">
+    <row r="599" spans="1:19" ht="12.75">
       <c r="A599" s="2"/>
       <c r="B599" s="2"/>
       <c r="C599" s="2"/>
@@ -16159,7 +16162,7 @@
       <c r="R599" s="2"/>
       <c r="S599" s="2"/>
     </row>
-    <row r="600" spans="1:19" ht="13.2">
+    <row r="600" spans="1:19" ht="12.75">
       <c r="A600" s="2"/>
       <c r="B600" s="2"/>
       <c r="C600" s="2"/>
@@ -16180,7 +16183,7 @@
       <c r="R600" s="2"/>
       <c r="S600" s="2"/>
     </row>
-    <row r="601" spans="1:19" ht="13.2">
+    <row r="601" spans="1:19" ht="12.75">
       <c r="A601" s="2"/>
       <c r="B601" s="2"/>
       <c r="C601" s="2"/>
@@ -16201,7 +16204,7 @@
       <c r="R601" s="2"/>
       <c r="S601" s="2"/>
     </row>
-    <row r="602" spans="1:19" ht="13.2">
+    <row r="602" spans="1:19" ht="12.75">
       <c r="A602" s="2"/>
       <c r="B602" s="2"/>
       <c r="C602" s="2"/>
@@ -16222,7 +16225,7 @@
       <c r="R602" s="2"/>
       <c r="S602" s="2"/>
     </row>
-    <row r="603" spans="1:19" ht="13.2">
+    <row r="603" spans="1:19" ht="12.75">
       <c r="A603" s="2"/>
       <c r="B603" s="2"/>
       <c r="C603" s="2"/>
@@ -16243,7 +16246,7 @@
       <c r="R603" s="2"/>
       <c r="S603" s="2"/>
     </row>
-    <row r="604" spans="1:19" ht="13.2">
+    <row r="604" spans="1:19" ht="12.75">
       <c r="A604" s="2"/>
       <c r="B604" s="2"/>
       <c r="C604" s="2"/>
@@ -16264,7 +16267,7 @@
       <c r="R604" s="2"/>
       <c r="S604" s="2"/>
     </row>
-    <row r="605" spans="1:19" ht="13.2">
+    <row r="605" spans="1:19" ht="12.75">
       <c r="A605" s="2"/>
       <c r="B605" s="2"/>
       <c r="C605" s="2"/>
@@ -16285,7 +16288,7 @@
       <c r="R605" s="2"/>
       <c r="S605" s="2"/>
     </row>
-    <row r="606" spans="1:19" ht="13.2">
+    <row r="606" spans="1:19" ht="12.75">
       <c r="A606" s="2"/>
       <c r="B606" s="2"/>
       <c r="C606" s="2"/>
@@ -16306,7 +16309,7 @@
       <c r="R606" s="2"/>
       <c r="S606" s="2"/>
     </row>
-    <row r="607" spans="1:19" ht="13.2">
+    <row r="607" spans="1:19" ht="12.75">
       <c r="A607" s="2"/>
       <c r="B607" s="2"/>
       <c r="C607" s="2"/>
@@ -16327,7 +16330,7 @@
       <c r="R607" s="2"/>
       <c r="S607" s="2"/>
     </row>
-    <row r="608" spans="1:19" ht="13.2">
+    <row r="608" spans="1:19" ht="12.75">
       <c r="A608" s="2"/>
       <c r="B608" s="2"/>
       <c r="C608" s="2"/>
@@ -16348,7 +16351,7 @@
       <c r="R608" s="2"/>
       <c r="S608" s="2"/>
     </row>
-    <row r="609" spans="1:19" ht="13.2">
+    <row r="609" spans="1:19" ht="12.75">
       <c r="A609" s="2"/>
       <c r="B609" s="2"/>
       <c r="C609" s="2"/>
@@ -16369,7 +16372,7 @@
       <c r="R609" s="2"/>
       <c r="S609" s="2"/>
     </row>
-    <row r="610" spans="1:19" ht="13.2">
+    <row r="610" spans="1:19" ht="12.75">
       <c r="A610" s="2"/>
       <c r="B610" s="2"/>
       <c r="C610" s="2"/>
@@ -16390,7 +16393,7 @@
       <c r="R610" s="2"/>
       <c r="S610" s="2"/>
     </row>
-    <row r="611" spans="1:19" ht="13.2">
+    <row r="611" spans="1:19" ht="12.75">
       <c r="A611" s="2"/>
       <c r="B611" s="2"/>
       <c r="C611" s="2"/>
@@ -16411,7 +16414,7 @@
       <c r="R611" s="2"/>
       <c r="S611" s="2"/>
     </row>
-    <row r="612" spans="1:19" ht="13.2">
+    <row r="612" spans="1:19" ht="12.75">
       <c r="A612" s="2"/>
       <c r="B612" s="2"/>
       <c r="C612" s="2"/>
@@ -16432,7 +16435,7 @@
       <c r="R612" s="2"/>
       <c r="S612" s="2"/>
     </row>
-    <row r="613" spans="1:19" ht="13.2">
+    <row r="613" spans="1:19" ht="12.75">
       <c r="A613" s="2"/>
       <c r="B613" s="2"/>
       <c r="C613" s="2"/>
@@ -16453,7 +16456,7 @@
       <c r="R613" s="2"/>
       <c r="S613" s="2"/>
     </row>
-    <row r="614" spans="1:19" ht="13.2">
+    <row r="614" spans="1:19" ht="12.75">
       <c r="A614" s="2"/>
       <c r="B614" s="2"/>
       <c r="C614" s="2"/>
@@ -16474,7 +16477,7 @@
       <c r="R614" s="2"/>
       <c r="S614" s="2"/>
     </row>
-    <row r="615" spans="1:19" ht="13.2">
+    <row r="615" spans="1:19" ht="12.75">
       <c r="A615" s="2"/>
       <c r="B615" s="2"/>
       <c r="C615" s="2"/>
@@ -16495,7 +16498,7 @@
       <c r="R615" s="2"/>
       <c r="S615" s="2"/>
     </row>
-    <row r="616" spans="1:19" ht="13.2">
+    <row r="616" spans="1:19" ht="12.75">
       <c r="A616" s="2"/>
       <c r="B616" s="2"/>
       <c r="C616" s="2"/>
@@ -16516,7 +16519,7 @@
       <c r="R616" s="2"/>
       <c r="S616" s="2"/>
     </row>
-    <row r="617" spans="1:19" ht="13.2">
+    <row r="617" spans="1:19" ht="12.75">
       <c r="A617" s="2"/>
       <c r="B617" s="2"/>
       <c r="C617" s="2"/>
@@ -16537,7 +16540,7 @@
       <c r="R617" s="2"/>
       <c r="S617" s="2"/>
     </row>
-    <row r="618" spans="1:19" ht="13.2">
+    <row r="618" spans="1:19" ht="12.75">
       <c r="A618" s="2"/>
       <c r="B618" s="2"/>
       <c r="C618" s="2"/>
@@ -16558,7 +16561,7 @@
       <c r="R618" s="2"/>
       <c r="S618" s="2"/>
     </row>
-    <row r="619" spans="1:19" ht="13.2">
+    <row r="619" spans="1:19" ht="12.75">
       <c r="A619" s="2"/>
       <c r="B619" s="2"/>
       <c r="C619" s="2"/>
@@ -16579,7 +16582,7 @@
       <c r="R619" s="2"/>
       <c r="S619" s="2"/>
     </row>
-    <row r="620" spans="1:19" ht="13.2">
+    <row r="620" spans="1:19" ht="12.75">
       <c r="A620" s="2"/>
       <c r="B620" s="2"/>
       <c r="C620" s="2"/>
@@ -16600,7 +16603,7 @@
       <c r="R620" s="2"/>
       <c r="S620" s="2"/>
     </row>
-    <row r="621" spans="1:19" ht="13.2">
+    <row r="621" spans="1:19" ht="12.75">
       <c r="A621" s="2"/>
       <c r="B621" s="2"/>
       <c r="C621" s="2"/>
@@ -16621,7 +16624,7 @@
       <c r="R621" s="2"/>
       <c r="S621" s="2"/>
     </row>
-    <row r="622" spans="1:19" ht="13.2">
+    <row r="622" spans="1:19" ht="12.75">
       <c r="A622" s="2"/>
       <c r="B622" s="2"/>
       <c r="C622" s="2"/>
@@ -16642,7 +16645,7 @@
       <c r="R622" s="2"/>
       <c r="S622" s="2"/>
     </row>
-    <row r="623" spans="1:19" ht="13.2">
+    <row r="623" spans="1:19" ht="12.75">
       <c r="A623" s="2"/>
       <c r="B623" s="2"/>
       <c r="C623" s="2"/>
@@ -16663,7 +16666,7 @@
       <c r="R623" s="2"/>
       <c r="S623" s="2"/>
     </row>
-    <row r="624" spans="1:19" ht="13.2">
+    <row r="624" spans="1:19" ht="12.75">
       <c r="A624" s="2"/>
       <c r="B624" s="2"/>
       <c r="C624" s="2"/>
@@ -16684,7 +16687,7 @@
       <c r="R624" s="2"/>
       <c r="S624" s="2"/>
     </row>
-    <row r="625" spans="1:19" ht="13.2">
+    <row r="625" spans="1:19" ht="12.75">
       <c r="A625" s="2"/>
       <c r="B625" s="2"/>
       <c r="C625" s="2"/>
@@ -16705,7 +16708,7 @@
       <c r="R625" s="2"/>
       <c r="S625" s="2"/>
     </row>
-    <row r="626" spans="1:19" ht="13.2">
+    <row r="626" spans="1:19" ht="12.75">
       <c r="A626" s="2"/>
       <c r="B626" s="2"/>
       <c r="C626" s="2"/>
@@ -16726,7 +16729,7 @@
       <c r="R626" s="2"/>
       <c r="S626" s="2"/>
     </row>
-    <row r="627" spans="1:19" ht="13.2">
+    <row r="627" spans="1:19" ht="12.75">
       <c r="A627" s="2"/>
       <c r="B627" s="2"/>
       <c r="C627" s="2"/>
@@ -16747,7 +16750,7 @@
       <c r="R627" s="2"/>
       <c r="S627" s="2"/>
     </row>
-    <row r="628" spans="1:19" ht="13.2">
+    <row r="628" spans="1:19" ht="12.75">
       <c r="A628" s="2"/>
       <c r="B628" s="2"/>
       <c r="C628" s="2"/>
@@ -16768,7 +16771,7 @@
       <c r="R628" s="2"/>
       <c r="S628" s="2"/>
     </row>
-    <row r="629" spans="1:19" ht="13.2">
+    <row r="629" spans="1:19" ht="12.75">
       <c r="A629" s="2"/>
       <c r="B629" s="2"/>
       <c r="C629" s="2"/>
@@ -16789,7 +16792,7 @@
       <c r="R629" s="2"/>
       <c r="S629" s="2"/>
     </row>
-    <row r="630" spans="1:19" ht="13.2">
+    <row r="630" spans="1:19" ht="12.75">
       <c r="A630" s="2"/>
       <c r="B630" s="2"/>
       <c r="C630" s="2"/>
@@ -16810,7 +16813,7 @@
       <c r="R630" s="2"/>
       <c r="S630" s="2"/>
     </row>
-    <row r="631" spans="1:19" ht="13.2">
+    <row r="631" spans="1:19" ht="12.75">
       <c r="A631" s="2"/>
       <c r="B631" s="2"/>
       <c r="C631" s="2"/>
@@ -16831,7 +16834,7 @@
       <c r="R631" s="2"/>
       <c r="S631" s="2"/>
     </row>
-    <row r="632" spans="1:19" ht="13.2">
+    <row r="632" spans="1:19" ht="12.75">
       <c r="A632" s="2"/>
       <c r="B632" s="2"/>
       <c r="C632" s="2"/>
@@ -16852,7 +16855,7 @@
       <c r="R632" s="2"/>
       <c r="S632" s="2"/>
     </row>
-    <row r="633" spans="1:19" ht="13.2">
+    <row r="633" spans="1:19" ht="12.75">
       <c r="A633" s="2"/>
       <c r="B633" s="2"/>
       <c r="C633" s="2"/>
@@ -16873,7 +16876,7 @@
       <c r="R633" s="2"/>
       <c r="S633" s="2"/>
     </row>
-    <row r="634" spans="1:19" ht="13.2">
+    <row r="634" spans="1:19" ht="12.75">
       <c r="A634" s="2"/>
       <c r="B634" s="2"/>
       <c r="C634" s="2"/>
@@ -16894,7 +16897,7 @@
       <c r="R634" s="2"/>
       <c r="S634" s="2"/>
     </row>
-    <row r="635" spans="1:19" ht="13.2">
+    <row r="635" spans="1:19" ht="12.75">
       <c r="A635" s="2"/>
       <c r="B635" s="2"/>
       <c r="C635" s="2"/>
@@ -16915,7 +16918,7 @@
       <c r="R635" s="2"/>
       <c r="S635" s="2"/>
     </row>
-    <row r="636" spans="1:19" ht="13.2">
+    <row r="636" spans="1:19" ht="12.75">
       <c r="A636" s="2"/>
       <c r="B636" s="2"/>
       <c r="C636" s="2"/>
@@ -16936,7 +16939,7 @@
       <c r="R636" s="2"/>
       <c r="S636" s="2"/>
     </row>
-    <row r="637" spans="1:19" ht="13.2">
+    <row r="637" spans="1:19" ht="12.75">
       <c r="A637" s="2"/>
       <c r="B637" s="2"/>
       <c r="C637" s="2"/>
@@ -16957,7 +16960,7 @@
       <c r="R637" s="2"/>
       <c r="S637" s="2"/>
     </row>
-    <row r="638" spans="1:19" ht="13.2">
+    <row r="638" spans="1:19" ht="12.75">
       <c r="A638" s="2"/>
       <c r="B638" s="2"/>
       <c r="C638" s="2"/>
@@ -16978,7 +16981,7 @@
       <c r="R638" s="2"/>
       <c r="S638" s="2"/>
     </row>
-    <row r="639" spans="1:19" ht="13.2">
+    <row r="639" spans="1:19" ht="12.75">
       <c r="A639" s="2"/>
       <c r="B639" s="2"/>
       <c r="C639" s="2"/>
@@ -16999,7 +17002,7 @@
       <c r="R639" s="2"/>
       <c r="S639" s="2"/>
     </row>
-    <row r="640" spans="1:19" ht="13.2">
+    <row r="640" spans="1:19" ht="12.75">
       <c r="A640" s="2"/>
       <c r="B640" s="2"/>
       <c r="C640" s="2"/>
@@ -17020,7 +17023,7 @@
       <c r="R640" s="2"/>
       <c r="S640" s="2"/>
     </row>
-    <row r="641" spans="1:19" ht="13.2">
+    <row r="641" spans="1:19" ht="12.75">
       <c r="A641" s="2"/>
       <c r="B641" s="2"/>
       <c r="C641" s="2"/>
@@ -17041,7 +17044,7 @@
       <c r="R641" s="2"/>
       <c r="S641" s="2"/>
     </row>
-    <row r="642" spans="1:19" ht="13.2">
+    <row r="642" spans="1:19" ht="12.75">
       <c r="A642" s="2"/>
       <c r="B642" s="2"/>
       <c r="C642" s="2"/>
@@ -17062,7 +17065,7 @@
       <c r="R642" s="2"/>
       <c r="S642" s="2"/>
     </row>
-    <row r="643" spans="1:19" ht="13.2">
+    <row r="643" spans="1:19" ht="12.75">
       <c r="A643" s="2"/>
       <c r="B643" s="2"/>
       <c r="C643" s="2"/>
@@ -17083,7 +17086,7 @@
       <c r="R643" s="2"/>
       <c r="S643" s="2"/>
     </row>
-    <row r="644" spans="1:19" ht="13.2">
+    <row r="644" spans="1:19" ht="12.75">
       <c r="A644" s="2"/>
       <c r="B644" s="2"/>
       <c r="C644" s="2"/>
@@ -17104,7 +17107,7 @@
       <c r="R644" s="2"/>
       <c r="S644" s="2"/>
     </row>
-    <row r="645" spans="1:19" ht="13.2">
+    <row r="645" spans="1:19" ht="12.75">
       <c r="A645" s="2"/>
       <c r="B645" s="2"/>
       <c r="C645" s="2"/>
@@ -17125,7 +17128,7 @@
       <c r="R645" s="2"/>
       <c r="S645" s="2"/>
     </row>
-    <row r="646" spans="1:19" ht="13.2">
+    <row r="646" spans="1:19" ht="12.75">
       <c r="A646" s="2"/>
       <c r="B646" s="2"/>
       <c r="C646" s="2"/>
@@ -17146,7 +17149,7 @@
       <c r="R646" s="2"/>
       <c r="S646" s="2"/>
     </row>
-    <row r="647" spans="1:19" ht="13.2">
+    <row r="647" spans="1:19" ht="12.75">
       <c r="A647" s="2"/>
       <c r="B647" s="2"/>
       <c r="C647" s="2"/>
@@ -17167,7 +17170,7 @@
       <c r="R647" s="2"/>
       <c r="S647" s="2"/>
     </row>
-    <row r="648" spans="1:19" ht="13.2">
+    <row r="648" spans="1:19" ht="12.75">
       <c r="A648" s="2"/>
       <c r="B648" s="2"/>
       <c r="C648" s="2"/>
@@ -17188,7 +17191,7 @@
       <c r="R648" s="2"/>
       <c r="S648" s="2"/>
     </row>
-    <row r="649" spans="1:19" ht="13.2">
+    <row r="649" spans="1:19" ht="12.75">
       <c r="A649" s="2"/>
       <c r="B649" s="2"/>
       <c r="C649" s="2"/>
@@ -17209,7 +17212,7 @@
       <c r="R649" s="2"/>
       <c r="S649" s="2"/>
     </row>
-    <row r="650" spans="1:19" ht="13.2">
+    <row r="650" spans="1:19" ht="12.75">
       <c r="A650" s="2"/>
       <c r="B650" s="2"/>
       <c r="C650" s="2"/>
@@ -17230,7 +17233,7 @@
       <c r="R650" s="2"/>
       <c r="S650" s="2"/>
     </row>
-    <row r="651" spans="1:19" ht="13.2">
+    <row r="651" spans="1:19" ht="12.75">
       <c r="A651" s="2"/>
       <c r="B651" s="2"/>
       <c r="C651" s="2"/>
@@ -17251,7 +17254,7 @@
       <c r="R651" s="2"/>
       <c r="S651" s="2"/>
     </row>
-    <row r="652" spans="1:19" ht="13.2">
+    <row r="652" spans="1:19" ht="12.75">
       <c r="A652" s="2"/>
       <c r="B652" s="2"/>
       <c r="C652" s="2"/>
@@ -17272,7 +17275,7 @@
       <c r="R652" s="2"/>
       <c r="S652" s="2"/>
     </row>
-    <row r="653" spans="1:19" ht="13.2">
+    <row r="653" spans="1:19" ht="12.75">
       <c r="A653" s="2"/>
       <c r="B653" s="2"/>
       <c r="C653" s="2"/>
@@ -17293,7 +17296,7 @@
       <c r="R653" s="2"/>
       <c r="S653" s="2"/>
     </row>
-    <row r="654" spans="1:19" ht="13.2">
+    <row r="654" spans="1:19" ht="12.75">
       <c r="A654" s="2"/>
       <c r="B654" s="2"/>
       <c r="C654" s="2"/>
@@ -17314,7 +17317,7 @@
       <c r="R654" s="2"/>
       <c r="S654" s="2"/>
     </row>
-    <row r="655" spans="1:19" ht="13.2">
+    <row r="655" spans="1:19" ht="12.75">
       <c r="A655" s="2"/>
       <c r="B655" s="2"/>
       <c r="C655" s="2"/>
@@ -17335,7 +17338,7 @@
       <c r="R655" s="2"/>
       <c r="S655" s="2"/>
     </row>
-    <row r="656" spans="1:19" ht="13.2">
+    <row r="656" spans="1:19" ht="12.75">
       <c r="A656" s="2"/>
       <c r="B656" s="2"/>
       <c r="C656" s="2"/>
@@ -17356,7 +17359,7 @@
       <c r="R656" s="2"/>
       <c r="S656" s="2"/>
     </row>
-    <row r="657" spans="1:19" ht="13.2">
+    <row r="657" spans="1:19" ht="12.75">
       <c r="A657" s="2"/>
       <c r="B657" s="2"/>
       <c r="C657" s="2"/>
@@ -17377,7 +17380,7 @@
       <c r="R657" s="2"/>
       <c r="S657" s="2"/>
     </row>
-    <row r="658" spans="1:19" ht="13.2">
+    <row r="658" spans="1:19" ht="12.75">
       <c r="A658" s="2"/>
       <c r="B658" s="2"/>
       <c r="C658" s="2"/>
@@ -17398,7 +17401,7 @@
       <c r="R658" s="2"/>
       <c r="S658" s="2"/>
     </row>
-    <row r="659" spans="1:19" ht="13.2">
+    <row r="659" spans="1:19" ht="12.75">
       <c r="A659" s="2"/>
       <c r="B659" s="2"/>
       <c r="C659" s="2"/>
@@ -17419,7 +17422,7 @@
       <c r="R659" s="2"/>
       <c r="S659" s="2"/>
     </row>
-    <row r="660" spans="1:19" ht="13.2">
+    <row r="660" spans="1:19" ht="12.75">
       <c r="A660" s="2"/>
       <c r="B660" s="2"/>
       <c r="C660" s="2"/>
@@ -17440,7 +17443,7 @@
       <c r="R660" s="2"/>
       <c r="S660" s="2"/>
     </row>
-    <row r="661" spans="1:19" ht="13.2">
+    <row r="661" spans="1:19" ht="12.75">
       <c r="A661" s="2"/>
       <c r="B661" s="2"/>
       <c r="C661" s="2"/>
@@ -17461,7 +17464,7 @@
       <c r="R661" s="2"/>
       <c r="S661" s="2"/>
     </row>
-    <row r="662" spans="1:19" ht="13.2">
+    <row r="662" spans="1:19" ht="12.75">
       <c r="A662" s="2"/>
       <c r="B662" s="2"/>
       <c r="C662" s="2"/>
@@ -17482,7 +17485,7 @@
       <c r="R662" s="2"/>
       <c r="S662" s="2"/>
     </row>
-    <row r="663" spans="1:19" ht="13.2">
+    <row r="663" spans="1:19" ht="12.75">
       <c r="A663" s="2"/>
       <c r="B663" s="2"/>
       <c r="C663" s="2"/>
@@ -17503,7 +17506,7 @@
       <c r="R663" s="2"/>
       <c r="S663" s="2"/>
     </row>
-    <row r="664" spans="1:19" ht="13.2">
+    <row r="664" spans="1:19" ht="12.75">
       <c r="A664" s="2"/>
       <c r="B664" s="2"/>
       <c r="C664" s="2"/>
@@ -17524,7 +17527,7 @@
       <c r="R664" s="2"/>
       <c r="S664" s="2"/>
     </row>
-    <row r="665" spans="1:19" ht="13.2">
+    <row r="665" spans="1:19" ht="12.75">
       <c r="A665" s="2"/>
       <c r="B665" s="2"/>
       <c r="C665" s="2"/>
@@ -17545,7 +17548,7 @@
       <c r="R665" s="2"/>
       <c r="S665" s="2"/>
     </row>
-    <row r="666" spans="1:19" ht="13.2">
+    <row r="666" spans="1:19" ht="12.75">
       <c r="A666" s="2"/>
       <c r="B666" s="2"/>
       <c r="C666" s="2"/>
@@ -17566,7 +17569,7 @@
       <c r="R666" s="2"/>
       <c r="S666" s="2"/>
     </row>
-    <row r="667" spans="1:19" ht="13.2">
+    <row r="667" spans="1:19" ht="12.75">
       <c r="A667" s="2"/>
       <c r="B667" s="2"/>
       <c r="C667" s="2"/>
@@ -17587,7 +17590,7 @@
       <c r="R667" s="2"/>
       <c r="S667" s="2"/>
     </row>
-    <row r="668" spans="1:19" ht="13.2">
+    <row r="668" spans="1:19" ht="12.75">
       <c r="A668" s="2"/>
       <c r="B668" s="2"/>
       <c r="C668" s="2"/>
@@ -17608,7 +17611,7 @@
       <c r="R668" s="2"/>
       <c r="S668" s="2"/>
     </row>
-    <row r="669" spans="1:19" ht="13.2">
+    <row r="669" spans="1:19" ht="12.75">
       <c r="A669" s="2"/>
       <c r="B669" s="2"/>
       <c r="C669" s="2"/>
@@ -17629,7 +17632,7 @@
       <c r="R669" s="2"/>
       <c r="S669" s="2"/>
     </row>
-    <row r="670" spans="1:19" ht="13.2">
+    <row r="670" spans="1:19" ht="12.75">
       <c r="A670" s="2"/>
       <c r="B670" s="2"/>
       <c r="C670" s="2"/>
@@ -17650,7 +17653,7 @@
       <c r="R670" s="2"/>
       <c r="S670" s="2"/>
     </row>
-    <row r="671" spans="1:19" ht="13.2">
+    <row r="671" spans="1:19" ht="12.75">
       <c r="A671" s="2"/>
       <c r="B671" s="2"/>
       <c r="C671" s="2"/>
@@ -17671,7 +17674,7 @@
       <c r="R671" s="2"/>
       <c r="S671" s="2"/>
     </row>
-    <row r="672" spans="1:19" ht="13.2">
+    <row r="672" spans="1:19" ht="12.75">
       <c r="A672" s="2"/>
       <c r="B672" s="2"/>
       <c r="C672" s="2"/>
@@ -17692,7 +17695,7 @@
       <c r="R672" s="2"/>
       <c r="S672" s="2"/>
     </row>
-    <row r="673" spans="1:19" ht="13.2">
+    <row r="673" spans="1:19" ht="12.75">
       <c r="A673" s="2"/>
       <c r="B673" s="2"/>
       <c r="C673" s="2"/>
@@ -17713,7 +17716,7 @@
       <c r="R673" s="2"/>
       <c r="S673" s="2"/>
     </row>
-    <row r="674" spans="1:19" ht="13.2">
+    <row r="674" spans="1:19" ht="12.75">
       <c r="A674" s="2"/>
       <c r="B674" s="2"/>
       <c r="C674" s="2"/>
@@ -17734,7 +17737,7 @@
       <c r="R674" s="2"/>
       <c r="S674" s="2"/>
     </row>
-    <row r="675" spans="1:19" ht="13.2">
+    <row r="675" spans="1:19" ht="12.75">
       <c r="A675" s="2"/>
       <c r="B675" s="2"/>
       <c r="C675" s="2"/>
@@ -17755,7 +17758,7 @@
       <c r="R675" s="2"/>
       <c r="S675" s="2"/>
     </row>
-    <row r="676" spans="1:19" ht="13.2">
+    <row r="676" spans="1:19" ht="12.75">
       <c r="A676" s="2"/>
       <c r="B676" s="2"/>
       <c r="C676" s="2"/>
@@ -17776,7 +17779,7 @@
       <c r="R676" s="2"/>
       <c r="S676" s="2"/>
     </row>
-    <row r="677" spans="1:19" ht="13.2">
+    <row r="677" spans="1:19" ht="12.75">
       <c r="A677" s="2"/>
       <c r="B677" s="2"/>
       <c r="C677" s="2"/>
@@ -17797,7 +17800,7 @@
       <c r="R677" s="2"/>
       <c r="S677" s="2"/>
     </row>
-    <row r="678" spans="1:19" ht="13.2">
+    <row r="678" spans="1:19" ht="12.75">
       <c r="A678" s="2"/>
       <c r="B678" s="2"/>
       <c r="C678" s="2"/>
@@ -17818,7 +17821,7 @@
       <c r="R678" s="2"/>
       <c r="S678" s="2"/>
     </row>
-    <row r="679" spans="1:19" ht="13.2">
+    <row r="679" spans="1:19" ht="12.75">
       <c r="A679" s="2"/>
       <c r="B679" s="2"/>
       <c r="C679" s="2"/>
@@ -17839,7 +17842,7 @@
       <c r="R679" s="2"/>
       <c r="S679" s="2"/>
     </row>
-    <row r="680" spans="1:19" ht="13.2">
+    <row r="680" spans="1:19" ht="12.75">
       <c r="A680" s="2"/>
       <c r="B680" s="2"/>
       <c r="C680" s="2"/>
@@ -17860,7 +17863,7 @@
       <c r="R680" s="2"/>
       <c r="S680" s="2"/>
     </row>
-    <row r="681" spans="1:19" ht="13.2">
+    <row r="681" spans="1:19" ht="12.75">
       <c r="A681" s="2"/>
       <c r="B681" s="2"/>
       <c r="C681" s="2"/>
@@ -17881,7 +17884,7 @@
       <c r="R681" s="2"/>
       <c r="S681" s="2"/>
     </row>
-    <row r="682" spans="1:19" ht="13.2">
+    <row r="682" spans="1:19" ht="12.75">
       <c r="A682" s="2"/>
       <c r="B682" s="2"/>
       <c r="C682" s="2"/>
@@ -17902,7 +17905,7 @@
       <c r="R682" s="2"/>
       <c r="S682" s="2"/>
     </row>
-    <row r="683" spans="1:19" ht="13.2">
+    <row r="683" spans="1:19" ht="12.75">
       <c r="A683" s="2"/>
       <c r="B683" s="2"/>
       <c r="C683" s="2"/>
@@ -17923,7 +17926,7 @@
       <c r="R683" s="2"/>
       <c r="S683" s="2"/>
     </row>
-    <row r="684" spans="1:19" ht="13.2">
+    <row r="684" spans="1:19" ht="12.75">
       <c r="A684" s="2"/>
       <c r="B684" s="2"/>
       <c r="C684" s="2"/>
@@ -17944,7 +17947,7 @@
       <c r="R684" s="2"/>
       <c r="S684" s="2"/>
     </row>
-    <row r="685" spans="1:19" ht="13.2">
+    <row r="685" spans="1:19" ht="12.75">
       <c r="A685" s="2"/>
       <c r="B685" s="2"/>
       <c r="C685" s="2"/>
@@ -17965,7 +17968,7 @@
       <c r="R685" s="2"/>
       <c r="S685" s="2"/>
     </row>
-    <row r="686" spans="1:19" ht="13.2">
+    <row r="686" spans="1:19" ht="12.75">
       <c r="A686" s="2"/>
       <c r="B686" s="2"/>
       <c r="C686" s="2"/>
@@ -17986,7 +17989,7 @@
       <c r="R686" s="2"/>
       <c r="S686" s="2"/>
     </row>
-    <row r="687" spans="1:19" ht="13.2">
+    <row r="687" spans="1:19" ht="12.75">
       <c r="A687" s="2"/>
       <c r="B687" s="2"/>
       <c r="C687" s="2"/>
@@ -18007,7 +18010,7 @@
       <c r="R687" s="2"/>
       <c r="S687" s="2"/>
     </row>
-    <row r="688" spans="1:19" ht="13.2">
+    <row r="688" spans="1:19" ht="12.75">
       <c r="A688" s="2"/>
       <c r="B688" s="2"/>
       <c r="C688" s="2"/>
@@ -18028,7 +18031,7 @@
       <c r="R688" s="2"/>
       <c r="S688" s="2"/>
     </row>
-    <row r="689" spans="1:19" ht="13.2">
+    <row r="689" spans="1:19" ht="12.75">
       <c r="A689" s="2"/>
       <c r="B689" s="2"/>
       <c r="C689" s="2"/>
@@ -18049,7 +18052,7 @@
       <c r="R689" s="2"/>
       <c r="S689" s="2"/>
     </row>
-    <row r="690" spans="1:19" ht="13.2">
+    <row r="690" spans="1:19" ht="12.75">
       <c r="A690" s="2"/>
       <c r="B690" s="2"/>
       <c r="C690" s="2"/>
@@ -18070,7 +18073,7 @@
       <c r="R690" s="2"/>
       <c r="S690" s="2"/>
     </row>
-    <row r="691" spans="1:19" ht="13.2">
+    <row r="691" spans="1:19" ht="12.75">
       <c r="A691" s="2"/>
       <c r="B691" s="2"/>
       <c r="C691" s="2"/>
@@ -18091,7 +18094,7 @@
       <c r="R691" s="2"/>
       <c r="S691" s="2"/>
     </row>
-    <row r="692" spans="1:19" ht="13.2">
+    <row r="692" spans="1:19" ht="12.75">
       <c r="A692" s="2"/>
       <c r="B692" s="2"/>
       <c r="C692" s="2"/>
@@ -18112,7 +18115,7 @@
       <c r="R692" s="2"/>
       <c r="S692" s="2"/>
     </row>
-    <row r="693" spans="1:19" ht="13.2">
+    <row r="693" spans="1:19" ht="12.75">
       <c r="A693" s="2"/>
       <c r="B693" s="2"/>
       <c r="C693" s="2"/>
@@ -18133,7 +18136,7 @@
       <c r="R693" s="2"/>
       <c r="S693" s="2"/>
     </row>
-    <row r="694" spans="1:19" ht="13.2">
+    <row r="694" spans="1:19" ht="12.75">
       <c r="A694" s="2"/>
       <c r="B694" s="2"/>
       <c r="C694" s="2"/>
@@ -18154,7 +18157,7 @@
       <c r="R694" s="2"/>
       <c r="S694" s="2"/>
     </row>
-    <row r="695" spans="1:19" ht="13.2">
+    <row r="695" spans="1:19" ht="12.75">
       <c r="A695" s="2"/>
       <c r="B695" s="2"/>
       <c r="C695" s="2"/>
@@ -18175,7 +18178,7 @@
       <c r="R695" s="2"/>
       <c r="S695" s="2"/>
     </row>
-    <row r="696" spans="1:19" ht="13.2">
+    <row r="696" spans="1:19" ht="12.75">
       <c r="A696" s="2"/>
       <c r="B696" s="2"/>
       <c r="C696" s="2"/>
@@ -18196,7 +18199,7 @@
       <c r="R696" s="2"/>
       <c r="S696" s="2"/>
     </row>
-    <row r="697" spans="1:19" ht="13.2">
+    <row r="697" spans="1:19" ht="12.75">
       <c r="A697" s="2"/>
       <c r="B697" s="2"/>
       <c r="C697" s="2"/>
@@ -18217,7 +18220,7 @@
       <c r="R697" s="2"/>
       <c r="S697" s="2"/>
     </row>
-    <row r="698" spans="1:19" ht="13.2">
+    <row r="698" spans="1:19" ht="12.75">
       <c r="A698" s="2"/>
       <c r="B698" s="2"/>
       <c r="C698" s="2"/>
@@ -18238,7 +18241,7 @@
       <c r="R698" s="2"/>
       <c r="S698" s="2"/>
     </row>
-    <row r="699" spans="1:19" ht="13.2">
+    <row r="699" spans="1:19" ht="12.75">
       <c r="A699" s="2"/>
       <c r="B699" s="2"/>
       <c r="C699" s="2"/>
@@ -18259,7 +18262,7 @@
       <c r="R699" s="2"/>
       <c r="S699" s="2"/>
     </row>
-    <row r="700" spans="1:19" ht="13.2">
+    <row r="700" spans="1:19" ht="12.75">
       <c r="A700" s="2"/>
       <c r="B700" s="2"/>
       <c r="C700" s="2"/>
@@ -18280,7 +18283,7 @@
       <c r="R700" s="2"/>
       <c r="S700" s="2"/>
     </row>
-    <row r="701" spans="1:19" ht="13.2">
+    <row r="701" spans="1:19" ht="12.75">
       <c r="A701" s="2"/>
       <c r="B701" s="2"/>
       <c r="C701" s="2"/>
@@ -18301,7 +18304,7 @@
       <c r="R701" s="2"/>
       <c r="S701" s="2"/>
     </row>
-    <row r="702" spans="1:19" ht="13.2">
+    <row r="702" spans="1:19" ht="12.75">
       <c r="A702" s="2"/>
       <c r="B702" s="2"/>
       <c r="C702" s="2"/>
@@ -18322,7 +18325,7 @@
       <c r="R702" s="2"/>
       <c r="S702" s="2"/>
     </row>
-    <row r="703" spans="1:19" ht="13.2">
+    <row r="703" spans="1:19" ht="12.75">
       <c r="A703" s="2"/>
       <c r="B703" s="2"/>
       <c r="C703" s="2"/>
@@ -18343,7 +18346,7 @@
       <c r="R703" s="2"/>
       <c r="S703" s="2"/>
     </row>
-    <row r="704" spans="1:19" ht="13.2">
+    <row r="704" spans="1:19" ht="12.75">
       <c r="A704" s="2"/>
       <c r="B704" s="2"/>
       <c r="C704" s="2"/>
@@ -18364,7 +18367,7 @@
       <c r="R704" s="2"/>
       <c r="S704" s="2"/>
     </row>
-    <row r="705" spans="1:19" ht="13.2">
+    <row r="705" spans="1:19" ht="12.75">
       <c r="A705" s="2"/>
       <c r="B705" s="2"/>
       <c r="C705" s="2"/>
@@ -18385,7 +18388,7 @@
       <c r="R705" s="2"/>
       <c r="S705" s="2"/>
     </row>
-    <row r="706" spans="1:19" ht="13.2">
+    <row r="706" spans="1:19" ht="12.75">
       <c r="A706" s="2"/>
       <c r="B706" s="2"/>
       <c r="C706" s="2"/>
@@ -18406,7 +18409,7 @@
       <c r="R706" s="2"/>
       <c r="S706" s="2"/>
     </row>
-    <row r="707" spans="1:19" ht="13.2">
+    <row r="707" spans="1:19" ht="12.75">
       <c r="A707" s="2"/>
       <c r="B707" s="2"/>
       <c r="C707" s="2"/>
@@ -18427,7 +18430,7 @@
       <c r="R707" s="2"/>
       <c r="S707" s="2"/>
     </row>
-    <row r="708" spans="1:19" ht="13.2">
+    <row r="708" spans="1:19" ht="12.75">
       <c r="A708" s="2"/>
       <c r="B708" s="2"/>
       <c r="C708" s="2"/>
@@ -18448,7 +18451,7 @@
       <c r="R708" s="2"/>
       <c r="S708" s="2"/>
     </row>
-    <row r="709" spans="1:19" ht="13.2">
+    <row r="709" spans="1:19" ht="12.75">
       <c r="A709" s="2"/>
       <c r="B709" s="2"/>
       <c r="C709" s="2"/>
@@ -18469,7 +18472,7 @@
       <c r="R709" s="2"/>
       <c r="S709" s="2"/>
     </row>
-    <row r="710" spans="1:19" ht="13.2">
+    <row r="710" spans="1:19" ht="12.75">
       <c r="A710" s="2"/>
       <c r="B710" s="2"/>
       <c r="C710" s="2"/>
@@ -18490,7 +18493,7 @@
       <c r="R710" s="2"/>
       <c r="S710" s="2"/>
     </row>
-    <row r="711" spans="1:19" ht="13.2">
+    <row r="711" spans="1:19" ht="12.75">
       <c r="A711" s="2"/>
       <c r="B711" s="2"/>
       <c r="C711" s="2"/>
@@ -18511,7 +18514,7 @@
       <c r="R711" s="2"/>
       <c r="S711" s="2"/>
     </row>
-    <row r="712" spans="1:19" ht="13.2">
+    <row r="712" spans="1:19" ht="12.75">
       <c r="A712" s="2"/>
       <c r="B712" s="2"/>
       <c r="C712" s="2"/>
@@ -18532,7 +18535,7 @@
       <c r="R712" s="2"/>
       <c r="S712" s="2"/>
     </row>
-    <row r="713" spans="1:19" ht="13.2">
+    <row r="713" spans="1:19" ht="12.75">
       <c r="A713" s="2"/>
       <c r="B713" s="2"/>
       <c r="C713" s="2"/>
@@ -18553,7 +18556,7 @@
       <c r="R713" s="2"/>
       <c r="S713" s="2"/>
     </row>
-    <row r="714" spans="1:19" ht="13.2">
+    <row r="714" spans="1:19" ht="12.75">
       <c r="A714" s="2"/>
       <c r="B714" s="2"/>
       <c r="C714" s="2"/>
@@ -18574,7 +18577,7 @@
       <c r="R714" s="2"/>
       <c r="S714" s="2"/>
     </row>
-    <row r="715" spans="1:19" ht="13.2">
+    <row r="715" spans="1:19" ht="12.75">
       <c r="A715" s="2"/>
       <c r="B715" s="2"/>
       <c r="C715" s="2"/>
@@ -18595,7 +18598,7 @@
       <c r="R715" s="2"/>
       <c r="S715" s="2"/>
     </row>
-    <row r="716" spans="1:19" ht="13.2">
+    <row r="716" spans="1:19" ht="12.75">
       <c r="A716" s="2"/>
       <c r="B716" s="2"/>
       <c r="C716" s="2"/>
@@ -18616,7 +18619,7 @@
       <c r="R716" s="2"/>
       <c r="S716" s="2"/>
     </row>
-    <row r="717" spans="1:19" ht="13.2">
+    <row r="717" spans="1:19" ht="12.75">
       <c r="A717" s="2"/>
       <c r="B717" s="2"/>
       <c r="C717" s="2"/>
@@ -18637,7 +18640,7 @@
       <c r="R717" s="2"/>
       <c r="S717" s="2"/>
     </row>
-    <row r="718" spans="1:19" ht="13.2">
+    <row r="718" spans="1:19" ht="12.75">
       <c r="A718" s="2"/>
       <c r="B718" s="2"/>
       <c r="C718" s="2"/>
@@ -18658,7 +18661,7 @@
       <c r="R718" s="2"/>
       <c r="S718" s="2"/>
     </row>
-    <row r="719" spans="1:19" ht="13.2">
+    <row r="719" spans="1:19" ht="12.75">
       <c r="A719" s="2"/>
       <c r="B719" s="2"/>
       <c r="C719" s="2"/>
@@ -18679,7 +18682,7 @@
       <c r="R719" s="2"/>
       <c r="S719" s="2"/>
     </row>
-    <row r="720" spans="1:19" ht="13.2">
+    <row r="720" spans="1:19" ht="12.75">
       <c r="A720" s="2"/>
       <c r="B720" s="2"/>
       <c r="C720" s="2"/>
@@ -18700,7 +18703,7 @@
       <c r="R720" s="2"/>
       <c r="S720" s="2"/>
     </row>
-    <row r="721" spans="1:19" ht="13.2">
+    <row r="721" spans="1:19" ht="12.75">
       <c r="A721" s="2"/>
       <c r="B721" s="2"/>
       <c r="C721" s="2"/>
@@ -18721,7 +18724,7 @@
       <c r="R721" s="2"/>
       <c r="S721" s="2"/>
     </row>
-    <row r="722" spans="1:19" ht="13.2">
+    <row r="722" spans="1:19" ht="12.75">
       <c r="A722" s="2"/>
       <c r="B722" s="2"/>
       <c r="C722" s="2"/>
@@ -18742,7 +18745,7 @@
       <c r="R722" s="2"/>
       <c r="S722" s="2"/>
     </row>
-    <row r="723" spans="1:19" ht="13.2">
+    <row r="723" spans="1:19" ht="12.75">
       <c r="A723" s="2"/>
       <c r="B723" s="2"/>
       <c r="C723" s="2"/>
@@ -18763,7 +18766,7 @@
       <c r="R723" s="2"/>
       <c r="S723" s="2"/>
     </row>
-    <row r="724" spans="1:19" ht="13.2">
+    <row r="724" spans="1:19" ht="12.75">
       <c r="A724" s="2"/>
       <c r="B724" s="2"/>
       <c r="C724" s="2"/>
@@ -18784,7 +18787,7 @@
       <c r="R724" s="2"/>
       <c r="S724" s="2"/>
     </row>
-    <row r="725" spans="1:19" ht="13.2">
+    <row r="725" spans="1:19" ht="12.75">
       <c r="A725" s="2"/>
       <c r="B725" s="2"/>
       <c r="C725" s="2"/>
@@ -18805,7 +18808,7 @@
       <c r="R725" s="2"/>
       <c r="S725" s="2"/>
     </row>
-    <row r="726" spans="1:19" ht="13.2">
+    <row r="726" spans="1:19" ht="12.75">
       <c r="A726" s="2"/>
       <c r="B726" s="2"/>
       <c r="C726" s="2"/>
@@ -18826,7 +18829,7 @@
       <c r="R726" s="2"/>
       <c r="S726" s="2"/>
     </row>
-    <row r="727" spans="1:19" ht="13.2">
+    <row r="727" spans="1:19" ht="12.75">
       <c r="A727" s="2"/>
       <c r="B727" s="2"/>
       <c r="C727" s="2"/>
@@ -18847,7 +18850,7 @@
       <c r="R727" s="2"/>
       <c r="S727" s="2"/>
     </row>
-    <row r="728" spans="1:19" ht="13.2">
+    <row r="728" spans="1:19" ht="12.75">
       <c r="A728" s="2"/>
       <c r="B728" s="2"/>
       <c r="C728" s="2"/>
@@ -18868,7 +18871,7 @@
       <c r="R728" s="2"/>
       <c r="S728" s="2"/>
     </row>
-    <row r="729" spans="1:19" ht="13.2">
+    <row r="729" spans="1:19" ht="12.75">
       <c r="A729" s="2"/>
       <c r="B729" s="2"/>
       <c r="C729" s="2"/>
@@ -18889,7 +18892,7 @@
       <c r="R729" s="2"/>
       <c r="S729" s="2"/>
     </row>
-    <row r="730" spans="1:19" ht="13.2">
+    <row r="730" spans="1:19" ht="12.75">
       <c r="A730" s="2"/>
       <c r="B730" s="2"/>
       <c r="C730" s="2"/>
@@ -18910,7 +18913,7 @@
       <c r="R730" s="2"/>
       <c r="S730" s="2"/>
     </row>
-    <row r="731" spans="1:19" ht="13.2">
+    <row r="731" spans="1:19" ht="12.75">
       <c r="A731" s="2"/>
       <c r="B731" s="2"/>
       <c r="C731" s="2"/>
@@ -18931,7 +18934,7 @@
       <c r="R731" s="2"/>
       <c r="S731" s="2"/>
     </row>
-    <row r="732" spans="1:19" ht="13.2">
+    <row r="732" spans="1:19" ht="12.75">
       <c r="A732" s="2"/>
       <c r="B732" s="2"/>
       <c r="C732" s="2"/>
@@ -18952,7 +18955,7 @@
       <c r="R732" s="2"/>
       <c r="S732" s="2"/>
     </row>
-    <row r="733" spans="1:19" ht="13.2">
+    <row r="733" spans="1:19" ht="12.75">
       <c r="A733" s="2"/>
       <c r="B733" s="2"/>
       <c r="C733" s="2"/>
@@ -18973,7 +18976,7 @@
       <c r="R733" s="2"/>
       <c r="S733" s="2"/>
     </row>
-    <row r="734" spans="1:19" ht="13.2">
+    <row r="734" spans="1:19" ht="12.75">
       <c r="A734" s="2"/>
       <c r="B734" s="2"/>
       <c r="C734" s="2"/>
@@ -18994,7 +18997,7 @@
       <c r="R734" s="2"/>
       <c r="S734" s="2"/>
     </row>
-    <row r="735" spans="1:19" ht="13.2">
+    <row r="735" spans="1:19" ht="12.75">
       <c r="A735" s="2"/>
       <c r="B735" s="2"/>
       <c r="C735" s="2"/>
@@ -19015,7 +19018,7 @@
       <c r="R735" s="2"/>
       <c r="S735" s="2"/>
     </row>
-    <row r="736" spans="1:19" ht="13.2">
+    <row r="736" spans="1:19" ht="12.75">
       <c r="A736" s="2"/>
       <c r="B736" s="2"/>
       <c r="C736" s="2"/>
@@ -19036,7 +19039,7 @@
       <c r="R736" s="2"/>
       <c r="S736" s="2"/>
     </row>
-    <row r="737" spans="1:19" ht="13.2">
+    <row r="737" spans="1:19" ht="12.75">
       <c r="A737" s="2"/>
       <c r="B737" s="2"/>
       <c r="C737" s="2"/>
@@ -19057,7 +19060,7 @@
       <c r="R737" s="2"/>
       <c r="S737" s="2"/>
     </row>
-    <row r="738" spans="1:19" ht="13.2">
+    <row r="738" spans="1:19" ht="12.75">
       <c r="A738" s="2"/>
       <c r="B738" s="2"/>
       <c r="C738" s="2"/>
@@ -19078,7 +19081,7 @@
       <c r="R738" s="2"/>
       <c r="S738" s="2"/>
     </row>
-    <row r="739" spans="1:19" ht="13.2">
+    <row r="739" spans="1:19" ht="12.75">
       <c r="A739" s="2"/>
       <c r="B739" s="2"/>
       <c r="C739" s="2"/>
@@ -19099,7 +19102,7 @@
       <c r="R739" s="2"/>
       <c r="S739" s="2"/>
     </row>
-    <row r="740" spans="1:19" ht="13.2">
+    <row r="740" spans="1:19" ht="12.75">
       <c r="A740" s="2"/>
       <c r="B740" s="2"/>
       <c r="C740" s="2"/>
@@ -19120,7 +19123,7 @@
       <c r="R740" s="2"/>
       <c r="S740" s="2"/>
     </row>
-    <row r="741" spans="1:19" ht="13.2">
+    <row r="741" spans="1:19" ht="12.75">
       <c r="A741" s="2"/>
       <c r="B741" s="2"/>
       <c r="C741" s="2"/>
@@ -19141,7 +19144,7 @@
       <c r="R741" s="2"/>
       <c r="S741" s="2"/>
     </row>
-    <row r="742" spans="1:19" ht="13.2">
+    <row r="742" spans="1:19" ht="12.75">
       <c r="A742" s="2"/>
       <c r="B742" s="2"/>
       <c r="C742" s="2"/>
@@ -19162,7 +19165,7 @@
       <c r="R742" s="2"/>
       <c r="S742" s="2"/>
     </row>
-    <row r="743" spans="1:19" ht="13.2">
+    <row r="743" spans="1:19" ht="12.75">
       <c r="A743" s="2"/>
       <c r="B743" s="2"/>
       <c r="C743" s="2"/>
@@ -19183,7 +19186,7 @@
       <c r="R743" s="2"/>
       <c r="S743" s="2"/>
     </row>
-    <row r="744" spans="1:19" ht="13.2">
+    <row r="744" spans="1:19" ht="12.75">
       <c r="A744" s="2"/>
       <c r="B744" s="2"/>
       <c r="C744" s="2"/>
@@ -19204,7 +19207,7 @@
       <c r="R744" s="2"/>
       <c r="S744" s="2"/>
     </row>
-    <row r="745" spans="1:19" ht="13.2">
+    <row r="745" spans="1:19" ht="12.75">
       <c r="A745" s="2"/>
       <c r="B745" s="2"/>
       <c r="C745" s="2"/>
@@ -19225,7 +19228,7 @@
       <c r="R745" s="2"/>
       <c r="S745" s="2"/>
     </row>
-    <row r="746" spans="1:19" ht="13.2">
+    <row r="746" spans="1:19" ht="12.75">
       <c r="A746" s="2"/>
       <c r="B746" s="2"/>
       <c r="C746" s="2"/>
@@ -19246,7 +19249,7 @@
       <c r="R746" s="2"/>
       <c r="S746" s="2"/>
     </row>
-    <row r="747" spans="1:19" ht="13.2">
+    <row r="747" spans="1:19" ht="12.75">
       <c r="A747" s="2"/>
       <c r="B747" s="2"/>
       <c r="C747" s="2"/>
@@ -19267,7 +19270,7 @@
       <c r="R747" s="2"/>
       <c r="S747" s="2"/>
     </row>
-    <row r="748" spans="1:19" ht="13.2">
+    <row r="748" spans="1:19" ht="12.75">
       <c r="A748" s="2"/>
       <c r="B748" s="2"/>
       <c r="C748" s="2"/>
@@ -19288,7 +19291,7 @@
       <c r="R748" s="2"/>
       <c r="S748" s="2"/>
     </row>
-    <row r="749" spans="1:19" ht="13.2">
+    <row r="749" spans="1:19" ht="12.75">
       <c r="A749" s="2"/>
       <c r="B749" s="2"/>
       <c r="C749" s="2"/>
@@ -19309,7 +19312,7 @@
       <c r="R749" s="2"/>
       <c r="S749" s="2"/>
     </row>
-    <row r="750" spans="1:19" ht="13.2">
+    <row r="750" spans="1:19" ht="12.75">
       <c r="A750" s="2"/>
       <c r="B750" s="2"/>
       <c r="C750" s="2"/>
@@ -19330,7 +19333,7 @@
       <c r="R750" s="2"/>
       <c r="S750" s="2"/>
     </row>
-    <row r="751" spans="1:19" ht="13.2">
+    <row r="751" spans="1:19" ht="12.75">
       <c r="A751" s="2"/>
       <c r="B751" s="2"/>
       <c r="C751" s="2"/>
@@ -19351,7 +19354,7 @@
       <c r="R751" s="2"/>
       <c r="S751" s="2"/>
     </row>
-    <row r="752" spans="1:19" ht="13.2">
+    <row r="752" spans="1:19" ht="12.75">
       <c r="A752" s="2"/>
       <c r="B752" s="2"/>
       <c r="C752" s="2"/>
@@ -19372,7 +19375,7 @@
       <c r="R752" s="2"/>
       <c r="S752" s="2"/>
     </row>
-    <row r="753" spans="1:19" ht="13.2">
+    <row r="753" spans="1:19" ht="12.75">
       <c r="A753" s="2"/>
       <c r="B753" s="2"/>
       <c r="C753" s="2"/>
@@ -19393,7 +19396,7 @@
       <c r="R753" s="2"/>
       <c r="S753" s="2"/>
     </row>
-    <row r="754" spans="1:19" ht="13.2">
+    <row r="754" spans="1:19" ht="12.75">
       <c r="A754" s="2"/>
       <c r="B754" s="2"/>
       <c r="C754" s="2"/>
@@ -19414,7 +19417,7 @@
       <c r="R754" s="2"/>
       <c r="S754" s="2"/>
     </row>
-    <row r="755" spans="1:19" ht="13.2">
+    <row r="755" spans="1:19" ht="12.75">
       <c r="A755" s="2"/>
       <c r="B755" s="2"/>
       <c r="C755" s="2"/>
@@ -19435,7 +19438,7 @@
       <c r="R755" s="2"/>
       <c r="S755" s="2"/>
     </row>
-    <row r="756" spans="1:19" ht="13.2">
+    <row r="756" spans="1:19" ht="12.75">
       <c r="A756" s="2"/>
       <c r="B756" s="2"/>
       <c r="C756" s="2"/>
@@ -19456,7 +19459,7 @@
       <c r="R756" s="2"/>
       <c r="S756" s="2"/>
     </row>
-    <row r="757" spans="1:19" ht="13.2">
+    <row r="757" spans="1:19" ht="12.75">
       <c r="A757" s="2"/>
       <c r="B757" s="2"/>
       <c r="C757" s="2"/>
@@ -19477,7 +19480,7 @@
       <c r="R757" s="2"/>
       <c r="S757" s="2"/>
     </row>
-    <row r="758" spans="1:19" ht="13.2">
+    <row r="758" spans="1:19" ht="12.75">
       <c r="A758" s="2"/>
       <c r="B758" s="2"/>
       <c r="C758" s="2"/>
@@ -19498,7 +19501,7 @@
       <c r="R758" s="2"/>
       <c r="S758" s="2"/>
     </row>
-    <row r="759" spans="1:19" ht="13.2">
+    <row r="759" spans="1:19" ht="12.75">
       <c r="A759" s="2"/>
       <c r="B759" s="2"/>
       <c r="C759" s="2"/>
@@ -19519,7 +19522,7 @@
       <c r="R759" s="2"/>
       <c r="S759" s="2"/>
     </row>
-    <row r="760" spans="1:19" ht="13.2">
+    <row r="760" spans="1:19" ht="12.75">
       <c r="A760" s="2"/>
       <c r="B760" s="2"/>
       <c r="C760" s="2"/>
@@ -19540,7 +19543,7 @@
       <c r="R760" s="2"/>
       <c r="S760" s="2"/>
     </row>
-    <row r="761" spans="1:19" ht="13.2">
+    <row r="761" spans="1:19" ht="12.75">
       <c r="A761" s="2"/>
       <c r="B761" s="2"/>
       <c r="C761" s="2"/>
@@ -19561,7 +19564,7 @@
       <c r="R761" s="2"/>
       <c r="S761" s="2"/>
     </row>
-    <row r="762" spans="1:19" ht="13.2">
+    <row r="762" spans="1:19" ht="12.75">
       <c r="A762" s="2"/>
       <c r="B762" s="2"/>
       <c r="C762" s="2"/>
@@ -19582,7 +19585,7 @@
       <c r="R762" s="2"/>
       <c r="S762" s="2"/>
     </row>
-    <row r="763" spans="1:19" ht="13.2">
+    <row r="763" spans="1:19" ht="12.75">
       <c r="A763" s="2"/>
       <c r="B763" s="2"/>
       <c r="C763" s="2"/>
@@ -19603,7 +19606,7 @@
       <c r="R763" s="2"/>
       <c r="S763" s="2"/>
     </row>
-    <row r="764" spans="1:19" ht="13.2">
+    <row r="764" spans="1:19" ht="12.75">
       <c r="A764" s="2"/>
       <c r="B764" s="2"/>
       <c r="C764" s="2"/>
@@ -19624,7 +19627,7 @@
       <c r="R764" s="2"/>
       <c r="S764" s="2"/>
     </row>
-    <row r="765" spans="1:19" ht="13.2">
+    <row r="765" spans="1:19" ht="12.75">
       <c r="A765" s="2"/>
       <c r="B765" s="2"/>
       <c r="C765" s="2"/>
@@ -19645,7 +19648,7 @@
       <c r="R765" s="2"/>
       <c r="S765" s="2"/>
     </row>
-    <row r="766" spans="1:19" ht="13.2">
+    <row r="766" spans="1:19" ht="12.75">
       <c r="A766" s="2"/>
       <c r="B766" s="2"/>
       <c r="C766" s="2"/>
@@ -19666,7 +19669,7 @@
       <c r="R766" s="2"/>
       <c r="S766" s="2"/>
     </row>
-    <row r="767" spans="1:19" ht="13.2">
+    <row r="767" spans="1:19" ht="12.75">
       <c r="A767" s="2"/>
       <c r="B767" s="2"/>
       <c r="C767" s="2"/>
@@ -19687,7 +19690,7 @@
       <c r="R767" s="2"/>
       <c r="S767" s="2"/>
     </row>
-    <row r="768" spans="1:19" ht="13.2">
+    <row r="768" spans="1:19" ht="12.75">
       <c r="A768" s="2"/>
       <c r="B768" s="2"/>
       <c r="C768" s="2"/>
@@ -19708,7 +19711,7 @@
       <c r="R768" s="2"/>
       <c r="S768" s="2"/>
     </row>
-    <row r="769" spans="1:19" ht="13.2">
+    <row r="769" spans="1:19" ht="12.75">
       <c r="A769" s="2"/>
       <c r="B769" s="2"/>
       <c r="C769" s="2"/>
@@ -19729,7 +19732,7 @@
       <c r="R769" s="2"/>
       <c r="S769" s="2"/>
     </row>
-    <row r="770" spans="1:19" ht="13.2">
+    <row r="770" spans="1:19" ht="12.75">
       <c r="A770" s="2"/>
       <c r="B770" s="2"/>
       <c r="C770" s="2"/>
@@ -19750,7 +19753,7 @@
       <c r="R770" s="2"/>
       <c r="S770" s="2"/>
     </row>
-    <row r="771" spans="1:19" ht="13.2">
+    <row r="771" spans="1:19" ht="12.75">
       <c r="A771" s="2"/>
       <c r="B771" s="2"/>
       <c r="C771" s="2"/>
@@ -19771,7 +19774,7 @@
       <c r="R771" s="2"/>
       <c r="S771" s="2"/>
     </row>
-    <row r="772" spans="1:19" ht="13.2">
+    <row r="772" spans="1:19" ht="12.75">
       <c r="A772" s="2"/>
       <c r="B772" s="2"/>
       <c r="C772" s="2"/>
@@ -19792,7 +19795,7 @@
       <c r="R772" s="2"/>
       <c r="S772" s="2"/>
     </row>
-    <row r="773" spans="1:19" ht="13.2">
+    <row r="773" spans="1:19" ht="12.75">
       <c r="A773" s="2"/>
       <c r="B773" s="2"/>
       <c r="C773" s="2"/>
@@ -19813,7 +19816,7 @@
       <c r="R773" s="2"/>
       <c r="S773" s="2"/>
     </row>
-    <row r="774" spans="1:19" ht="13.2">
+    <row r="774" spans="1:19" ht="12.75">
       <c r="A774" s="2"/>
       <c r="B774" s="2"/>
       <c r="C774" s="2"/>
@@ -19834,7 +19837,7 @@
       <c r="R774" s="2"/>
       <c r="S774" s="2"/>
     </row>
-    <row r="775" spans="1:19" ht="13.2">
+    <row r="775" spans="1:19" ht="12.75">
       <c r="A775" s="2"/>
       <c r="B775" s="2"/>
       <c r="C775" s="2"/>
@@ -19855,7 +19858,7 @@
       <c r="R775" s="2"/>
       <c r="S775" s="2"/>
     </row>
-    <row r="776" spans="1:19" ht="13.2">
+    <row r="776" spans="1:19" ht="12.75">
       <c r="A776" s="2"/>
       <c r="B776" s="2"/>
       <c r="C776" s="2"/>
@@ -19876,7 +19879,7 @@
       <c r="R776" s="2"/>
       <c r="S776" s="2"/>
     </row>
-    <row r="777" spans="1:19" ht="13.2">
+    <row r="777" spans="1:19" ht="12.75">
       <c r="A777" s="2"/>
       <c r="B777" s="2"/>
       <c r="C777" s="2"/>
@@ -19897,7 +19900,7 @@
       <c r="R777" s="2"/>
       <c r="S777" s="2"/>
     </row>
-    <row r="778" spans="1:19" ht="13.2">
+    <row r="778" spans="1:19" ht="12.75">
       <c r="A778" s="2"/>
       <c r="B778" s="2"/>
       <c r="C778" s="2"/>
@@ -19918,7 +19921,7 @@
       <c r="R778" s="2"/>
       <c r="S778" s="2"/>
     </row>
-    <row r="779" spans="1:19" ht="13.2">
+    <row r="779" spans="1:19" ht="12.75">
       <c r="A779" s="2"/>
       <c r="B779" s="2"/>
       <c r="C779" s="2"/>
@@ -19939,7 +19942,7 @@
       <c r="R779" s="2"/>
       <c r="S779" s="2"/>
     </row>
-    <row r="780" spans="1:19" ht="13.2">
+    <row r="780" spans="1:19" ht="12.75">
       <c r="A780" s="2"/>
       <c r="B780" s="2"/>
       <c r="C780" s="2"/>
@@ -19960,7 +19963,7 @@
       <c r="R780" s="2"/>
       <c r="S780" s="2"/>
     </row>
-    <row r="781" spans="1:19" ht="13.2">
+    <row r="781" spans="1:19" ht="12.75">
       <c r="A781" s="2"/>
       <c r="B781" s="2"/>
       <c r="C781" s="2"/>
@@ -19981,7 +19984,7 @@
       <c r="R781" s="2"/>
       <c r="S781" s="2"/>
     </row>
-    <row r="782" spans="1:19" ht="13.2">
+    <row r="782" spans="1:19" ht="12.75">
       <c r="A782" s="2"/>
       <c r="B782" s="2"/>
       <c r="C782" s="2"/>
@@ -20002,7 +20005,7 @@
       <c r="R782" s="2"/>
       <c r="S782" s="2"/>
     </row>
-    <row r="783" spans="1:19" ht="13.2">
+    <row r="783" spans="1:19" ht="12.75">
       <c r="A783" s="2"/>
       <c r="B783" s="2"/>
       <c r="C783" s="2"/>
@@ -20023,7 +20026,7 @@
       <c r="R783" s="2"/>
       <c r="S783" s="2"/>
     </row>
-    <row r="784" spans="1:19" ht="13.2">
+    <row r="784" spans="1:19" ht="12.75">
       <c r="A784" s="2"/>
       <c r="B784" s="2"/>
       <c r="C784" s="2"/>
@@ -20044,7 +20047,7 @@
       <c r="R784" s="2"/>
       <c r="S784" s="2"/>
     </row>
-    <row r="785" spans="1:19" ht="13.2">
+    <row r="785" spans="1:19" ht="12.75">
       <c r="A785" s="2"/>
       <c r="B785" s="2"/>
       <c r="C785" s="2"/>
@@ -20065,7 +20068,7 @@
       <c r="R785" s="2"/>
       <c r="S785" s="2"/>
     </row>
-    <row r="786" spans="1:19" ht="13.2">
+    <row r="786" spans="1:19" ht="12.75">
       <c r="A786" s="2"/>
       <c r="B786" s="2"/>
       <c r="C786" s="2"/>
@@ -20086,7 +20089,7 @@
       <c r="R786" s="2"/>
       <c r="S786" s="2"/>
     </row>
-    <row r="787" spans="1:19" ht="13.2">
+    <row r="787" spans="1:19" ht="12.75">
       <c r="A787" s="2"/>
       <c r="B787" s="2"/>
       <c r="C787" s="2"/>
@@ -20107,7 +20110,7 @@
       <c r="R787" s="2"/>
       <c r="S787" s="2"/>
     </row>
-    <row r="788" spans="1:19" ht="13.2">
+    <row r="788" spans="1:19" ht="12.75">
       <c r="A788" s="2"/>
       <c r="B788" s="2"/>
       <c r="C788" s="2"/>
@@ -20128,7 +20131,7 @@
       <c r="R788" s="2"/>
       <c r="S788" s="2"/>
     </row>
-    <row r="789" spans="1:19" ht="13.2">
+    <row r="789" spans="1:19" ht="12.75">
       <c r="A789" s="2"/>
       <c r="B789" s="2"/>
       <c r="C789" s="2"/>
@@ -20149,7 +20152,7 @@
       <c r="R789" s="2"/>
       <c r="S789" s="2"/>
     </row>
-    <row r="790" spans="1:19" ht="13.2">
+    <row r="790" spans="1:19" ht="12.75">
       <c r="A790" s="2"/>
       <c r="B790" s="2"/>
       <c r="C790" s="2"/>
@@ -20170,7 +20173,7 @@
       <c r="R790" s="2"/>
       <c r="S790" s="2"/>
     </row>
-    <row r="791" spans="1:19" ht="13.2">
+    <row r="791" spans="1:19" ht="12.75">
       <c r="A791" s="2"/>
       <c r="B791" s="2"/>
       <c r="C791" s="2"/>
@@ -20191,7 +20194,7 @@
       <c r="R791" s="2"/>
       <c r="S791" s="2"/>
     </row>
-    <row r="792" spans="1:19" ht="13.2">
+    <row r="792" spans="1:19" ht="12.75">
       <c r="A792" s="2"/>
       <c r="B792" s="2"/>
       <c r="C792" s="2"/>
@@ -20212,7 +20215,7 @@
       <c r="R792" s="2"/>
       <c r="S792" s="2"/>
     </row>
-    <row r="793" spans="1:19" ht="13.2">
+    <row r="793" spans="1:19" ht="12.75">
       <c r="A793" s="2"/>
       <c r="B793" s="2"/>
       <c r="C793" s="2"/>
@@ -20233,7 +20236,7 @@
       <c r="R793" s="2"/>
       <c r="S793" s="2"/>
     </row>
-    <row r="794" spans="1:19" ht="13.2">
+    <row r="794" spans="1:19" ht="12.75">
       <c r="A794" s="2"/>
       <c r="B794" s="2"/>
       <c r="C794" s="2"/>
@@ -20254,7 +20257,7 @@
       <c r="R794" s="2"/>
       <c r="S794" s="2"/>
     </row>
-    <row r="795" spans="1:19" ht="13.2">
+    <row r="795" spans="1:19" ht="12.75">
       <c r="A795" s="2"/>
       <c r="B795" s="2"/>
       <c r="C795" s="2"/>
@@ -20275,7 +20278,7 @@
       <c r="R795" s="2"/>
       <c r="S795" s="2"/>
     </row>
-    <row r="796" spans="1:19" ht="13.2">
+    <row r="796" spans="1:19" ht="12.75">
       <c r="A796" s="2"/>
       <c r="B796" s="2"/>
       <c r="C796" s="2"/>
@@ -20296,7 +20299,7 @@
       <c r="R796" s="2"/>
       <c r="S796" s="2"/>
     </row>
-    <row r="797" spans="1:19" ht="13.2">
+    <row r="797" spans="1:19" ht="12.75">
       <c r="A797" s="2"/>
       <c r="B797" s="2"/>
       <c r="C797" s="2"/>
@@ -20317,7 +20320,7 @@
       <c r="R797" s="2"/>
       <c r="S797" s="2"/>
     </row>
-    <row r="798" spans="1:19" ht="13.2">
+    <row r="798" spans="1:19" ht="12.75">
       <c r="A798" s="2"/>
       <c r="B798" s="2"/>
       <c r="C798" s="2"/>
@@ -20338,7 +20341,7 @@
       <c r="R798" s="2"/>
       <c r="S798" s="2"/>
     </row>
-    <row r="799" spans="1:19" ht="13.2">
+    <row r="799" spans="1:19" ht="12.75">
       <c r="A799" s="2"/>
       <c r="B799" s="2"/>
       <c r="C799" s="2"/>
@@ -20359,7 +20362,7 @@
       <c r="R799" s="2"/>
       <c r="S799" s="2"/>
     </row>
-    <row r="800" spans="1:19" ht="13.2">
+    <row r="800" spans="1:19" ht="12.75">
       <c r="A800" s="2"/>
       <c r="B800" s="2"/>
       <c r="C800" s="2"/>
@@ -20380,7 +20383,7 @@
       <c r="R800" s="2"/>
       <c r="S800" s="2"/>
     </row>
-    <row r="801" spans="1:19" ht="13.2">
+    <row r="801" spans="1:19" ht="12.75">
       <c r="A801" s="2"/>
       <c r="B801" s="2"/>
       <c r="C801" s="2"/>
@@ -20401,7 +20404,7 @@
       <c r="R801" s="2"/>
       <c r="S801" s="2"/>
     </row>
-    <row r="802" spans="1:19" ht="13.2">
+    <row r="802" spans="1:19" ht="12.75">
       <c r="A802" s="2"/>
       <c r="B802" s="2"/>
       <c r="C802" s="2"/>
@@ -20422,7 +20425,7 @@
       <c r="R802" s="2"/>
       <c r="S802" s="2"/>
     </row>
-    <row r="803" spans="1:19" ht="13.2">
+    <row r="803" spans="1:19" ht="12.75">
       <c r="A803" s="2"/>
       <c r="B803" s="2"/>
       <c r="C803" s="2"/>
@@ -20443,7 +20446,7 @@
       <c r="R803" s="2"/>
       <c r="S803" s="2"/>
     </row>
-    <row r="804" spans="1:19" ht="13.2">
+    <row r="804" spans="1:19" ht="12.75">
       <c r="A804" s="2"/>
       <c r="B804" s="2"/>
       <c r="C804" s="2"/>
@@ -20464,7 +20467,7 @@
       <c r="R804" s="2"/>
       <c r="S804" s="2"/>
     </row>
-    <row r="805" spans="1:19" ht="13.2">
+    <row r="805" spans="1:19" ht="12.75">
       <c r="A805" s="2"/>
       <c r="B805" s="2"/>
       <c r="C805" s="2"/>
@@ -20485,7 +20488,7 @@
       <c r="R805" s="2"/>
       <c r="S805" s="2"/>
     </row>
-    <row r="806" spans="1:19" ht="13.2">
+    <row r="806" spans="1:19" ht="12.75">
       <c r="A806" s="2"/>
       <c r="B806" s="2"/>
       <c r="C806" s="2"/>
@@ -20506,7 +20509,7 @@
       <c r="R806" s="2"/>
       <c r="S806" s="2"/>
     </row>
-    <row r="807" spans="1:19" ht="13.2">
+    <row r="807" spans="1:19" ht="12.75">
       <c r="A807" s="2"/>
       <c r="B807" s="2"/>
       <c r="C807" s="2"/>
@@ -20527,7 +20530,7 @@
       <c r="R807" s="2"/>
       <c r="S807" s="2"/>
     </row>
-    <row r="808" spans="1:19" ht="13.2">
+    <row r="808" spans="1:19" ht="12.75">
       <c r="A808" s="2"/>
       <c r="B808" s="2"/>
       <c r="C808" s="2"/>
@@ -20548,7 +20551,7 @@
       <c r="R808" s="2"/>
       <c r="S808" s="2"/>
     </row>
-    <row r="809" spans="1:19" ht="13.2">
+    <row r="809" spans="1:19" ht="12.75">
       <c r="A809" s="2"/>
       <c r="B809" s="2"/>
       <c r="C809" s="2"/>
@@ -20569,7 +20572,7 @@
       <c r="R809" s="2"/>
       <c r="S809" s="2"/>
     </row>
-    <row r="810" spans="1:19" ht="13.2">
+    <row r="810" spans="1:19" ht="12.75">
       <c r="A810" s="2"/>
       <c r="B810" s="2"/>
       <c r="C810" s="2"/>
@@ -20590,7 +20593,7 @@
       <c r="R810" s="2"/>
       <c r="S810" s="2"/>
     </row>
-    <row r="811" spans="1:19" ht="13.2">
+    <row r="811" spans="1:19" ht="12.75">
       <c r="A811" s="2"/>
       <c r="B811" s="2"/>
       <c r="C811" s="2"/>
@@ -20611,7 +20614,7 @@
       <c r="R811" s="2"/>
       <c r="S811" s="2"/>
     </row>
-    <row r="812" spans="1:19" ht="13.2">
+    <row r="812" spans="1:19" ht="12.75">
       <c r="A812" s="2"/>
       <c r="B812" s="2"/>
       <c r="C812" s="2"/>
@@ -20632,7 +20635,7 @@
       <c r="R812" s="2"/>
       <c r="S812" s="2"/>
     </row>
-    <row r="813" spans="1:19" ht="13.2">
+    <row r="813" spans="1:19" ht="12.75">
       <c r="A813" s="2"/>
       <c r="B813" s="2"/>
       <c r="C813" s="2"/>
@@ -20653,7 +20656,7 @@
       <c r="R813" s="2"/>
       <c r="S813" s="2"/>
     </row>
-    <row r="814" spans="1:19" ht="13.2">
+    <row r="814" spans="1:19" ht="12.75">
       <c r="A814" s="2"/>
       <c r="B814" s="2"/>
       <c r="C814" s="2"/>
@@ -20674,7 +20677,7 @@
       <c r="R814" s="2"/>
       <c r="S814" s="2"/>
     </row>
-    <row r="815" spans="1:19" ht="13.2">
+    <row r="815" spans="1:19" ht="12.75">
       <c r="A815" s="2"/>
       <c r="B815" s="2"/>
       <c r="C815" s="2"/>
@@ -20695,7 +20698,7 @@
       <c r="R815" s="2"/>
       <c r="S815" s="2"/>
     </row>
-    <row r="816" spans="1:19" ht="13.2">
+    <row r="816" spans="1:19" ht="12.75">
       <c r="A816" s="2"/>
       <c r="B816" s="2"/>
       <c r="C816" s="2"/>
@@ -20716,7 +20719,7 @@
       <c r="R816" s="2"/>
       <c r="S816" s="2"/>
     </row>
-    <row r="817" spans="1:19" ht="13.2">
+    <row r="817" spans="1:19" ht="12.75">
       <c r="A817" s="2"/>
       <c r="B817" s="2"/>
       <c r="C817" s="2"/>
@@ -20737,7 +20740,7 @@
       <c r="R817" s="2"/>
       <c r="S817" s="2"/>
     </row>
-    <row r="818" spans="1:19" ht="13.2">
+    <row r="818" spans="1:19" ht="12.75">
       <c r="A818" s="2"/>
       <c r="B818" s="2"/>
       <c r="C818" s="2"/>
@@ -20758,7 +20761,7 @@
       <c r="R818" s="2"/>
       <c r="S818" s="2"/>
     </row>
-    <row r="819" spans="1:19" ht="13.2">
+    <row r="819" spans="1:19" ht="12.75">
       <c r="A819" s="2"/>
       <c r="B819" s="2"/>
       <c r="C819" s="2"/>
@@ -20779,7 +20782,7 @@
       <c r="R819" s="2"/>
       <c r="S819" s="2"/>
     </row>
-    <row r="820" spans="1:19" ht="13.2">
+    <row r="820" spans="1:19" ht="12.75">
       <c r="A820" s="2"/>
       <c r="B820" s="2"/>
       <c r="C820" s="2"/>
@@ -20800,7 +20803,7 @@
       <c r="R820" s="2"/>
       <c r="S820" s="2"/>
     </row>
-    <row r="821" spans="1:19" ht="13.2">
+    <row r="821" spans="1:19" ht="12.75">
       <c r="A821" s="2"/>
       <c r="B821" s="2"/>
       <c r="C821" s="2"/>
@@ -20821,7 +20824,7 @@
       <c r="R821" s="2"/>
       <c r="S821" s="2"/>
     </row>
-    <row r="822" spans="1:19" ht="13.2">
+    <row r="822" spans="1:19" ht="12.75">
       <c r="A822" s="2"/>
       <c r="B822" s="2"/>
       <c r="C822" s="2"/>
@@ -20842,7 +20845,7 @@
       <c r="R822" s="2"/>
       <c r="S822" s="2"/>
     </row>
-    <row r="823" spans="1:19" ht="13.2">
+    <row r="823" spans="1:19" ht="12.75">
       <c r="A823" s="2"/>
       <c r="B823" s="2"/>
       <c r="C823" s="2"/>
@@ -20863,7 +20866,7 @@
       <c r="R823" s="2"/>
       <c r="S823" s="2"/>
     </row>
-    <row r="824" spans="1:19" ht="13.2">
+    <row r="824" spans="1:19" ht="12.75">
       <c r="A824" s="2"/>
       <c r="B824" s="2"/>
       <c r="C824" s="2"/>
@@ -20884,7 +20887,7 @@
       <c r="R824" s="2"/>
       <c r="S824" s="2"/>
     </row>
-    <row r="825" spans="1:19" ht="13.2">
+    <row r="825" spans="1:19" ht="12.75">
       <c r="A825" s="2"/>
       <c r="B825" s="2"/>
       <c r="C825" s="2"/>
@@ -20905,7 +20908,7 @@
       <c r="R825" s="2"/>
       <c r="S825" s="2"/>
     </row>
-    <row r="826" spans="1:19" ht="13.2">
+    <row r="826" spans="1:19" ht="12.75">
       <c r="A826" s="2"/>
       <c r="B826" s="2"/>
       <c r="C826" s="2"/>
@@ -20926,7 +20929,7 @@
       <c r="R826" s="2"/>
       <c r="S826" s="2"/>
     </row>
-    <row r="827" spans="1:19" ht="13.2">
+    <row r="827" spans="1:19" ht="12.75">
       <c r="A827" s="2"/>
       <c r="B827" s="2"/>
       <c r="C827" s="2"/>
@@ -20947,7 +20950,7 @@
       <c r="R827" s="2"/>
       <c r="S827" s="2"/>
     </row>
-    <row r="828" spans="1:19" ht="13.2">
+    <row r="828" spans="1:19" ht="12.75">
       <c r="A828" s="2"/>
       <c r="B828" s="2"/>
       <c r="C828" s="2"/>
@@ -20968,7 +20971,7 @@
       <c r="R828" s="2"/>
       <c r="S828" s="2"/>
     </row>
-    <row r="829" spans="1:19" ht="13.2">
+    <row r="829" spans="1:19" ht="12.75">
       <c r="A829" s="2"/>
       <c r="B829" s="2"/>
       <c r="C829" s="2"/>
@@ -20989,7 +20992,7 @@
       <c r="R829" s="2"/>
       <c r="S829" s="2"/>
     </row>
-    <row r="830" spans="1:19" ht="13.2">
+    <row r="830" spans="1:19" ht="12.75">
       <c r="A830" s="2"/>
       <c r="B830" s="2"/>
       <c r="C830" s="2"/>
@@ -21010,7 +21013,7 @@
       <c r="R830" s="2"/>
       <c r="S830" s="2"/>
     </row>
-    <row r="831" spans="1:19" ht="13.2">
+    <row r="831" spans="1:19" ht="12.75">
       <c r="A831" s="2"/>
       <c r="B831" s="2"/>
       <c r="C831" s="2"/>
@@ -21031,7 +21034,7 @@
       <c r="R831" s="2"/>
       <c r="S831" s="2"/>
     </row>
-    <row r="832" spans="1:19" ht="13.2">
+    <row r="832" spans="1:19" ht="12.75">
       <c r="A832" s="2"/>
       <c r="B832" s="2"/>
       <c r="C832" s="2"/>
@@ -21052,7 +21055,7 @@
       <c r="R832" s="2"/>
       <c r="S832" s="2"/>
     </row>
-    <row r="833" spans="1:19" ht="13.2">
+    <row r="833" spans="1:19" ht="12.75">
       <c r="A833" s="2"/>
       <c r="B833" s="2"/>
       <c r="C833" s="2"/>
@@ -21073,7 +21076,7 @@
       <c r="R833" s="2"/>
       <c r="S833" s="2"/>
     </row>
-    <row r="834" spans="1:19" ht="13.2">
+    <row r="834" spans="1:19" ht="12.75">
       <c r="A834" s="2"/>
       <c r="B834" s="2"/>
       <c r="C834" s="2"/>
@@ -21094,7 +21097,7 @@
       <c r="R834" s="2"/>
       <c r="S834" s="2"/>
     </row>
-    <row r="835" spans="1:19" ht="13.2">
+    <row r="835" spans="1:19" ht="12.75">
       <c r="A835" s="2"/>
       <c r="B835" s="2"/>
       <c r="C835" s="2"/>
@@ -21115,7 +21118,7 @@
       <c r="R835" s="2"/>
       <c r="S835" s="2"/>
     </row>
-    <row r="836" spans="1:19" ht="13.2">
+    <row r="836" spans="1:19" ht="12.75">
       <c r="A836" s="2"/>
       <c r="B836" s="2"/>
       <c r="C836" s="2"/>
@@ -21136,7 +21139,7 @@
       <c r="R836" s="2"/>
       <c r="S836" s="2"/>
     </row>
-    <row r="837" spans="1:19" ht="13.2">
+    <row r="837" spans="1:19" ht="12.75">
       <c r="A837" s="2"/>
       <c r="B837" s="2"/>
       <c r="C837" s="2"/>
@@ -21157,7 +21160,7 @@
       <c r="R837" s="2"/>
       <c r="S837" s="2"/>
     </row>
-    <row r="838" spans="1:19" ht="13.2">
+    <row r="838" spans="1:19" ht="12.75">
       <c r="A838" s="2"/>
       <c r="B838" s="2"/>
       <c r="C838" s="2"/>
@@ -21178,7 +21181,7 @@
       <c r="R838" s="2"/>
       <c r="S838" s="2"/>
     </row>
-    <row r="839" spans="1:19" ht="13.2">
+    <row r="839" spans="1:19" ht="12.75">
       <c r="A839" s="2"/>
       <c r="B839" s="2"/>
       <c r="C839" s="2"/>
@@ -21199,7 +21202,7 @@
       <c r="R839" s="2"/>
       <c r="S839" s="2"/>
     </row>
-    <row r="840" spans="1:19" ht="13.2">
+    <row r="840" spans="1:19" ht="12.75">
       <c r="A840" s="2"/>
       <c r="B840" s="2"/>
       <c r="C840" s="2"/>
@@ -21220,7 +21223,7 @@
       <c r="R840" s="2"/>
       <c r="S840" s="2"/>
     </row>
-    <row r="841" spans="1:19" ht="13.2">
+    <row r="841" spans="1:19" ht="12.75">
       <c r="A841" s="2"/>
       <c r="B841" s="2"/>
       <c r="C841" s="2"/>
@@ -21241,7 +21244,7 @@
       <c r="R841" s="2"/>
       <c r="S841" s="2"/>
     </row>
-    <row r="842" spans="1:19" ht="13.2">
+    <row r="842" spans="1:19" ht="12.75">
       <c r="A842" s="2"/>
       <c r="B842" s="2"/>
       <c r="C842" s="2"/>
@@ -21262,7 +21265,7 @@
       <c r="R842" s="2"/>
       <c r="S842" s="2"/>
     </row>
-    <row r="843" spans="1:19" ht="13.2">
+    <row r="843" spans="1:19" ht="12.75">
       <c r="A843" s="2"/>
       <c r="B843" s="2"/>
       <c r="C843" s="2"/>
@@ -21283,7 +21286,7 @@
       <c r="R843" s="2"/>
       <c r="S843" s="2"/>
     </row>
-    <row r="844" spans="1:19" ht="13.2">
+    <row r="844" spans="1:19" ht="12.75">
       <c r="A844" s="2"/>
       <c r="B844" s="2"/>
       <c r="C844" s="2"/>
@@ -21304,7 +21307,7 @@
       <c r="R844" s="2"/>
       <c r="S844" s="2"/>
     </row>
-    <row r="845" spans="1:19" ht="13.2">
+    <row r="845" spans="1:19" ht="12.75">
       <c r="A845" s="2"/>
       <c r="B845" s="2"/>
       <c r="C845" s="2"/>
@@ -21325,7 +21328,7 @@
       <c r="R845" s="2"/>
       <c r="S845" s="2"/>
     </row>
-    <row r="846" spans="1:19" ht="13.2">
+    <row r="846" spans="1:19" ht="12.75">
       <c r="A846" s="2"/>
       <c r="B846" s="2"/>
       <c r="C846" s="2"/>
@@ -21346,7 +21349,7 @@
       <c r="R846" s="2"/>
       <c r="S846" s="2"/>
     </row>
-    <row r="847" spans="1:19" ht="13.2">
+    <row r="847" spans="1:19" ht="12.75">
       <c r="A847" s="2"/>
       <c r="B847" s="2"/>
       <c r="C847" s="2"/>
@@ -21367,7 +21370,7 @@
       <c r="R847" s="2"/>
       <c r="S847" s="2"/>
     </row>
-    <row r="848" spans="1:19" ht="13.2">
+    <row r="848" spans="1:19" ht="12.75">
       <c r="A848" s="2"/>
       <c r="B848" s="2"/>
       <c r="C848" s="2"/>
@@ -21388,7 +21391,7 @@
       <c r="R848" s="2"/>
       <c r="S848" s="2"/>
     </row>
-    <row r="849" spans="1:19" ht="13.2">
+    <row r="849" spans="1:19" ht="12.75">
       <c r="A849" s="2"/>
       <c r="B849" s="2"/>
       <c r="C849" s="2"/>
@@ -21409,7 +21412,7 @@
       <c r="R849" s="2"/>
       <c r="S849" s="2"/>
     </row>
-    <row r="850" spans="1:19" ht="13.2">
+    <row r="850" spans="1:19" ht="12.75">
       <c r="A850" s="2"/>
       <c r="B850" s="2"/>
       <c r="C850" s="2"/>
@@ -21430,7 +21433,7 @@
       <c r="R850" s="2"/>
       <c r="S850" s="2"/>
     </row>
-    <row r="851" spans="1:19" ht="13.2">
+    <row r="851" spans="1:19" ht="12.75">
       <c r="A851" s="2"/>
       <c r="B851" s="2"/>
       <c r="C851" s="2"/>
@@ -21451,7 +21454,7 @@
       <c r="R851" s="2"/>
       <c r="S851" s="2"/>
     </row>
-    <row r="852" spans="1:19" ht="13.2">
+    <row r="852" spans="1:19" ht="12.75">
       <c r="A852" s="2"/>
       <c r="B852" s="2"/>
       <c r="C852" s="2"/>
@@ -21472,7 +21475,7 @@
       <c r="R852" s="2"/>
       <c r="S852" s="2"/>
     </row>
-    <row r="853" spans="1:19" ht="13.2">
+    <row r="853" spans="1:19" ht="12.75">
       <c r="A853" s="2"/>
       <c r="B853" s="2"/>
       <c r="C853" s="2"/>
@@ -21493,7 +21496,7 @@
       <c r="R853" s="2"/>
       <c r="S853" s="2"/>
     </row>
-    <row r="854" spans="1:19" ht="13.2">
+    <row r="854" spans="1:19" ht="12.75">
       <c r="A854" s="2"/>
       <c r="B854" s="2"/>
       <c r="C854" s="2"/>
@@ -21514,7 +21517,7 @@
       <c r="R854" s="2"/>
       <c r="S854" s="2"/>
     </row>
-    <row r="855" spans="1:19" ht="13.2">
+    <row r="855" spans="1:19" ht="12.75">
       <c r="A855" s="2"/>
       <c r="B855" s="2"/>
       <c r="C855" s="2"/>
@@ -21535,7 +21538,7 @@
       <c r="R855" s="2"/>
       <c r="S855" s="2"/>
     </row>
-    <row r="856" spans="1:19" ht="13.2">
+    <row r="856" spans="1:19" ht="12.75">
       <c r="A856" s="2"/>
       <c r="B856" s="2"/>
       <c r="C856" s="2"/>
@@ -21556,7 +21559,7 @@
       <c r="R856" s="2"/>
       <c r="S856" s="2"/>
     </row>
-    <row r="857" spans="1:19" ht="13.2">
+    <row r="857" spans="1:19" ht="12.75">
       <c r="A857" s="2"/>
       <c r="B857" s="2"/>
       <c r="C857" s="2"/>
@@ -21577,7 +21580,7 @@
       <c r="R857" s="2"/>
       <c r="S857" s="2"/>
     </row>
-    <row r="858" spans="1:19" ht="13.2">
+    <row r="858" spans="1:19" ht="12.75">
       <c r="A858" s="2"/>
       <c r="B858" s="2"/>
       <c r="C858" s="2"/>
@@ -21598,7 +21601,7 @@
       <c r="R858" s="2"/>
       <c r="S858" s="2"/>
     </row>
-    <row r="859" spans="1:19" ht="13.2">
+    <row r="859" spans="1:19" ht="12.75">
       <c r="A859" s="2"/>
       <c r="B859" s="2"/>
       <c r="C859" s="2"/>
@@ -21619,7 +21622,7 @@
       <c r="R859" s="2"/>
       <c r="S859" s="2"/>
     </row>
-    <row r="860" spans="1:19" ht="13.2">
+    <row r="860" spans="1:19" ht="12.75">
       <c r="A860" s="2"/>
       <c r="B860" s="2"/>
       <c r="C860" s="2"/>
@@ -21640,7 +21643,7 @@
       <c r="R860" s="2"/>
       <c r="S860" s="2"/>
     </row>
-    <row r="861" spans="1:19" ht="13.2">
+    <row r="861" spans="1:19" ht="12.75">
       <c r="A861" s="2"/>
       <c r="B861" s="2"/>
       <c r="C861" s="2"/>
@@ -21661,7 +21664,7 @@
       <c r="R861" s="2"/>
       <c r="S861" s="2"/>
     </row>
-    <row r="862" spans="1:19" ht="13.2">
+    <row r="862" spans="1:19" ht="12.75">
       <c r="A862" s="2"/>
       <c r="B862" s="2"/>
       <c r="C862" s="2"/>
@@ -21682,7 +21685,7 @@
       <c r="R862" s="2"/>
       <c r="S862" s="2"/>
     </row>
-    <row r="863" spans="1:19" ht="13.2">
+    <row r="863" spans="1:19" ht="12.75">
       <c r="A863" s="2"/>
       <c r="B863" s="2"/>
       <c r="C863" s="2"/>
@@ -21703,7 +21706,7 @@
       <c r="R863" s="2"/>
       <c r="S863" s="2"/>
     </row>
-    <row r="864" spans="1:19" ht="13.2">
+    <row r="864" spans="1:19" ht="12.75">
       <c r="A864" s="2"/>
       <c r="B864" s="2"/>
       <c r="C864" s="2"/>
@@ -21724,7 +21727,7 @@
       <c r="R864" s="2"/>
       <c r="S864" s="2"/>
     </row>
-    <row r="865" spans="1:19" ht="13.2">
+    <row r="865" spans="1:19" ht="12.75">
       <c r="A865" s="2"/>
       <c r="B865" s="2"/>
       <c r="C865" s="2"/>
@@ -21745,7 +21748,7 @@
       <c r="R865" s="2"/>
       <c r="S865" s="2"/>
     </row>
-    <row r="866" spans="1:19" ht="13.2">
+    <row r="866" spans="1:19" ht="12.75">
       <c r="A866" s="2"/>
       <c r="B866" s="2"/>
       <c r="C866" s="2"/>
@@ -21766,7 +21769,7 @@
       <c r="R866" s="2"/>
       <c r="S866" s="2"/>
     </row>
-    <row r="867" spans="1:19" ht="13.2">
+    <row r="867" spans="1:19" ht="12.75">
       <c r="A867" s="2"/>
       <c r="B867" s="2"/>
       <c r="C867" s="2"/>
@@ -21787,7 +21790,7 @@
       <c r="R867" s="2"/>
       <c r="S867" s="2"/>
     </row>
-    <row r="868" spans="1:19" ht="13.2">
+    <row r="868" spans="1:19" ht="12.75">
       <c r="A868" s="2"/>
       <c r="B868" s="2"/>
       <c r="C868" s="2"/>
@@ -21808,7 +21811,7 @@
       <c r="R868" s="2"/>
       <c r="S868" s="2"/>
     </row>
-    <row r="869" spans="1:19" ht="13.2">
+    <row r="869" spans="1:19" ht="12.75">
       <c r="A869" s="2"/>
       <c r="B869" s="2"/>
       <c r="C869" s="2"/>
@@ -21829,7 +21832,7 @@
       <c r="R869" s="2"/>
       <c r="S869" s="2"/>
     </row>
-    <row r="870" spans="1:19" ht="13.2">
+    <row r="870" spans="1:19" ht="12.75">
       <c r="A870" s="2"/>
       <c r="B870" s="2"/>
       <c r="C870" s="2"/>
@@ -21850,7 +21853,7 @@
       <c r="R870" s="2"/>
       <c r="S870" s="2"/>
     </row>
-    <row r="871" spans="1:19" ht="13.2">
+    <row r="871" spans="1:19" ht="12.75">
       <c r="A871" s="2"/>
       <c r="B871" s="2"/>
       <c r="C871" s="2"/>
@@ -21871,7 +21874,7 @@
       <c r="R871" s="2"/>
       <c r="S871" s="2"/>
     </row>
-    <row r="872" spans="1:19" ht="13.2">
+    <row r="872" spans="1:19" ht="12.75">
       <c r="A872" s="2"/>
       <c r="B872" s="2"/>
       <c r="C872" s="2"/>
@@ -21892,7 +21895,7 @@
       <c r="R872" s="2"/>
       <c r="S872" s="2"/>
     </row>
-    <row r="873" spans="1:19" ht="13.2">
+    <row r="873" spans="1:19" ht="12.75">
       <c r="A873" s="2"/>
       <c r="B873" s="2"/>
       <c r="C873" s="2"/>
@@ -21913,7 +21916,7 @@
       <c r="R873" s="2"/>
       <c r="S873" s="2"/>
     </row>
-    <row r="874" spans="1:19" ht="13.2">
+    <row r="874" spans="1:19" ht="12.75">
       <c r="A874" s="2"/>
       <c r="B874" s="2"/>
       <c r="C874" s="2"/>
@@ -21934,7 +21937,7 @@
       <c r="R874" s="2"/>
       <c r="S874" s="2"/>
     </row>
-    <row r="875" spans="1:19" ht="13.2">
+    <row r="875" spans="1:19" ht="12.75">
       <c r="A875" s="2"/>
       <c r="B875" s="2"/>
       <c r="C875" s="2"/>
@@ -21955,7 +21958,7 @@
       <c r="R875" s="2"/>
       <c r="S875" s="2"/>
     </row>
-    <row r="876" spans="1:19" ht="13.2">
+    <row r="876" spans="1:19" ht="12.75">
       <c r="A876" s="2"/>
       <c r="B876" s="2"/>
       <c r="C876" s="2"/>
@@ -21976,7 +21979,7 @@
       <c r="R876" s="2"/>
       <c r="S876" s="2"/>
     </row>
-    <row r="877" spans="1:19" ht="13.2">
+    <row r="877" spans="1:19" ht="12.75">
       <c r="A877" s="2"/>
       <c r="B877" s="2"/>
       <c r="C877" s="2"/>
@@ -21997,7 +22000,7 @@
       <c r="R877" s="2"/>
       <c r="S877" s="2"/>
     </row>
-    <row r="878" spans="1:19" ht="13.2">
+    <row r="878" spans="1:19" ht="12.75">
       <c r="A878" s="2"/>
       <c r="B878" s="2"/>
       <c r="C878" s="2"/>
@@ -22018,7 +22021,7 @@
       <c r="R878" s="2"/>
       <c r="S878" s="2"/>
     </row>
-    <row r="879" spans="1:19" ht="13.2">
+    <row r="879" spans="1:19" ht="12.75">
       <c r="A879" s="2"/>
       <c r="B879" s="2"/>
       <c r="C879" s="2"/>
@@ -22039,7 +22042,7 @@
       <c r="R879" s="2"/>
       <c r="S879" s="2"/>
     </row>
-    <row r="880" spans="1:19" ht="13.2">
+    <row r="880" spans="1:19" ht="12.75">
       <c r="A880" s="2"/>
       <c r="B880" s="2"/>
       <c r="C880" s="2"/>
@@ -22060,7 +22063,7 @@
       <c r="R880" s="2"/>
       <c r="S880" s="2"/>
     </row>
-    <row r="881" spans="1:19" ht="13.2">
+    <row r="881" spans="1:19" ht="12.75">
       <c r="A881" s="2"/>
       <c r="B881" s="2"/>
       <c r="C881" s="2"/>
@@ -22081,7 +22084,7 @@
       <c r="R881" s="2"/>
       <c r="S881" s="2"/>
     </row>
-    <row r="882" spans="1:19" ht="13.2">
+    <row r="882" spans="1:19" ht="12.75">
       <c r="A882" s="2"/>
       <c r="B882" s="2"/>
       <c r="C882" s="2"/>
@@ -22102,7 +22105,7 @@
       <c r="R882" s="2"/>
       <c r="S882" s="2"/>
     </row>
-    <row r="883" spans="1:19" ht="13.2">
+    <row r="883" spans="1:19" ht="12.75">
       <c r="A883" s="2"/>
       <c r="B883" s="2"/>
       <c r="C883" s="2"/>
@@ -22123,7 +22126,7 @@
       <c r="R883" s="2"/>
       <c r="S883" s="2"/>
     </row>
-    <row r="884" spans="1:19" ht="13.2">
+    <row r="884" spans="1:19" ht="12.75">
       <c r="A884" s="2"/>
       <c r="B884" s="2"/>
       <c r="C884" s="2"/>
@@ -22144,7 +22147,7 @@
       <c r="R884" s="2"/>
       <c r="S884" s="2"/>
     </row>
-    <row r="885" spans="1:19" ht="13.2">
+    <row r="885" spans="1:19" ht="12.75">
       <c r="A885" s="2"/>
       <c r="B885" s="2"/>
       <c r="C885" s="2"/>
@@ -22165,7 +22168,7 @@
       <c r="R885" s="2"/>
       <c r="S885" s="2"/>
     </row>
-    <row r="886" spans="1:19" ht="13.2">
+    <row r="886" spans="1:19" ht="12.75">
       <c r="A886" s="2"/>
       <c r="B886" s="2"/>
       <c r="C886" s="2"/>
@@ -22186,7 +22189,7 @@
       <c r="R886" s="2"/>
       <c r="S886" s="2"/>
     </row>
-    <row r="887" spans="1:19" ht="13.2">
+    <row r="887" spans="1:19" ht="12.75">
       <c r="A887" s="2"/>
       <c r="B887" s="2"/>
       <c r="C887" s="2"/>
@@ -22207,7 +22210,7 @@
       <c r="R887" s="2"/>
       <c r="S887" s="2"/>
     </row>
-    <row r="888" spans="1:19" ht="13.2">
+    <row r="888" spans="1:19" ht="12.75">
       <c r="A888" s="2"/>
       <c r="B888" s="2"/>
       <c r="C888" s="2"/>
@@ -22228,7 +22231,7 @@
       <c r="R888" s="2"/>
       <c r="S888" s="2"/>
     </row>
-    <row r="889" spans="1:19" ht="13.2">
+    <row r="889" spans="1:19" ht="12.75">
       <c r="A889" s="2"/>
       <c r="B889" s="2"/>
       <c r="C889" s="2"/>
@@ -22249,7 +22252,7 @@
       <c r="R889" s="2"/>
       <c r="S889" s="2"/>
     </row>
-    <row r="890" spans="1:19" ht="13.2">
+    <row r="890" spans="1:19" ht="12.75">
       <c r="A890" s="2"/>
       <c r="B890" s="2"/>
       <c r="C890" s="2"/>
@@ -22270,7 +22273,7 @@
       <c r="R890" s="2"/>
       <c r="S890" s="2"/>
     </row>
-    <row r="891" spans="1:19" ht="13.2">
+    <row r="891" spans="1:19" ht="12.75">
       <c r="A891" s="2"/>
       <c r="B891" s="2"/>
       <c r="C891" s="2"/>
@@ -22291,7 +22294,7 @@
       <c r="R891" s="2"/>
       <c r="S891" s="2"/>
     </row>
-    <row r="892" spans="1:19" ht="13.2">
+    <row r="892" spans="1:19" ht="12.75">
       <c r="A892" s="2"/>
       <c r="B892" s="2"/>
       <c r="C892" s="2"/>
@@ -22312,7 +22315,7 @@
       <c r="R892" s="2"/>
       <c r="S892" s="2"/>
     </row>
-    <row r="893" spans="1:19" ht="13.2">
+    <row r="893" spans="1:19" ht="12.75">
       <c r="A893" s="2"/>
       <c r="B893" s="2"/>
       <c r="C893" s="2"/>
@@ -22333,7 +22336,7 @@
       <c r="R893" s="2"/>
       <c r="S893" s="2"/>
     </row>
-    <row r="894" spans="1:19" ht="13.2">
+    <row r="894" spans="1:19" ht="12.75">
       <c r="A894" s="2"/>
       <c r="B894" s="2"/>
       <c r="C894" s="2"/>
@@ -22354,7 +22357,7 @@
       <c r="R894" s="2"/>
       <c r="S894" s="2"/>
     </row>
-    <row r="895" spans="1:19" ht="13.2">
+    <row r="895" spans="1:19" ht="12.75">
       <c r="A895" s="2"/>
       <c r="B895" s="2"/>
       <c r="C895" s="2"/>
@@ -22375,7 +22378,7 @@
       <c r="R895" s="2"/>
       <c r="S895" s="2"/>
     </row>
-    <row r="896" spans="1:19" ht="13.2">
+    <row r="896" spans="1:19" ht="12.75">
       <c r="A896" s="2"/>
       <c r="B896" s="2"/>
       <c r="C896" s="2"/>
@@ -22396,7 +22399,7 @@
       <c r="R896" s="2"/>
       <c r="S896" s="2"/>
     </row>
-    <row r="897" spans="1:19" ht="13.2">
+    <row r="897" spans="1:19" ht="12.75">
       <c r="A897" s="2"/>
       <c r="B897" s="2"/>
       <c r="C897" s="2"/>
@@ -22417,7 +22420,7 @@
       <c r="R897" s="2"/>
       <c r="S897" s="2"/>
     </row>
-    <row r="898" spans="1:19" ht="13.2">
+    <row r="898" spans="1:19" ht="12.75">
       <c r="A898" s="2"/>
       <c r="B898" s="2"/>
       <c r="C898" s="2"/>
@@ -22438,7 +22441,7 @@
       <c r="R898" s="2"/>
       <c r="S898" s="2"/>
     </row>
-    <row r="899" spans="1:19" ht="13.2">
+    <row r="899" spans="1:19" ht="12.75">
       <c r="A899" s="2"/>
       <c r="B899" s="2"/>
       <c r="C899" s="2"/>
@@ -22459,7 +22462,7 @@
       <c r="R899" s="2"/>
       <c r="S899" s="2"/>
     </row>
-    <row r="900" spans="1:19" ht="13.2">
+    <row r="900" spans="1:19" ht="12.75">
       <c r="A900" s="2"/>
       <c r="B900" s="2"/>
       <c r="C900" s="2"/>
@@ -22480,7 +22483,7 @@
       <c r="R900" s="2"/>
       <c r="S900" s="2"/>
     </row>
-    <row r="901" spans="1:19" ht="13.2">
+    <row r="901" spans="1:19" ht="12.75">
       <c r="A901" s="2"/>
       <c r="B901" s="2"/>
       <c r="C901" s="2"/>
@@ -22501,7 +22504,7 @@
       <c r="R901" s="2"/>
       <c r="S901" s="2"/>
     </row>
-    <row r="902" spans="1:19" ht="13.2">
+    <row r="902" spans="1:19" ht="12.75">
       <c r="A902" s="2"/>
       <c r="B902" s="2"/>
       <c r="C902" s="2"/>
@@ -22522,7 +22525,7 @@
       <c r="R902" s="2"/>
       <c r="S902" s="2"/>
     </row>
-    <row r="903" spans="1:19" ht="13.2">
+    <row r="903" spans="1:19" ht="12.75">
       <c r="A903" s="2"/>
       <c r="B903" s="2"/>
       <c r="C903" s="2"/>
@@ -22543,7 +22546,7 @@
       <c r="R903" s="2"/>
       <c r="S903" s="2"/>
     </row>
-    <row r="904" spans="1:19" ht="13.2">
+    <row r="904" spans="1:19" ht="12.75">
       <c r="A904" s="2"/>
       <c r="B904" s="2"/>
       <c r="C904" s="2"/>
@@ -22564,7 +22567,7 @@
       <c r="R904" s="2"/>
       <c r="S904" s="2"/>
     </row>
-    <row r="905" spans="1:19" ht="13.2">
+    <row r="905" spans="1:19" ht="12.75">
       <c r="A905" s="2"/>
       <c r="B905" s="2"/>
       <c r="C905" s="2"/>
@@ -22585,7 +22588,7 @@
       <c r="R905" s="2"/>
       <c r="S905" s="2"/>
     </row>
-    <row r="906" spans="1:19" ht="13.2">
+    <row r="906" spans="1:19" ht="12.75">
       <c r="A906" s="2"/>
       <c r="B906" s="2"/>
       <c r="C906" s="2"/>
@@ -22606,7 +22609,7 @@
       <c r="R906" s="2"/>
       <c r="S906" s="2"/>
     </row>
-    <row r="907" spans="1:19" ht="13.2">
+    <row r="907" spans="1:19" ht="12.75">
       <c r="A907" s="2"/>
       <c r="B907" s="2"/>
       <c r="C907" s="2"/>
@@ -22627,7 +22630,7 @@
       <c r="R907" s="2"/>
       <c r="S907" s="2"/>
     </row>
-    <row r="908" spans="1:19" ht="13.2">
+    <row r="908" spans="1:19" ht="12.75">
       <c r="A908" s="2"/>
       <c r="B908" s="2"/>
       <c r="C908" s="2"/>
@@ -22648,7 +22651,7 @@
       <c r="R908" s="2"/>
       <c r="S908" s="2"/>
     </row>
-    <row r="909" spans="1:19" ht="13.2">
+    <row r="909" spans="1:19" ht="12.75">
       <c r="A909" s="2"/>
       <c r="B909" s="2"/>
       <c r="C909" s="2"/>
@@ -22669,7 +22672,7 @@
       <c r="R909" s="2"/>
       <c r="S909" s="2"/>
     </row>
-    <row r="910" spans="1:19" ht="13.2">
+    <row r="910" spans="1:19" ht="12.75">
       <c r="A910" s="2"/>
       <c r="B910" s="2"/>
       <c r="C910" s="2"/>
@@ -22690,7 +22693,7 @@
       <c r="R910" s="2"/>
       <c r="S910" s="2"/>
     </row>
-    <row r="911" spans="1:19" ht="13.2">
+    <row r="911" spans="1:19" ht="12.75">
       <c r="A911" s="2"/>
       <c r="B911" s="2"/>
       <c r="C911" s="2"/>
@@ -22711,7 +22714,7 @@
       <c r="R911" s="2"/>
       <c r="S911" s="2"/>
     </row>
-    <row r="912" spans="1:19" ht="13.2">
+    <row r="912" spans="1:19" ht="12.75">
       <c r="A912" s="2"/>
       <c r="B912" s="2"/>
       <c r="C912" s="2"/>
@@ -22732,7 +22735,7 @@
       <c r="R912" s="2"/>
       <c r="S912" s="2"/>
     </row>
-    <row r="913" spans="1:19" ht="13.2">
+    <row r="913" spans="1:19" ht="12.75">
       <c r="A913" s="2"/>
       <c r="B913" s="2"/>
       <c r="C913" s="2"/>
@@ -22753,7 +22756,7 @@
       <c r="R913" s="2"/>
       <c r="S913" s="2"/>
     </row>
-    <row r="914" spans="1:19" ht="13.2">
+    <row r="914" spans="1:19" ht="12.75">
       <c r="A914" s="2"/>
       <c r="B914" s="2"/>
       <c r="C914" s="2"/>
@@ -22774,7 +22777,7 @@
       <c r="R914" s="2"/>
       <c r="S914" s="2"/>
     </row>
-    <row r="915" spans="1:19" ht="13.2">
+    <row r="915" spans="1:19" ht="12.75">
       <c r="A915" s="2"/>
       <c r="B915" s="2"/>
       <c r="C915" s="2"/>
@@ -22795,7 +22798,7 @@
       <c r="R915" s="2"/>
       <c r="S915" s="2"/>
     </row>
-    <row r="916" spans="1:19" ht="13.2">
+    <row r="916" spans="1:19" ht="12.75">
       <c r="A916" s="2"/>
       <c r="B916" s="2"/>
       <c r="C916" s="2"/>
@@ -22816,7 +22819,7 @@
       <c r="R916" s="2"/>
       <c r="S916" s="2"/>
     </row>
-    <row r="917" spans="1:19" ht="13.2">
+    <row r="917" spans="1:19" ht="12.75">
       <c r="A917" s="2"/>
       <c r="B917" s="2"/>
       <c r="C917" s="2"/>
@@ -22837,7 +22840,7 @@
       <c r="R917" s="2"/>
       <c r="S917" s="2"/>
     </row>
-    <row r="918" spans="1:19" ht="13.2">
+    <row r="918" spans="1:19" ht="12.75">
       <c r="A918" s="2"/>
       <c r="B918" s="2"/>
       <c r="C918" s="2"/>
@@ -22858,7 +22861,7 @@
       <c r="R918" s="2"/>
       <c r="S918" s="2"/>
     </row>
-    <row r="919" spans="1:19" ht="13.2">
+    <row r="919" spans="1:19" ht="12.75">
       <c r="A919" s="2"/>
       <c r="B919" s="2"/>
       <c r="C919" s="2"/>
@@ -22879,7 +22882,7 @@
       <c r="R919" s="2"/>
       <c r="S919" s="2"/>
     </row>
-    <row r="920" spans="1:19" ht="13.2">
+    <row r="920" spans="1:19" ht="12.75">
       <c r="A920" s="2"/>
       <c r="B920" s="2"/>
       <c r="C920" s="2"/>
@@ -22900,7 +22903,7 @@
       <c r="R920" s="2"/>
       <c r="S920" s="2"/>
     </row>
-    <row r="921" spans="1:19" ht="13.2">
+    <row r="921" spans="1:19" ht="12.75">
       <c r="A921" s="2"/>
       <c r="B921" s="2"/>
       <c r="C921" s="2"/>
@@ -22921,7 +22924,7 @@
       <c r="R921" s="2"/>
       <c r="S921" s="2"/>
     </row>
-    <row r="922" spans="1:19" ht="13.2">
+    <row r="922" spans="1:19" ht="12.75">
       <c r="A922" s="2"/>
       <c r="B922" s="2"/>
       <c r="C922" s="2"/>
@@ -22942,7 +22945,7 @@
       <c r="R922" s="2"/>
       <c r="S922" s="2"/>
     </row>
-    <row r="923" spans="1:19" ht="13.2">
+    <row r="923" spans="1:19" ht="12.75">
       <c r="A923" s="2"/>
       <c r="B923" s="2"/>
       <c r="C923" s="2"/>
@@ -22963,7 +22966,7 @@
       <c r="R923" s="2"/>
       <c r="S923" s="2"/>
     </row>
-    <row r="924" spans="1:19" ht="13.2">
+    <row r="924" spans="1:19" ht="12.75">
       <c r="A924" s="2"/>
       <c r="B924" s="2"/>
       <c r="C924" s="2"/>
@@ -22984,7 +22987,7 @@
       <c r="R924" s="2"/>
       <c r="S924" s="2"/>
     </row>
-    <row r="925" spans="1:19" ht="13.2">
+    <row r="925" spans="1:19" ht="12.75">
       <c r="A925" s="2"/>
       <c r="B925" s="2"/>
       <c r="C925" s="2"/>
@@ -23005,7 +23008,7 @@
       <c r="R925" s="2"/>
       <c r="S925" s="2"/>
     </row>
-    <row r="926" spans="1:19" ht="13.2">
+    <row r="926" spans="1:19" ht="12.75">
       <c r="A926" s="2"/>
       <c r="B926" s="2"/>
       <c r="C926" s="2"/>
@@ -23026,7 +23029,7 @@
       <c r="R926" s="2"/>
       <c r="S926" s="2"/>
     </row>
-    <row r="927" spans="1:19" ht="13.2">
+    <row r="927" spans="1:19" ht="12.75">
       <c r="A927" s="2"/>
       <c r="B927" s="2"/>
       <c r="C927" s="2"/>
@@ -23047,7 +23050,7 @@
       <c r="R927" s="2"/>
       <c r="S927" s="2"/>
     </row>
-    <row r="928" spans="1:19" ht="13.2">
+    <row r="928" spans="1:19" ht="12.75">
       <c r="A928" s="2"/>
       <c r="B928" s="2"/>
       <c r="C928" s="2"/>
@@ -23068,7 +23071,7 @@
       <c r="R928" s="2"/>
       <c r="S928" s="2"/>
     </row>
-    <row r="929" spans="1:19" ht="13.2">
+    <row r="929" spans="1:19" ht="12.75">
       <c r="A929" s="2"/>
       <c r="B929" s="2"/>
       <c r="C929" s="2"/>
@@ -23089,7 +23092,7 @@
       <c r="R929" s="2"/>
       <c r="S929" s="2"/>
     </row>
-    <row r="930" spans="1:19" ht="13.2">
+    <row r="930" spans="1:19" ht="12.75">
       <c r="A930" s="2"/>
       <c r="B930" s="2"/>
       <c r="C930" s="2"/>
@@ -23110,7 +23113,7 @@
       <c r="R930" s="2"/>
       <c r="S930" s="2"/>
     </row>
-    <row r="931" spans="1:19" ht="13.2">
+    <row r="931" spans="1:19" ht="12.75">
       <c r="A931" s="2"/>
       <c r="B931" s="2"/>
       <c r="C931" s="2"/>
@@ -23131,7 +23134,7 @@
       <c r="R931" s="2"/>
       <c r="S931" s="2"/>
     </row>
-    <row r="932" spans="1:19" ht="13.2">
+    <row r="932" spans="1:19" ht="12.75">
       <c r="A932" s="2"/>
       <c r="B932" s="2"/>
       <c r="C932" s="2"/>
@@ -23152,7 +23155,7 @@
       <c r="R932" s="2"/>
       <c r="S932" s="2"/>
     </row>
-    <row r="933" spans="1:19" ht="13.2">
+    <row r="933" spans="1:19" ht="12.75">
       <c r="A933" s="2"/>
       <c r="B933" s="2"/>
       <c r="C933" s="2"/>
@@ -23173,7 +23176,7 @@
       <c r="R933" s="2"/>
       <c r="S933" s="2"/>
     </row>
-    <row r="934" spans="1:19" ht="13.2">
+    <row r="934" spans="1:19" ht="12.75">
       <c r="A934" s="2"/>
       <c r="B934" s="2"/>
       <c r="C934" s="2"/>
@@ -23194,7 +23197,7 @@
       <c r="R934" s="2"/>
       <c r="S934" s="2"/>
     </row>
-    <row r="935" spans="1:19" ht="13.2">
+    <row r="935" spans="1:19" ht="12.75">
       <c r="A935" s="2"/>
       <c r="B935" s="2"/>
       <c r="C935" s="2"/>
@@ -23215,7 +23218,7 @@
       <c r="R935" s="2"/>
       <c r="S935" s="2"/>
     </row>
-    <row r="936" spans="1:19" ht="13.2">
+    <row r="936" spans="1:19" ht="12.75">
       <c r="A936" s="2"/>
       <c r="B936" s="2"/>
       <c r="C936" s="2"/>
@@ -23236,7 +23239,7 @@
       <c r="R936" s="2"/>
       <c r="S936" s="2"/>
     </row>
-    <row r="937" spans="1:19" ht="13.2">
+    <row r="937" spans="1:19" ht="12.75">
       <c r="A937" s="2"/>
       <c r="B937" s="2"/>
       <c r="C937" s="2"/>
@@ -23257,7 +23260,7 @@
       <c r="R937" s="2"/>
       <c r="S937" s="2"/>
     </row>
-    <row r="938" spans="1:19" ht="13.2">
+    <row r="938" spans="1:19" ht="12.75">
       <c r="A938" s="2"/>
       <c r="B938" s="2"/>
       <c r="C938" s="2"/>
@@ -23278,7 +23281,7 @@
       <c r="R938" s="2"/>
       <c r="S938" s="2"/>
     </row>
-    <row r="939" spans="1:19" ht="13.2">
+    <row r="939" spans="1:19" ht="12.75">
       <c r="A939" s="2"/>
       <c r="B939" s="2"/>
       <c r="C939" s="2"/>
@@ -23299,7 +23302,7 @@
       <c r="R939" s="2"/>
       <c r="S939" s="2"/>
     </row>
-    <row r="940" spans="1:19" ht="13.2">
+    <row r="940" spans="1:19" ht="12.75">
       <c r="A940" s="2"/>
       <c r="B940" s="2"/>
       <c r="C940" s="2"/>
@@ -23320,7 +23323,7 @@
       <c r="R940" s="2"/>
       <c r="S940" s="2"/>
     </row>
-    <row r="941" spans="1:19" ht="13.2">
+    <row r="941" spans="1:19" ht="12.75">
       <c r="A941" s="2"/>
       <c r="B941" s="2"/>
       <c r="C941" s="2"/>
@@ -23341,7 +23344,7 @@
       <c r="R941" s="2"/>
       <c r="S941" s="2"/>
     </row>
-    <row r="942" spans="1:19" ht="13.2">
+    <row r="942" spans="1:19" ht="12.75">
       <c r="A942" s="2"/>
       <c r="B942" s="2"/>
       <c r="C942" s="2"/>
@@ -23362,7 +23365,7 @@
       <c r="R942" s="2"/>
       <c r="S942" s="2"/>
     </row>
-    <row r="943" spans="1:19" ht="13.2">
+    <row r="943" spans="1:19" ht="12.75">
       <c r="A943" s="2"/>
       <c r="B943" s="2"/>
       <c r="C943" s="2"/>
@@ -23383,7 +23386,7 @@
       <c r="R943" s="2"/>
       <c r="S943" s="2"/>
     </row>
-    <row r="944" spans="1:19" ht="13.2">
+    <row r="944" spans="1:19" ht="12.75">
       <c r="A944" s="2"/>
       <c r="B944" s="2"/>
       <c r="C944" s="2"/>
@@ -23404,7 +23407,7 @@
       <c r="R944" s="2"/>
       <c r="S944" s="2"/>
     </row>
-    <row r="945" spans="1:19" ht="13.2">
+    <row r="945" spans="1:19" ht="12.75">
       <c r="A945" s="2"/>
       <c r="B945" s="2"/>
       <c r="C945" s="2"/>
@@ -23425,7 +23428,7 @@
       <c r="R945" s="2"/>
       <c r="S945" s="2"/>
     </row>
-    <row r="946" spans="1:19" ht="13.2">
+    <row r="946" spans="1:19" ht="12.75">
       <c r="A946" s="2"/>
       <c r="B946" s="2"/>
       <c r="C946" s="2"/>
@@ -23446,7 +23449,7 @@
       <c r="R946" s="2"/>
       <c r="S946" s="2"/>
     </row>
-    <row r="947" spans="1:19" ht="13.2">
+    <row r="947" spans="1:19" ht="12.75">
       <c r="A947" s="2"/>
       <c r="B947" s="2"/>
       <c r="C947" s="2"/>
@@ -23467,7 +23470,7 @@
       <c r="R947" s="2"/>
       <c r="S947" s="2"/>
     </row>
-    <row r="948" spans="1:19" ht="13.2">
+    <row r="948" spans="1:19" ht="12.75">
       <c r="A948" s="2"/>
       <c r="B948" s="2"/>
       <c r="C948" s="2"/>
@@ -23488,7 +23491,7 @@
       <c r="R948" s="2"/>
       <c r="S948" s="2"/>
     </row>
-    <row r="949" spans="1:19" ht="13.2">
+    <row r="949" spans="1:19" ht="12.75">
       <c r="A949" s="2"/>
       <c r="B949" s="2"/>
       <c r="C949" s="2"/>
@@ -23509,7 +23512,7 @@
       <c r="R949" s="2"/>
       <c r="S949" s="2"/>
     </row>
-    <row r="950" spans="1:19" ht="13.2">
+    <row r="950" spans="1:19" ht="12.75">
       <c r="A950" s="2"/>
       <c r="B950" s="2"/>
       <c r="C950" s="2"/>
@@ -23530,7 +23533,7 @@
       <c r="R950" s="2"/>
       <c r="S950" s="2"/>
     </row>
-    <row r="951" spans="1:19" ht="13.2">
+    <row r="951" spans="1:19" ht="12.75">
       <c r="A951" s="2"/>
       <c r="B951" s="2"/>
       <c r="C951" s="2"/>
@@ -23551,7 +23554,7 @@
       <c r="R951" s="2"/>
       <c r="S951" s="2"/>
     </row>
-    <row r="952" spans="1:19" ht="13.2">
+    <row r="952" spans="1:19" ht="12.75">
       <c r="A952" s="2"/>
       <c r="B952" s="2"/>
       <c r="C952" s="2"/>
@@ -23572,7 +23575,7 @@
       <c r="R952" s="2"/>
       <c r="S952" s="2"/>
     </row>
-    <row r="953" spans="1:19" ht="13.2">
+    <row r="953" spans="1:19" ht="12.75">
       <c r="A953" s="2"/>
       <c r="B953" s="2"/>
       <c r="C953" s="2"/>
@@ -23593,7 +23596,7 @@
       <c r="R953" s="2"/>
       <c r="S953" s="2"/>
     </row>
-    <row r="954" spans="1:19" ht="13.2">
+    <row r="954" spans="1:19" ht="12.75">
       <c r="A954" s="2"/>
       <c r="B954" s="2"/>
       <c r="C954" s="2"/>
@@ -23614,7 +23617,7 @@
       <c r="R954" s="2"/>
       <c r="S954" s="2"/>
     </row>
-    <row r="955" spans="1:19" ht="13.2">
+    <row r="955" spans="1:19" ht="12.75">
       <c r="A955" s="2"/>
       <c r="B955" s="2"/>
       <c r="C955" s="2"/>
@@ -23635,7 +23638,7 @@
       <c r="R955" s="2"/>
       <c r="S955" s="2"/>
     </row>
-    <row r="956" spans="1:19" ht="13.2">
+    <row r="956" spans="1:19" ht="12.75">
       <c r="A956" s="2"/>
       <c r="B956" s="2"/>
       <c r="C956" s="2"/>
@@ -23656,7 +23659,7 @@
       <c r="R956" s="2"/>
       <c r="S956" s="2"/>
     </row>
-    <row r="957" spans="1:19" ht="13.2">
+    <row r="957" spans="1:19" ht="12.75">
       <c r="A957" s="2"/>
       <c r="B957" s="2"/>
       <c r="C957" s="2"/>
@@ -23677,7 +23680,7 @@
       <c r="R957" s="2"/>
       <c r="S957" s="2"/>
     </row>
-    <row r="958" spans="1:19" ht="13.2">
+    <row r="958" spans="1:19" ht="12.75">
       <c r="A958" s="2"/>
       <c r="B958" s="2"/>
       <c r="C958" s="2"/>
@@ -23698,7 +23701,7 @@
       <c r="R958" s="2"/>
       <c r="S958" s="2"/>
     </row>
-    <row r="959" spans="1:19" ht="13.2">
+    <row r="959" spans="1:19" ht="12.75">
       <c r="A959" s="2"/>
       <c r="B959" s="2"/>
       <c r="C959" s="2"/>
@@ -23719,7 +23722,7 @@
       <c r="R959" s="2"/>
       <c r="S959" s="2"/>
     </row>
-    <row r="960" spans="1:19" ht="13.2">
+    <row r="960" spans="1:19" ht="12.75">
       <c r="A960" s="2"/>
       <c r="B960" s="2"/>
       <c r="C960" s="2"/>
@@ -23740,7 +23743,7 @@
       <c r="R960" s="2"/>
       <c r="S960" s="2"/>
     </row>
-    <row r="961" spans="1:19" ht="13.2">
+    <row r="961" spans="1:19" ht="12.75">
       <c r="A961" s="2"/>
       <c r="B961" s="2"/>
       <c r="C961" s="2"/>
@@ -23761,7 +23764,7 @@
       <c r="R961" s="2"/>
       <c r="S961" s="2"/>
     </row>
-    <row r="962" spans="1:19" ht="13.2">
+    <row r="962" spans="1:19" ht="12.75">
       <c r="A962" s="2"/>
       <c r="B962" s="2"/>
       <c r="C962" s="2"/>
@@ -23782,7 +23785,7 @@
       <c r="R962" s="2"/>
       <c r="S962" s="2"/>
     </row>
-    <row r="963" spans="1:19" ht="13.2">
+    <row r="963" spans="1:19" ht="12.75">
       <c r="A963" s="2"/>
       <c r="B963" s="2"/>
       <c r="C963" s="2"/>
@@ -23803,7 +23806,7 @@
       <c r="R963" s="2"/>
       <c r="S963" s="2"/>
     </row>
-    <row r="964" spans="1:19" ht="13.2">
+    <row r="964" spans="1:19" ht="12.75">
       <c r="A964" s="2"/>
       <c r="B964" s="2"/>
       <c r="C964" s="2"/>
@@ -23824,7 +23827,7 @@
       <c r="R964" s="2"/>
       <c r="S964" s="2"/>
     </row>
-    <row r="965" spans="1:19" ht="13.2">
+    <row r="965" spans="1:19" ht="12.75">
       <c r="A965" s="2"/>
       <c r="B965" s="2"/>
       <c r="C965" s="2"/>
@@ -23845,7 +23848,7 @@
       <c r="R965" s="2"/>
       <c r="S965" s="2"/>
     </row>
-    <row r="966" spans="1:19" ht="13.2">
+    <row r="966" spans="1:19" ht="12.75">
       <c r="A966" s="2"/>
       <c r="B966" s="2"/>
       <c r="C966" s="2"/>
@@ -23866,7 +23869,7 @@
       <c r="R966" s="2"/>
       <c r="S966" s="2"/>
     </row>
-    <row r="967" spans="1:19" ht="13.2">
+    <row r="967" spans="1:19" ht="12.75">
       <c r="A967" s="2"/>
       <c r="B967" s="2"/>
       <c r="C967" s="2"/>
@@ -23887,7 +23890,7 @@
       <c r="R967" s="2"/>
       <c r="S967" s="2"/>
     </row>
-    <row r="968" spans="1:19" ht="13.2">
+    <row r="968" spans="1:19" ht="12.75">
       <c r="A968" s="2"/>
       <c r="B968" s="2"/>
       <c r="C968" s="2"/>
@@ -23908,7 +23911,7 @@
       <c r="R968" s="2"/>
       <c r="S968" s="2"/>
     </row>
-    <row r="969" spans="1:19" ht="13.2">
+    <row r="969" spans="1:19" ht="12.75">
       <c r="A969" s="2"/>
       <c r="B969" s="2"/>
       <c r="C969" s="2"/>
@@ -23929,7 +23932,7 @@
       <c r="R969" s="2"/>
       <c r="S969" s="2"/>
     </row>
-    <row r="970" spans="1:19" ht="13.2">
+    <row r="970" spans="1:19" ht="12.75">
       <c r="A970" s="2"/>
       <c r="B970" s="2"/>
       <c r="C970" s="2"/>
@@ -23950,7 +23953,7 @@
       <c r="R970" s="2"/>
       <c r="S970" s="2"/>
     </row>
-    <row r="971" spans="1:19" ht="13.2">
+    <row r="971" spans="1:19" ht="12.75">
       <c r="A971" s="2"/>
       <c r="B971" s="2"/>
       <c r="C971" s="2"/>
@@ -23971,7 +23974,7 @@
       <c r="R971" s="2"/>
       <c r="S971" s="2"/>
     </row>
-    <row r="972" spans="1:19" ht="13.2">
+    <row r="972" spans="1:19" ht="12.75">
       <c r="A972" s="2"/>
       <c r="B972" s="2"/>
       <c r="C972" s="2"/>
@@ -23992,7 +23995,7 @@
       <c r="R972" s="2"/>
       <c r="S972" s="2"/>
     </row>
-    <row r="973" spans="1:19" ht="13.2">
+    <row r="973" spans="1:19" ht="12.75">
       <c r="A973" s="2"/>
       <c r="B973" s="2"/>
       <c r="C973" s="2"/>
@@ -24013,7 +24016,7 @@
       <c r="R973" s="2"/>
       <c r="S973" s="2"/>
     </row>
-    <row r="974" spans="1:19" ht="13.2">
+    <row r="974" spans="1:19" ht="12.75">
       <c r="A974" s="2"/>
       <c r="B974" s="2"/>
       <c r="C974" s="2"/>
@@ -24034,7 +24037,7 @@
       <c r="R974" s="2"/>
       <c r="S974" s="2"/>
     </row>
-    <row r="975" spans="1:19" ht="13.2">
+    <row r="975" spans="1:19" ht="12.75">
       <c r="A975" s="2"/>
       <c r="B975" s="2"/>
       <c r="C975" s="2"/>
@@ -24055,7 +24058,7 @@
       <c r="R975" s="2"/>
       <c r="S975" s="2"/>
     </row>
-    <row r="976" spans="1:19" ht="13.2">
+    <row r="976" spans="1:19" ht="12.75">
       <c r="A976" s="2"/>
       <c r="B976" s="2"/>
       <c r="C976" s="2"/>
@@ -24076,7 +24079,7 @@
       <c r="R976" s="2"/>
       <c r="S976" s="2"/>
     </row>
-    <row r="977" spans="1:19" ht="13.2">
+    <row r="977" spans="1:19" ht="12.75">
       <c r="A977" s="2"/>
       <c r="B977" s="2"/>
       <c r="C977" s="2"/>
@@ -24097,7 +24100,7 @@
       <c r="R977" s="2"/>
       <c r="S977" s="2"/>
     </row>
-    <row r="978" spans="1:19" ht="13.2">
+    <row r="978" spans="1:19" ht="12.75">
       <c r="A978" s="2"/>
       <c r="B978" s="2"/>
       <c r="C978" s="2"/>
@@ -24118,7 +24121,7 @@
       <c r="R978" s="2"/>
       <c r="S978" s="2"/>
     </row>
-    <row r="979" spans="1:19" ht="13.2">
+    <row r="979" spans="1:19" ht="12.75">
       <c r="A979" s="2"/>
       <c r="B979" s="2"/>
       <c r="C979" s="2"/>
@@ -24139,7 +24142,7 @@
       <c r="R979" s="2"/>
       <c r="S979" s="2"/>
     </row>
-    <row r="980" spans="1:19" ht="13.2">
+    <row r="980" spans="1:19" ht="12.75">
       <c r="A980" s="2"/>
       <c r="B980" s="2"/>
       <c r="C980" s="2"/>
@@ -24160,7 +24163,7 @@
       <c r="R980" s="2"/>
       <c r="S980" s="2"/>
     </row>
-    <row r="981" spans="1:19" ht="13.2">
+    <row r="981" spans="1:19" ht="12.75">
       <c r="A981" s="2"/>
       <c r="B981" s="2"/>
       <c r="C981" s="2"/>
@@ -24181,7 +24184,7 @@
       <c r="R981" s="2"/>
       <c r="S981" s="2"/>
     </row>
-    <row r="982" spans="1:19" ht="13.2">
+    <row r="982" spans="1:19" ht="12.75">
       <c r="A982" s="2"/>
       <c r="B982" s="2"/>
       <c r="C982" s="2"/>
@@ -24202,7 +24205,7 @@
       <c r="R982" s="2"/>
       <c r="S982" s="2"/>
     </row>
-    <row r="983" spans="1:19" ht="13.2">
+    <row r="983" spans="1:19" ht="12.75">
       <c r="A983" s="2"/>
       <c r="B983" s="2"/>
       <c r="C983" s="2"/>
@@ -24223,7 +24226,7 @@
       <c r="R983" s="2"/>
       <c r="S983" s="2"/>
     </row>
-    <row r="984" spans="1:19" ht="13.2">
+    <row r="984" spans="1:19" ht="12.75">
       <c r="A984" s="2"/>
       <c r="B984" s="2"/>
       <c r="C984" s="2"/>
@@ -24244,7 +24247,7 @@
       <c r="R984" s="2"/>
       <c r="S984" s="2"/>
     </row>
-    <row r="985" spans="1:19" ht="13.2">
+    <row r="985" spans="1:19" ht="12.75">
       <c r="A985" s="2"/>
       <c r="B985" s="2"/>
       <c r="C985" s="2"/>
@@ -24265,7 +24268,7 @@
       <c r="R985" s="2"/>
       <c r="S985" s="2"/>
     </row>
-    <row r="986" spans="1:19" ht="13.2">
+    <row r="986" spans="1:19" ht="12.75">
       <c r="A986" s="2"/>
       <c r="B986" s="2"/>
       <c r="C986" s="2"/>
@@ -24286,7 +24289,7 @@
       <c r="R986" s="2"/>
       <c r="S986" s="2"/>
     </row>
-    <row r="987" spans="1:19" ht="13.2">
+    <row r="987" spans="1:19" ht="12.75">
       <c r="A987" s="2"/>
       <c r="B987" s="2"/>
       <c r="C987" s="2"/>
@@ -24307,7 +24310,7 @@
       <c r="R987" s="2"/>
       <c r="S987" s="2"/>
     </row>
-    <row r="988" spans="1:19" ht="13.2">
+    <row r="988" spans="1:19" ht="12.75">
       <c r="A988" s="2"/>
       <c r="B988" s="2"/>
       <c r="C988" s="2"/>
@@ -24328,7 +24331,7 @@
       <c r="R988" s="2"/>
       <c r="S988" s="2"/>
     </row>
-    <row r="989" spans="1:19" ht="13.2">
+    <row r="989" spans="1:19" ht="12.75">
       <c r="A989" s="2"/>
       <c r="B989" s="2"/>
       <c r="C989" s="2"/>
@@ -24349,7 +24352,7 @@
       <c r="R989" s="2"/>
       <c r="S989" s="2"/>
     </row>
-    <row r="990" spans="1:19" ht="13.2">
+    <row r="990" spans="1:19" ht="12.75">
       <c r="A990" s="2"/>
       <c r="B990" s="2"/>
       <c r="C990" s="2"/>
@@ -24370,7 +24373,7 @@
       <c r="R990" s="2"/>
       <c r="S990" s="2"/>
     </row>
-    <row r="991" spans="1:19" ht="13.2">
+    <row r="991" spans="1:19" ht="12.75">
       <c r="A991" s="2"/>
       <c r="B991" s="2"/>
       <c r="C991" s="2"/>
@@ -24391,7 +24394,7 @@
       <c r="R991" s="2"/>
       <c r="S991" s="2"/>
     </row>
-    <row r="992" spans="1:19" ht="13.2">
+    <row r="992" spans="1:19" ht="12.75">
       <c r="A992" s="2"/>
       <c r="B992" s="2"/>
       <c r="C992" s="2"/>
@@ -24412,7 +24415,7 @@
       <c r="R992" s="2"/>
       <c r="S992" s="2"/>
     </row>
-    <row r="993" spans="1:19" ht="13.2">
+    <row r="993" spans="1:19" ht="12.75">
       <c r="A993" s="2"/>
       <c r="B993" s="2"/>
       <c r="C993" s="2"/>
@@ -24433,7 +24436,7 @@
       <c r="R993" s="2"/>
       <c r="S993" s="2"/>
     </row>
-    <row r="994" spans="1:19" ht="13.2">
+    <row r="994" spans="1:19" ht="12.75">
       <c r="A994" s="2"/>
       <c r="B994" s="2"/>
       <c r="C994" s="2"/>
@@ -24454,7 +24457,7 @@
       <c r="R994" s="2"/>
       <c r="S994" s="2"/>
     </row>
-    <row r="995" spans="1:19" ht="13.2">
+    <row r="995" spans="1:19" ht="12.75">
       <c r="A995" s="2"/>
       <c r="B995" s="2"/>
       <c r="C995" s="2"/>
@@ -24475,7 +24478,7 @@
       <c r="R995" s="2"/>
       <c r="S995" s="2"/>
     </row>
-    <row r="996" spans="1:19" ht="13.2">
+    <row r="996" spans="1:19" ht="12.75">
       <c r="A996" s="2"/>
       <c r="B996" s="2"/>
       <c r="C996" s="2"/>
@@ -24496,7 +24499,7 @@
       <c r="R996" s="2"/>
       <c r="S996" s="2"/>
     </row>
-    <row r="997" spans="1:19" ht="13.2">
+    <row r="997" spans="1:19" ht="12.75">
       <c r="A997" s="2"/>
       <c r="B997" s="2"/>
       <c r="C997" s="2"/>
@@ -24517,7 +24520,7 @@
       <c r="R997" s="2"/>
       <c r="S997" s="2"/>
     </row>
-    <row r="998" spans="1:19" ht="13.2">
+    <row r="998" spans="1:19" ht="12.75">
       <c r="A998" s="2"/>
       <c r="B998" s="2"/>
       <c r="C998" s="2"/>
@@ -24538,7 +24541,7 @@
       <c r="R998" s="2"/>
       <c r="S998" s="2"/>
     </row>
-    <row r="999" spans="1:19" ht="13.2">
+    <row r="999" spans="1:19" ht="12.75">
       <c r="A999" s="2"/>
       <c r="B999" s="2"/>
       <c r="C999" s="2"/>
@@ -24559,7 +24562,7 @@
       <c r="R999" s="2"/>
       <c r="S999" s="2"/>
     </row>
-    <row r="1000" spans="1:19" ht="13.2">
+    <row r="1000" spans="1:19" ht="12.75">
       <c r="A1000" s="2"/>
       <c r="B1000" s="2"/>
       <c r="C1000" s="2"/>
@@ -24580,7 +24583,7 @@
       <c r="R1000" s="2"/>
       <c r="S1000" s="2"/>
     </row>
-    <row r="1001" spans="1:19" ht="13.2">
+    <row r="1001" spans="1:19" ht="12.75">
       <c r="A1001" s="2"/>
       <c r="B1001" s="2"/>
       <c r="C1001" s="2"/>
@@ -24601,7 +24604,7 @@
       <c r="R1001" s="2"/>
       <c r="S1001" s="2"/>
     </row>
-    <row r="1002" spans="1:19" ht="13.2">
+    <row r="1002" spans="1:19" ht="12.75">
       <c r="A1002" s="2"/>
       <c r="B1002" s="2"/>
       <c r="C1002" s="2"/>
@@ -24622,7 +24625,7 @@
       <c r="R1002" s="2"/>
       <c r="S1002" s="2"/>
     </row>
-    <row r="1003" spans="1:19" ht="13.2">
+    <row r="1003" spans="1:19" ht="12.75">
       <c r="A1003" s="2"/>
       <c r="B1003" s="2"/>
       <c r="C1003" s="2"/>
@@ -24643,7 +24646,7 @@
       <c r="R1003" s="2"/>
       <c r="S1003" s="2"/>
     </row>
-    <row r="1004" spans="1:19" ht="13.2">
+    <row r="1004" spans="1:19" ht="12.75">
       <c r="A1004" s="2"/>
       <c r="B1004" s="2"/>
       <c r="C1004" s="2"/>
@@ -24664,7 +24667,7 @@
       <c r="R1004" s="2"/>
       <c r="S1004" s="2"/>
     </row>
-    <row r="1005" spans="1:19" ht="13.2">
+    <row r="1005" spans="1:19" ht="12.75">
       <c r="A1005" s="2"/>
       <c r="B1005" s="2"/>
       <c r="C1005" s="2"/>
@@ -24685,7 +24688,7 @@
       <c r="R1005" s="2"/>
       <c r="S1005" s="2"/>
     </row>
-    <row r="1006" spans="1:19" ht="13.2">
+    <row r="1006" spans="1:19" ht="12.75">
       <c r="A1006" s="2"/>
       <c r="B1006" s="2"/>
       <c r="C1006" s="2"/>
@@ -24706,7 +24709,7 @@
       <c r="R1006" s="2"/>
       <c r="S1006" s="2"/>
     </row>
-    <row r="1007" spans="1:19" ht="13.2">
+    <row r="1007" spans="1:19" ht="12.75">
       <c r="A1007" s="2"/>
       <c r="B1007" s="2"/>
       <c r="C1007" s="2"/>
@@ -24727,7 +24730,7 @@
       <c r="R1007" s="2"/>
       <c r="S1007" s="2"/>
     </row>
-    <row r="1008" spans="1:19" ht="13.2">
+    <row r="1008" spans="1:19" ht="12.75">
       <c r="A1008" s="2"/>
       <c r="B1008" s="2"/>
       <c r="C1008" s="2"/>
@@ -24748,7 +24751,7 @@
       <c r="R1008" s="2"/>
       <c r="S1008" s="2"/>
     </row>
-    <row r="1009" spans="1:19" ht="13.2">
+    <row r="1009" spans="1:19" ht="12.75">
       <c r="A1009" s="2"/>
       <c r="B1009" s="2"/>
       <c r="C1009" s="2"/>
@@ -24769,7 +24772,7 @@
       <c r="R1009" s="2"/>
       <c r="S1009" s="2"/>
     </row>
-    <row r="1010" spans="1:19" ht="13.2">
+    <row r="1010" spans="1:19" ht="12.75">
       <c r="A1010" s="2"/>
       <c r="B1010" s="2"/>
       <c r="C1010" s="2"/>
@@ -24790,7 +24793,7 @@
       <c r="R1010" s="2"/>
       <c r="S1010" s="2"/>
     </row>
-    <row r="1011" spans="1:19" ht="13.2">
+    <row r="1011" spans="1:19" ht="12.75">
       <c r="A1011" s="2"/>
       <c r="B1011" s="2"/>
       <c r="C1011" s="2"/>
@@ -24811,7 +24814,7 @@
       <c r="R1011" s="2"/>
       <c r="S1011" s="2"/>
     </row>
-    <row r="1012" spans="1:19" ht="13.2">
+    <row r="1012" spans="1:19" ht="12.75">
       <c r="A1012" s="2"/>
       <c r="B1012" s="2"/>
       <c r="C1012" s="2"/>
@@ -24832,7 +24835,7 @@
       <c r="R1012" s="2"/>
       <c r="S1012" s="2"/>
     </row>
-    <row r="1013" spans="1:19" ht="13.2">
+    <row r="1013" spans="1:19" ht="12.75">
       <c r="A1013" s="2"/>
       <c r="B1013" s="2"/>
       <c r="C1013" s="2"/>
@@ -24853,7 +24856,7 @@
       <c r="R1013" s="2"/>
       <c r="S1013" s="2"/>
     </row>
-    <row r="1014" spans="1:19" ht="13.2">
+    <row r="1014" spans="1:19" ht="12.75">
       <c r="A1014" s="2"/>
       <c r="B1014" s="2"/>
       <c r="C1014" s="2"/>
@@ -24874,7 +24877,7 @@
       <c r="R1014" s="2"/>
       <c r="S1014" s="2"/>
     </row>
-    <row r="1015" spans="1:19" ht="13.2">
+    <row r="1015" spans="1:19" ht="12.75">
       <c r="A1015" s="2"/>
       <c r="B1015" s="2"/>
       <c r="C1015" s="2"/>
@@ -24895,7 +24898,7 @@
       <c r="R1015" s="2"/>
       <c r="S1015" s="2"/>
     </row>
-    <row r="1016" spans="1:19" ht="13.2">
+    <row r="1016" spans="1:19" ht="12.75">
       <c r="A1016" s="2"/>
       <c r="B1016" s="2"/>
       <c r="C1016" s="2"/>
@@ -24916,7 +24919,7 @@
       <c r="R1016" s="2"/>
       <c r="S1016" s="2"/>
     </row>
-    <row r="1017" spans="1:19" ht="13.2">
+    <row r="1017" spans="1:19" ht="12.75">
       <c r="A1017" s="2"/>
       <c r="B1017" s="2"/>
       <c r="C1017" s="2"/>
@@ -24937,7 +24940,7 @@
       <c r="R1017" s="2"/>
       <c r="S1017" s="2"/>
     </row>
-    <row r="1018" spans="1:19" ht="13.2">
+    <row r="1018" spans="1:19" ht="12.75">
       <c r="A1018" s="2"/>
       <c r="B1018" s="2"/>
       <c r="C1018" s="2"/>
@@ -24958,7 +24961,7 @@
       <c r="R1018" s="2"/>
       <c r="S1018" s="2"/>
     </row>
-    <row r="1019" spans="1:19" ht="13.2">
+    <row r="1019" spans="1:19" ht="12.75">
       <c r="A1019" s="2"/>
       <c r="B1019" s="2"/>
       <c r="C1019" s="2"/>
@@ -24979,7 +24982,7 @@
       <c r="R1019" s="2"/>
       <c r="S1019" s="2"/>
     </row>
-    <row r="1020" spans="1:19" ht="13.2">
+    <row r="1020" spans="1:19" ht="12.75">
       <c r="A1020" s="2"/>
       <c r="B1020" s="2"/>
       <c r="C1020" s="2"/>
@@ -25000,7 +25003,7 @@
       <c r="R1020" s="2"/>
       <c r="S1020" s="2"/>
     </row>
-    <row r="1021" spans="1:19" ht="13.2">
+    <row r="1021" spans="1:19" ht="12.75">
       <c r="A1021" s="2"/>
       <c r="B1021" s="2"/>
       <c r="C1021" s="2"/>
@@ -25021,7 +25024,7 @@
       <c r="R1021" s="2"/>
       <c r="S1021" s="2"/>
     </row>
-    <row r="1022" spans="1:19" ht="13.2">
+    <row r="1022" spans="1:19" ht="12.75">
       <c r="A1022" s="2"/>
       <c r="B1022" s="2"/>
       <c r="C1022" s="2"/>
@@ -25042,7 +25045,7 @@
       <c r="R1022" s="2"/>
       <c r="S1022" s="2"/>
     </row>
-    <row r="1023" spans="1:19" ht="13.2">
+    <row r="1023" spans="1:19" ht="12.75">
       <c r="A1023" s="2"/>
       <c r="B1023" s="2"/>
       <c r="C1023" s="2"/>
@@ -25063,7 +25066,7 @@
       <c r="R1023" s="2"/>
       <c r="S1023" s="2"/>
     </row>
-    <row r="1024" spans="1:19" ht="13.2">
+    <row r="1024" spans="1:19" ht="12.75">
       <c r="A1024" s="2"/>
       <c r="B1024" s="2"/>
       <c r="C1024" s="2"/>
@@ -25084,7 +25087,7 @@
       <c r="R1024" s="2"/>
       <c r="S1024" s="2"/>
     </row>
-    <row r="1025" spans="1:19" ht="13.2">
+    <row r="1025" spans="1:19" ht="12.75">
       <c r="A1025" s="2"/>
       <c r="B1025" s="2"/>
       <c r="C1025" s="2"/>
@@ -25105,7 +25108,7 @@
       <c r="R1025" s="2"/>
       <c r="S1025" s="2"/>
     </row>
-    <row r="1026" spans="1:19" ht="13.2">
+    <row r="1026" spans="1:19" ht="12.75">
       <c r="A1026" s="2"/>
       <c r="B1026" s="2"/>
       <c r="C1026" s="2"/>
@@ -25126,7 +25129,7 @@
       <c r="R1026" s="2"/>
       <c r="S1026" s="2"/>
     </row>
-    <row r="1027" spans="1:19" ht="13.2">
+    <row r="1027" spans="1:19" ht="12.75">
       <c r="A1027" s="2"/>
       <c r="B1027" s="2"/>
       <c r="C1027" s="2"/>
@@ -25147,7 +25150,7 @@
       <c r="R1027" s="2"/>
       <c r="S1027" s="2"/>
     </row>
-    <row r="1028" spans="1:19" ht="13.2">
+    <row r="1028" spans="1:19" ht="12.75">
       <c r="A1028" s="2"/>
       <c r="B1028" s="2"/>
       <c r="C1028" s="2"/>
@@ -25168,7 +25171,7 @@
       <c r="R1028" s="2"/>
       <c r="S1028" s="2"/>
     </row>
-    <row r="1029" spans="1:19" ht="13.2">
+    <row r="1029" spans="1:19" ht="12.75">
       <c r="A1029" s="2"/>
       <c r="B1029" s="2"/>
       <c r="C1029" s="2"/>
@@ -25189,7 +25192,7 @@
       <c r="R1029" s="2"/>
       <c r="S1029" s="2"/>
     </row>
-    <row r="1030" spans="1:19" ht="13.2">
+    <row r="1030" spans="1:19" ht="12.75">
       <c r="A1030" s="2"/>
       <c r="B1030" s="2"/>
       <c r="C1030" s="2"/>
@@ -25210,7 +25213,7 @@
       <c r="R1030" s="2"/>
       <c r="S1030" s="2"/>
     </row>
-    <row r="1031" spans="1:19" ht="13.2">
+    <row r="1031" spans="1:19" ht="12.75">
       <c r="A1031" s="2"/>
       <c r="B1031" s="2"/>
       <c r="C1031" s="2"/>
@@ -25231,7 +25234,7 @@
       <c r="R1031" s="2"/>
       <c r="S1031" s="2"/>
     </row>
-    <row r="1032" spans="1:19" ht="13.2">
+    <row r="1032" spans="1:19" ht="12.75">
       <c r="A1032" s="2"/>
       <c r="B1032" s="2"/>
       <c r="C1032" s="2"/>
@@ -25252,7 +25255,7 @@
       <c r="R1032" s="2"/>
       <c r="S1032" s="2"/>
     </row>
-    <row r="1033" spans="1:19" ht="13.2">
+    <row r="1033" spans="1:19" ht="12.75">
       <c r="A1033" s="2"/>
       <c r="B1033" s="2"/>
       <c r="C1033" s="2"/>
@@ -25273,7 +25276,7 @@
       <c r="R1033" s="2"/>
       <c r="S1033" s="2"/>
     </row>
-    <row r="1034" spans="1:19" ht="13.2">
+    <row r="1034" spans="1:19" ht="12.75">
       <c r="A1034" s="2"/>
       <c r="B1034" s="2"/>
       <c r="C1034" s="2"/>
@@ -25294,7 +25297,7 @@
       <c r="R1034" s="2"/>
       <c r="S1034" s="2"/>
     </row>
-    <row r="1035" spans="1:19" ht="13.2">
+    <row r="1035" spans="1:19" ht="12.75">
       <c r="A1035" s="2"/>
       <c r="B1035" s="2"/>
       <c r="C1035" s="2"/>
@@ -25315,7 +25318,7 @@
       <c r="R1035" s="2"/>
       <c r="S1035" s="2"/>
     </row>
-    <row r="1036" spans="1:19" ht="13.2">
+    <row r="1036" spans="1:19" ht="12.75">
       <c r="A1036" s="2"/>
       <c r="B1036" s="2"/>
       <c r="C1036" s="2"/>
